--- a/Automation Anywhere/Bots/TrivalentePolizas/Docs/Config.xlsx
+++ b/Automation Anywhere/Bots/TrivalentePolizas/Docs/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emergys1-my.sharepoint.com/personal/hector_agraz_emergys_com/Documents/PoC/trivalente/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="706" documentId="13_ncr:1_{C7F5C9BE-343D-4A21-9979-4AFCA04948A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71018E17-7F6F-4469-9877-7B3660D876D9}"/>
+  <xr:revisionPtr revIDLastSave="773" documentId="13_ncr:1_{C7F5C9BE-343D-4A21-9979-4AFCA04948A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9345451-C25E-4D90-8953-9BDBE3B0F4A2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="74">
   <si>
     <t>Name</t>
   </si>
@@ -101,9 +101,6 @@
     <t>C:\RPA\Trivalente\Scripts\</t>
   </si>
   <si>
-    <t>C:\RPA\Trivalente\Logs\{y}\{m}\</t>
-  </si>
-  <si>
     <t>C:\RPA\Trivalente\</t>
   </si>
   <si>
@@ -111,9 +108,6 @@
   </si>
   <si>
     <t>C:\AdminXML\MiAdminXML.exe</t>
-  </si>
-  <si>
-    <t>PathCompaqI</t>
   </si>
   <si>
     <t>PathDocs</t>
@@ -280,6 +274,60 @@
  &lt;/table&gt;
    &lt;/body&gt;
   &lt;/html&gt;</t>
+  </si>
+  <si>
+    <t>Identificador</t>
+  </si>
+  <si>
+    <t>CompanyRFC</t>
+  </si>
+  <si>
+    <t>RetryBot</t>
+  </si>
+  <si>
+    <t>PathContpaqI</t>
+  </si>
+  <si>
+    <t>SheetRFC</t>
+  </si>
+  <si>
+    <t>RFC</t>
+  </si>
+  <si>
+    <t>C:\RPA\Trivalente\Logs\{y}\{m}</t>
+  </si>
+  <si>
+    <t>PathXMLEmitted</t>
+  </si>
+  <si>
+    <t>C:\AdminXML\BovedaCFDi\{0}\Emitidas\{y}\{m}\</t>
+  </si>
+  <si>
+    <t>PathXMLRecived</t>
+  </si>
+  <si>
+    <t>C:\AdminXML\BovedaCFDi\{0}\Recibidas\{y}\{m}\</t>
+  </si>
+  <si>
+    <t>PathXMLDif</t>
+  </si>
+  <si>
+    <t>Emitidas</t>
+  </si>
+  <si>
+    <t>hector.agraz@emergys.com</t>
+  </si>
+  <si>
+    <t>FiscalReportXlsx</t>
+  </si>
+  <si>
+    <t>Concentrado Fiscal</t>
+  </si>
+  <si>
+    <t>ReportExt</t>
+  </si>
+  <si>
+    <t>.xlsx</t>
   </si>
 </sst>
 </file>
@@ -359,7 +407,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -369,6 +417,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -653,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -683,48 +732,48 @@
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>12</v>
+      <c r="B3" s="7" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" t="s">
-        <v>12</v>
+      <c r="B6" s="7" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -743,10 +792,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -759,7 +808,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -767,7 +816,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -780,10 +829,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -791,7 +840,7 @@
         <v>17</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -807,7 +856,7 @@
         <v>11</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -815,7 +864,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -823,102 +872,170 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
+        <v>63</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>51</v>
+        <v>70</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B34" s="1" t="s">
         <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A36:C36"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{7E2A60B6-5F3A-4B23-8FE5-01F213F08C6C}"/>
+    <hyperlink ref="B6" r:id="rId2" xr:uid="{3546B9DB-36BC-4906-B1CC-9C3F62CA4285}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
--- a/Automation Anywhere/Bots/TrivalentePolizas/Docs/Config.xlsx
+++ b/Automation Anywhere/Bots/TrivalentePolizas/Docs/Config.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emergys1-my.sharepoint.com/personal/hector_agraz_emergys_com/Documents/PoC/trivalente/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="773" documentId="13_ncr:1_{C7F5C9BE-343D-4A21-9979-4AFCA04948A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9345451-C25E-4D90-8953-9BDBE3B0F4A2}"/>
+  <xr:revisionPtr revIDLastSave="447" documentId="13_ncr:1_{62BB57DF-9B20-48A6-BABA-6E1C1C45F8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1016ED09-9D24-4846-AE4E-59EAB1473C75}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1080" yWindow="-13620" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcMode="manual"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="214">
   <si>
     <t>Name</t>
   </si>
@@ -74,9 +74,6 @@
     <t>PathLogs</t>
   </si>
   <si>
-    <t>hector.agraz@emergys.com;gamaliel.herrera@emergys.com</t>
-  </si>
-  <si>
     <t>StartBot</t>
   </si>
   <si>
@@ -146,9 +143,6 @@
     <t>ProjectCode</t>
   </si>
   <si>
-    <t>GenerarPolizas</t>
-  </si>
-  <si>
     <t>StartSubject</t>
   </si>
   <si>
@@ -158,12 +152,6 @@
     <t>StartBody</t>
   </si>
   <si>
-    <t>{U}\OneDrive - Emergys\Trivalente\Inputs\</t>
-  </si>
-  <si>
-    <t>{U}\OneDrive - Emergys\Trivalente\Catalogo Empresas.xlsx</t>
-  </si>
-  <si>
     <t>EndSubject</t>
   </si>
   <si>
@@ -195,9 +183,6 @@
   </si>
   <si>
     <t>SheetEmpresas</t>
-  </si>
-  <si>
-    <t>Empresas</t>
   </si>
   <si>
     <t>&lt;html&gt;
@@ -291,50 +276,502 @@
     <t>SheetRFC</t>
   </si>
   <si>
-    <t>RFC</t>
-  </si>
-  <si>
     <t>C:\RPA\Trivalente\Logs\{y}\{m}</t>
   </si>
   <si>
     <t>PathXMLEmitted</t>
   </si>
   <si>
-    <t>C:\AdminXML\BovedaCFDi\{0}\Emitidas\{y}\{m}\</t>
-  </si>
-  <si>
     <t>PathXMLRecived</t>
   </si>
   <si>
-    <t>C:\AdminXML\BovedaCFDi\{0}\Recibidas\{y}\{m}\</t>
-  </si>
-  <si>
     <t>PathXMLDif</t>
   </si>
   <si>
     <t>Emitidas</t>
   </si>
   <si>
+    <t>FiscalReportXlsx</t>
+  </si>
+  <si>
+    <t>Concentrado Fiscal</t>
+  </si>
+  <si>
+    <t>ReportExt</t>
+  </si>
+  <si>
+    <t>.xlsx</t>
+  </si>
+  <si>
+    <t>ErrorBot</t>
+  </si>
+  <si>
+    <t>XmlLoaded</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>XmlLoaded2</t>
+  </si>
+  <si>
+    <t>sPathSSXml</t>
+  </si>
+  <si>
+    <t>{0} ErrorXML.png</t>
+  </si>
+  <si>
+    <t>XMLsNotificationMail</t>
+  </si>
+  <si>
+    <t>XMlsNotificationSubject</t>
+  </si>
+  <si>
+    <t>XMLsNotificationBody</t>
+  </si>
+  <si>
+    <t>Data Config</t>
+  </si>
+  <si>
+    <t>LeapPxY</t>
+  </si>
+  <si>
+    <t>TotalRowLoadXMLE</t>
+  </si>
+  <si>
+    <t>TotalRowLoadXMLR</t>
+  </si>
+  <si>
+    <t>ProjectCode1</t>
+  </si>
+  <si>
+    <t>cer</t>
+  </si>
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>txt</t>
+  </si>
+  <si>
+    <t>Unavailable</t>
+  </si>
+  <si>
+    <t>ButonUnavailable</t>
+  </si>
+  <si>
+    <t>Vigent</t>
+  </si>
+  <si>
+    <t>Vigente</t>
+  </si>
+  <si>
+    <t>FormatYearXML</t>
+  </si>
+  <si>
+    <t>FormatMonthXML</t>
+  </si>
+  <si>
+    <t>yyyy</t>
+  </si>
+  <si>
+    <t>InitialDayXML</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>DateSeparation</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>MM</t>
+  </si>
+  <si>
+    <t>Error en la carga del XML.</t>
+  </si>
+  <si>
+    <t>ColumDate</t>
+  </si>
+  <si>
+    <t>ColumCompanyName</t>
+  </si>
+  <si>
+    <t>ColumNoPolicy</t>
+  </si>
+  <si>
+    <t>Sheet Accounts</t>
+  </si>
+  <si>
+    <t>ColumConsecutiveA</t>
+  </si>
+  <si>
+    <t>ColumTypeReceipt</t>
+  </si>
+  <si>
+    <t>Invoice</t>
+  </si>
+  <si>
+    <t>Factura</t>
+  </si>
+  <si>
+    <t>ValidatePolicy</t>
+  </si>
+  <si>
+    <t>FunctionPolicyInvoice</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>ColumIE</t>
+  </si>
+  <si>
+    <t>C:\RPA\Trivalente\History\{y}\{m}\</t>
+  </si>
+  <si>
+    <t>FileReportInvoices</t>
+  </si>
+  <si>
+    <t>{0} Reporte de facturas.xlsx</t>
+  </si>
+  <si>
+    <t>PathHistory</t>
+  </si>
+  <si>
+    <t>Process</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>NoProcess</t>
+  </si>
+  <si>
+    <t>RFC MXN</t>
+  </si>
+  <si>
+    <t>Empresas MXN</t>
+  </si>
+  <si>
+    <t>CreditablePaid</t>
+  </si>
+  <si>
+    <t>ConceptBank</t>
+  </si>
+  <si>
+    <t>Tranferencia</t>
+  </si>
+  <si>
+    <t>Outstanding</t>
+  </si>
+  <si>
+    <t>ProjectCode2</t>
+  </si>
+  <si>
+    <t>Ingreso</t>
+  </si>
+  <si>
+    <t>Income</t>
+  </si>
+  <si>
+    <t>Clientes</t>
+  </si>
+  <si>
+    <t>SheetIncome</t>
+  </si>
+  <si>
+    <t>SheetEgress</t>
+  </si>
+  <si>
+    <t>Proveedores</t>
+  </si>
+  <si>
+    <t>q</t>
+  </si>
+  <si>
+    <t>ColumnStatusReport</t>
+  </si>
+  <si>
+    <t>Rep</t>
+  </si>
+  <si>
+    <t>CurrencyUSD</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>CurrencyMXN</t>
+  </si>
+  <si>
+    <t>MXN</t>
+  </si>
+  <si>
+    <t>COBRO A CLIENTES VÍA REP MXN</t>
+  </si>
+  <si>
+    <t>ChargeCustRepMXN</t>
+  </si>
+  <si>
+    <t>COBRO A CLIENTES VÍA FACTURA MXN</t>
+  </si>
+  <si>
+    <t>ChargeCustInvMXN</t>
+  </si>
+  <si>
+    <t>ChargeCustRepUSD</t>
+  </si>
+  <si>
+    <t>ChargeCustInvUSD</t>
+  </si>
+  <si>
+    <t>COBRO A CLIENTES VÍA REP USD</t>
+  </si>
+  <si>
+    <t>COBRO A CLIENTES VÍA FACTURA USD</t>
+  </si>
+  <si>
+    <t>ChargeSuptRepMXN</t>
+  </si>
+  <si>
+    <t>PAGO A PROVEEDORES VÍA REP MXN</t>
+  </si>
+  <si>
+    <t>ChargeSuptInvMXN</t>
+  </si>
+  <si>
+    <t>PAGO A PROVEEDORES VÍA FACTURA MXN</t>
+  </si>
+  <si>
+    <t>ChargeSuptInvUSD</t>
+  </si>
+  <si>
+    <t>ChargeSuptRepUSD</t>
+  </si>
+  <si>
+    <t>PAGO A PROVEEDORES VÍA REP USD</t>
+  </si>
+  <si>
+    <t>PAGO A PROVEEDORES VÍA FACTURA USD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Existen segmentos </t>
+  </si>
+  <si>
+    <t>DontExistAcc</t>
+  </si>
+  <si>
+    <t>Ya existe</t>
+  </si>
+  <si>
+    <t>ExistPolicy</t>
+  </si>
+  <si>
+    <t>NotifNoProv</t>
+  </si>
+  <si>
+    <t>NotifNoProvSubjet</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>ValueNo</t>
+  </si>
+  <si>
+    <t>account</t>
+  </si>
+  <si>
+    <t>SheetsProv</t>
+  </si>
+  <si>
+    <t>NotErroProv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No cuadra totales en provision de Ventas </t>
+  </si>
+  <si>
+    <t>Error al Enviar {0}</t>
+  </si>
+  <si>
+    <t>NotErroProvSubject</t>
+  </si>
+  <si>
+    <t>Day of Weeks</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>ma</t>
+  </si>
+  <si>
+    <t>mi</t>
+  </si>
+  <si>
+    <t>j</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>MI</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>C:\Compac\Empresas\Reportes\Contpaq\Mis Reportes\Razfinanc_NG.xls</t>
+  </si>
+  <si>
+    <t>PathXlsRazFinac</t>
+  </si>
+  <si>
+    <t>CopyInfo.py</t>
+  </si>
+  <si>
+    <t>ScriptCopyInfo</t>
+  </si>
+  <si>
     <t>hector.agraz@emergys.com</t>
   </si>
   <si>
-    <t>FiscalReportXlsx</t>
-  </si>
-  <si>
-    <t>Concentrado Fiscal</t>
-  </si>
-  <si>
-    <t>ReportExt</t>
-  </si>
-  <si>
-    <t>.xlsx</t>
+    <t>{U}\OneDrive - TRIVALENTE\Trivalente\Inputs\</t>
+  </si>
+  <si>
+    <t>{U}\OneDrive - TRIVALENTE\Trivalente\Catalogo Empresas.xlsx</t>
+  </si>
+  <si>
+    <t>ScriptXlsm</t>
+  </si>
+  <si>
+    <t>GetFolios.xlsm</t>
+  </si>
+  <si>
+    <t>PathXMLs</t>
+  </si>
+  <si>
+    <t>C:\AdminXML\BovedaCFDi\</t>
+  </si>
+  <si>
+    <t>Hola buen día.
+Por este medio se informa que, durante el proceso de carga del archivo XML, se identificó un error que no está relacionado con duplicidad.
+Se adjunta el detalle correspondiente, para su revisión y seguimiento.
+&lt;img src="data:image/png;base64, {0}"&gt;
+Saludos cordiales.</t>
+  </si>
+  <si>
+    <t>PathXlsRazFinacBack</t>
+  </si>
+  <si>
+    <t>C:\Compac\Empresas\Reportes\Contpaq\Mis Reportes\_backup\Razfinanc_NG.xls</t>
+  </si>
+  <si>
+    <t>Matriz Gastos|Matriz Ventas</t>
+  </si>
+  <si>
+    <t>ErrorBotDownLoadXML</t>
+  </si>
+  <si>
+    <t>Excepción de Bot</t>
+  </si>
+  <si>
+    <t>Me dirijo a ustedes para informarles sobre una excepción que se encontró al momento de descargar los XMLs desde el aplicativo Cómputo Contable de la empresa.
+El RFC de la empresa afectada es {e}.
+Este es el reintento número {r} de la operación/validación.
+Favor de validar esta incidencia y notificarnos las acciones a seguir o si se requiere información adicional para su resolución.</t>
+  </si>
+  <si>
+    <t>ErrorSubject</t>
+  </si>
+  <si>
+    <t>C:\AdminXML\BovedaCFDi\{0}\Emitidas\{y}\{N}\</t>
+  </si>
+  <si>
+    <t>C:\AdminXML\BovedaCFDi\{0}\Recibidas\{y}\{N}\</t>
+  </si>
+  <si>
+    <t>Creacion de poliza tipo REP/FActura con contabilizador</t>
+  </si>
+  <si>
+    <t>ProjectCode3</t>
+  </si>
+  <si>
+    <t>Provisiones Gastos/Ventas</t>
+  </si>
+  <si>
+    <t>Descargar Facturas XML</t>
+  </si>
+  <si>
+    <t>Subir Facturas XML</t>
+  </si>
+  <si>
+    <t>Hola buen día.
+Por este medio se informa que, durante el proceso de validacion de los cuadres de los totales de provicion de gastos no cuadran:
+{0} es diferente de {1}
+El RFC de la empresa afectada es {e}.
+Favor de validar
+Saludos cordiales.</t>
+  </si>
+  <si>
+    <t>Favor de validar el siguiente mensaje:
+{0}
+El RFC de la empresa afectada es {e}.</t>
+  </si>
+  <si>
+    <t>ErrorBody</t>
+  </si>
+  <si>
+    <t>Se presentó la siguiente excepción {0},
+Se origino al procesar la empresa {e}, Con RFC: {r}.
+Por favor, validar el motivo de la excepción y confirmar una vez que se haya revisado.
+Saludos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -379,6 +816,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF4E6B8C"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -407,7 +851,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -417,7 +861,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -702,7 +1150,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D39"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:XFD118"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -730,312 +1179,9123 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>69</v>
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="B5" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>69</v>
+        <v>206</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>6</v>
+        <v>37</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+      <c r="B14" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+      <c r="B15" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>20</v>
+        <v>199</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+      <c r="B18" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>23</v>
+        <v>160</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>66</v>
+        <v>74</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B25" s="1">
-        <v>3</v>
+        <v>73</v>
+      </c>
+      <c r="B23" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>71</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>30</v>
+        <v>116</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
+        <v>14</v>
+      </c>
+      <c r="B35" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>47</v>
+        <v>58</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>49</v>
+        <v>57</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B39" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B42" s="10"/>
+      <c r="C42" s="10"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>51</v>
       </c>
     </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B64" s="10"/>
+      <c r="C64" s="10"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B73" s="10"/>
+      <c r="C73" s="10"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B80" s="10"/>
+      <c r="C80" s="10"/>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B81" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B82" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B83" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B84" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B90" s="1">
+        <v>11801000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B91" s="1">
+        <v>11901000</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16384" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16384" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16384" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16384" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16384" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16384" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B102" s="6">
+        <v>60261000</v>
+      </c>
+      <c r="D102" s="6"/>
+      <c r="F102" s="6"/>
+      <c r="H102" s="6"/>
+      <c r="J102" s="6"/>
+      <c r="L102" s="6"/>
+      <c r="N102" s="6"/>
+      <c r="P102" s="6"/>
+      <c r="R102" s="6"/>
+      <c r="T102" s="6"/>
+      <c r="V102" s="6"/>
+      <c r="X102" s="6"/>
+      <c r="Z102" s="6"/>
+      <c r="AB102" s="6"/>
+      <c r="AD102" s="6"/>
+      <c r="AF102" s="6"/>
+      <c r="AH102" s="6"/>
+      <c r="AJ102" s="6"/>
+      <c r="AL102" s="6"/>
+      <c r="AN102" s="6"/>
+      <c r="AP102" s="6"/>
+      <c r="AR102" s="6"/>
+      <c r="AT102" s="6"/>
+      <c r="AV102" s="6"/>
+      <c r="AX102" s="6"/>
+      <c r="AZ102" s="6"/>
+      <c r="BB102" s="6"/>
+      <c r="BD102" s="6"/>
+      <c r="BF102" s="6"/>
+      <c r="BH102" s="6"/>
+      <c r="BJ102" s="6"/>
+      <c r="BL102" s="6"/>
+      <c r="BN102" s="6"/>
+      <c r="BP102" s="6"/>
+      <c r="BR102" s="6"/>
+      <c r="BT102" s="6"/>
+      <c r="BV102" s="6"/>
+      <c r="BX102" s="6"/>
+      <c r="BZ102" s="6"/>
+      <c r="CB102" s="6"/>
+      <c r="CD102" s="6"/>
+      <c r="CF102" s="6"/>
+      <c r="CH102" s="6"/>
+      <c r="CJ102" s="6"/>
+      <c r="CL102" s="6"/>
+      <c r="CN102" s="6"/>
+      <c r="CP102" s="6"/>
+      <c r="CR102" s="6"/>
+      <c r="CT102" s="6"/>
+      <c r="CV102" s="6"/>
+      <c r="CX102" s="6"/>
+      <c r="CZ102" s="6"/>
+      <c r="DB102" s="6"/>
+      <c r="DD102" s="6"/>
+      <c r="DF102" s="6"/>
+      <c r="DH102" s="6"/>
+      <c r="DJ102" s="6"/>
+      <c r="DL102" s="6"/>
+      <c r="DN102" s="6"/>
+      <c r="DP102" s="6"/>
+      <c r="DR102" s="6"/>
+      <c r="DT102" s="6"/>
+      <c r="DV102" s="6"/>
+      <c r="DX102" s="6"/>
+      <c r="DZ102" s="6"/>
+      <c r="EB102" s="6"/>
+      <c r="ED102" s="6"/>
+      <c r="EF102" s="6"/>
+      <c r="EH102" s="6"/>
+      <c r="EJ102" s="6"/>
+      <c r="EL102" s="6"/>
+      <c r="EN102" s="6"/>
+      <c r="EP102" s="6"/>
+      <c r="ER102" s="6"/>
+      <c r="ET102" s="6"/>
+      <c r="EV102" s="6"/>
+      <c r="EX102" s="6"/>
+      <c r="EZ102" s="6"/>
+      <c r="FB102" s="6"/>
+      <c r="FD102" s="6"/>
+      <c r="FF102" s="6"/>
+      <c r="FH102" s="6"/>
+      <c r="FJ102" s="6"/>
+      <c r="FL102" s="6"/>
+      <c r="FN102" s="6"/>
+      <c r="FP102" s="6"/>
+      <c r="FR102" s="6"/>
+      <c r="FT102" s="6"/>
+      <c r="FV102" s="6"/>
+      <c r="FX102" s="6"/>
+      <c r="FZ102" s="6"/>
+      <c r="GB102" s="6"/>
+      <c r="GD102" s="6"/>
+      <c r="GF102" s="6"/>
+      <c r="GH102" s="6"/>
+      <c r="GJ102" s="6"/>
+      <c r="GL102" s="6"/>
+      <c r="GN102" s="6"/>
+      <c r="GP102" s="6"/>
+      <c r="GR102" s="6"/>
+      <c r="GT102" s="6"/>
+      <c r="GV102" s="6"/>
+      <c r="GX102" s="6"/>
+      <c r="GZ102" s="6"/>
+      <c r="HB102" s="6"/>
+      <c r="HD102" s="6"/>
+      <c r="HF102" s="6"/>
+      <c r="HH102" s="6"/>
+      <c r="HJ102" s="6"/>
+      <c r="HL102" s="6"/>
+      <c r="HN102" s="6"/>
+      <c r="HP102" s="6"/>
+      <c r="HR102" s="6"/>
+      <c r="HT102" s="6"/>
+      <c r="HV102" s="6"/>
+      <c r="HX102" s="6"/>
+      <c r="HZ102" s="6"/>
+      <c r="IB102" s="6"/>
+      <c r="ID102" s="6"/>
+      <c r="IF102" s="6"/>
+      <c r="IH102" s="6"/>
+      <c r="IJ102" s="6"/>
+      <c r="IL102" s="6"/>
+      <c r="IN102" s="6"/>
+      <c r="IP102" s="6"/>
+      <c r="IR102" s="6"/>
+      <c r="IT102" s="6"/>
+      <c r="IV102" s="6"/>
+      <c r="IX102" s="6"/>
+      <c r="IZ102" s="6"/>
+      <c r="JB102" s="6"/>
+      <c r="JD102" s="6"/>
+      <c r="JF102" s="6"/>
+      <c r="JH102" s="6"/>
+      <c r="JJ102" s="6"/>
+      <c r="JL102" s="6"/>
+      <c r="JN102" s="6"/>
+      <c r="JP102" s="6"/>
+      <c r="JR102" s="6"/>
+      <c r="JT102" s="6"/>
+      <c r="JV102" s="6"/>
+      <c r="JX102" s="6"/>
+      <c r="JZ102" s="6"/>
+      <c r="KB102" s="6"/>
+      <c r="KD102" s="6"/>
+      <c r="KF102" s="6"/>
+      <c r="KH102" s="6"/>
+      <c r="KJ102" s="6"/>
+      <c r="KL102" s="6"/>
+      <c r="KN102" s="6"/>
+      <c r="KP102" s="6"/>
+      <c r="KR102" s="6"/>
+      <c r="KT102" s="6"/>
+      <c r="KV102" s="6"/>
+      <c r="KX102" s="6"/>
+      <c r="KZ102" s="6"/>
+      <c r="LB102" s="6"/>
+      <c r="LD102" s="6"/>
+      <c r="LF102" s="6"/>
+      <c r="LH102" s="6"/>
+      <c r="LJ102" s="6"/>
+      <c r="LL102" s="6"/>
+      <c r="LN102" s="6"/>
+      <c r="LP102" s="6"/>
+      <c r="LR102" s="6"/>
+      <c r="LT102" s="6"/>
+      <c r="LV102" s="6"/>
+      <c r="LX102" s="6"/>
+      <c r="LZ102" s="6"/>
+      <c r="MB102" s="6"/>
+      <c r="MD102" s="6"/>
+      <c r="MF102" s="6"/>
+      <c r="MH102" s="6"/>
+      <c r="MJ102" s="6"/>
+      <c r="ML102" s="6"/>
+      <c r="MN102" s="6"/>
+      <c r="MP102" s="6"/>
+      <c r="MR102" s="6"/>
+      <c r="MT102" s="6"/>
+      <c r="MV102" s="6"/>
+      <c r="MX102" s="6"/>
+      <c r="MZ102" s="6"/>
+      <c r="NB102" s="6"/>
+      <c r="ND102" s="6"/>
+      <c r="NF102" s="6"/>
+      <c r="NH102" s="6"/>
+      <c r="NJ102" s="6"/>
+      <c r="NL102" s="6"/>
+      <c r="NN102" s="6"/>
+      <c r="NP102" s="6"/>
+      <c r="NR102" s="6"/>
+      <c r="NT102" s="6"/>
+      <c r="NV102" s="6"/>
+      <c r="NX102" s="6"/>
+      <c r="NZ102" s="6"/>
+      <c r="OB102" s="6"/>
+      <c r="OD102" s="6"/>
+      <c r="OF102" s="6"/>
+      <c r="OH102" s="6"/>
+      <c r="OJ102" s="6"/>
+      <c r="OL102" s="6"/>
+      <c r="ON102" s="6"/>
+      <c r="OP102" s="6"/>
+      <c r="OR102" s="6"/>
+      <c r="OT102" s="6"/>
+      <c r="OV102" s="6"/>
+      <c r="OX102" s="6"/>
+      <c r="OZ102" s="6"/>
+      <c r="PB102" s="6"/>
+      <c r="PD102" s="6"/>
+      <c r="PF102" s="6"/>
+      <c r="PH102" s="6"/>
+      <c r="PJ102" s="6"/>
+      <c r="PL102" s="6"/>
+      <c r="PN102" s="6"/>
+      <c r="PP102" s="6"/>
+      <c r="PR102" s="6"/>
+      <c r="PT102" s="6"/>
+      <c r="PV102" s="6"/>
+      <c r="PX102" s="6"/>
+      <c r="PZ102" s="6"/>
+      <c r="QB102" s="6"/>
+      <c r="QD102" s="6"/>
+      <c r="QF102" s="6"/>
+      <c r="QH102" s="6"/>
+      <c r="QJ102" s="6"/>
+      <c r="QL102" s="6"/>
+      <c r="QN102" s="6"/>
+      <c r="QP102" s="6"/>
+      <c r="QR102" s="6"/>
+      <c r="QT102" s="6"/>
+      <c r="QV102" s="6"/>
+      <c r="QX102" s="6"/>
+      <c r="QZ102" s="6"/>
+      <c r="RB102" s="6"/>
+      <c r="RD102" s="6"/>
+      <c r="RF102" s="6"/>
+      <c r="RH102" s="6"/>
+      <c r="RJ102" s="6"/>
+      <c r="RL102" s="6"/>
+      <c r="RN102" s="6"/>
+      <c r="RP102" s="6"/>
+      <c r="RR102" s="6"/>
+      <c r="RT102" s="6"/>
+      <c r="RV102" s="6"/>
+      <c r="RX102" s="6"/>
+      <c r="RZ102" s="6"/>
+      <c r="SB102" s="6"/>
+      <c r="SD102" s="6"/>
+      <c r="SF102" s="6"/>
+      <c r="SH102" s="6"/>
+      <c r="SJ102" s="6"/>
+      <c r="SL102" s="6"/>
+      <c r="SN102" s="6"/>
+      <c r="SP102" s="6"/>
+      <c r="SR102" s="6"/>
+      <c r="ST102" s="6"/>
+      <c r="SV102" s="6"/>
+      <c r="SX102" s="6"/>
+      <c r="SZ102" s="6"/>
+      <c r="TB102" s="6"/>
+      <c r="TD102" s="6"/>
+      <c r="TF102" s="6"/>
+      <c r="TH102" s="6"/>
+      <c r="TJ102" s="6"/>
+      <c r="TL102" s="6"/>
+      <c r="TN102" s="6"/>
+      <c r="TP102" s="6"/>
+      <c r="TR102" s="6"/>
+      <c r="TT102" s="6"/>
+      <c r="TV102" s="6"/>
+      <c r="TX102" s="6"/>
+      <c r="TZ102" s="6"/>
+      <c r="UB102" s="6"/>
+      <c r="UD102" s="6"/>
+      <c r="UF102" s="6"/>
+      <c r="UH102" s="6"/>
+      <c r="UJ102" s="6"/>
+      <c r="UL102" s="6"/>
+      <c r="UN102" s="6"/>
+      <c r="UP102" s="6"/>
+      <c r="UR102" s="6"/>
+      <c r="UT102" s="6"/>
+      <c r="UV102" s="6"/>
+      <c r="UX102" s="6"/>
+      <c r="UZ102" s="6"/>
+      <c r="VB102" s="6"/>
+      <c r="VD102" s="6"/>
+      <c r="VF102" s="6"/>
+      <c r="VH102" s="6"/>
+      <c r="VJ102" s="6"/>
+      <c r="VL102" s="6"/>
+      <c r="VN102" s="6"/>
+      <c r="VP102" s="6"/>
+      <c r="VR102" s="6"/>
+      <c r="VT102" s="6"/>
+      <c r="VV102" s="6"/>
+      <c r="VX102" s="6"/>
+      <c r="VZ102" s="6"/>
+      <c r="WB102" s="6"/>
+      <c r="WD102" s="6"/>
+      <c r="WF102" s="6"/>
+      <c r="WH102" s="6"/>
+      <c r="WJ102" s="6"/>
+      <c r="WL102" s="6"/>
+      <c r="WN102" s="6"/>
+      <c r="WP102" s="6"/>
+      <c r="WR102" s="6"/>
+      <c r="WT102" s="6"/>
+      <c r="WV102" s="6"/>
+      <c r="WX102" s="6"/>
+      <c r="WZ102" s="6"/>
+      <c r="XB102" s="6"/>
+      <c r="XD102" s="6"/>
+      <c r="XF102" s="6"/>
+      <c r="XH102" s="6"/>
+      <c r="XJ102" s="6"/>
+      <c r="XL102" s="6"/>
+      <c r="XN102" s="6"/>
+      <c r="XP102" s="6"/>
+      <c r="XR102" s="6"/>
+      <c r="XT102" s="6"/>
+      <c r="XV102" s="6"/>
+      <c r="XX102" s="6"/>
+      <c r="XZ102" s="6"/>
+      <c r="YB102" s="6"/>
+      <c r="YD102" s="6"/>
+      <c r="YF102" s="6"/>
+      <c r="YH102" s="6"/>
+      <c r="YJ102" s="6"/>
+      <c r="YL102" s="6"/>
+      <c r="YN102" s="6"/>
+      <c r="YP102" s="6"/>
+      <c r="YR102" s="6"/>
+      <c r="YT102" s="6"/>
+      <c r="YV102" s="6"/>
+      <c r="YX102" s="6"/>
+      <c r="YZ102" s="6"/>
+      <c r="ZB102" s="6"/>
+      <c r="ZD102" s="6"/>
+      <c r="ZF102" s="6"/>
+      <c r="ZH102" s="6"/>
+      <c r="ZJ102" s="6"/>
+      <c r="ZL102" s="6"/>
+      <c r="ZN102" s="6"/>
+      <c r="ZP102" s="6"/>
+      <c r="ZR102" s="6"/>
+      <c r="ZT102" s="6"/>
+      <c r="ZV102" s="6"/>
+      <c r="ZX102" s="6"/>
+      <c r="ZZ102" s="6"/>
+      <c r="AAB102" s="6"/>
+      <c r="AAD102" s="6"/>
+      <c r="AAF102" s="6"/>
+      <c r="AAH102" s="6"/>
+      <c r="AAJ102" s="6"/>
+      <c r="AAL102" s="6"/>
+      <c r="AAN102" s="6"/>
+      <c r="AAP102" s="6"/>
+      <c r="AAR102" s="6"/>
+      <c r="AAT102" s="6"/>
+      <c r="AAV102" s="6"/>
+      <c r="AAX102" s="6"/>
+      <c r="AAZ102" s="6"/>
+      <c r="ABB102" s="6"/>
+      <c r="ABD102" s="6"/>
+      <c r="ABF102" s="6"/>
+      <c r="ABH102" s="6"/>
+      <c r="ABJ102" s="6"/>
+      <c r="ABL102" s="6"/>
+      <c r="ABN102" s="6"/>
+      <c r="ABP102" s="6"/>
+      <c r="ABR102" s="6"/>
+      <c r="ABT102" s="6"/>
+      <c r="ABV102" s="6"/>
+      <c r="ABX102" s="6"/>
+      <c r="ABZ102" s="6"/>
+      <c r="ACB102" s="6"/>
+      <c r="ACD102" s="6"/>
+      <c r="ACF102" s="6"/>
+      <c r="ACH102" s="6"/>
+      <c r="ACJ102" s="6"/>
+      <c r="ACL102" s="6"/>
+      <c r="ACN102" s="6"/>
+      <c r="ACP102" s="6"/>
+      <c r="ACR102" s="6"/>
+      <c r="ACT102" s="6"/>
+      <c r="ACV102" s="6"/>
+      <c r="ACX102" s="6"/>
+      <c r="ACZ102" s="6"/>
+      <c r="ADB102" s="6"/>
+      <c r="ADD102" s="6"/>
+      <c r="ADF102" s="6"/>
+      <c r="ADH102" s="6"/>
+      <c r="ADJ102" s="6"/>
+      <c r="ADL102" s="6"/>
+      <c r="ADN102" s="6"/>
+      <c r="ADP102" s="6"/>
+      <c r="ADR102" s="6"/>
+      <c r="ADT102" s="6"/>
+      <c r="ADV102" s="6"/>
+      <c r="ADX102" s="6"/>
+      <c r="ADZ102" s="6"/>
+      <c r="AEB102" s="6"/>
+      <c r="AED102" s="6"/>
+      <c r="AEF102" s="6"/>
+      <c r="AEH102" s="6"/>
+      <c r="AEJ102" s="6"/>
+      <c r="AEL102" s="6"/>
+      <c r="AEN102" s="6"/>
+      <c r="AEP102" s="6"/>
+      <c r="AER102" s="6"/>
+      <c r="AET102" s="6"/>
+      <c r="AEV102" s="6"/>
+      <c r="AEX102" s="6"/>
+      <c r="AEZ102" s="6"/>
+      <c r="AFB102" s="6"/>
+      <c r="AFD102" s="6"/>
+      <c r="AFF102" s="6"/>
+      <c r="AFH102" s="6"/>
+      <c r="AFJ102" s="6"/>
+      <c r="AFL102" s="6"/>
+      <c r="AFN102" s="6"/>
+      <c r="AFP102" s="6"/>
+      <c r="AFR102" s="6"/>
+      <c r="AFT102" s="6"/>
+      <c r="AFV102" s="6"/>
+      <c r="AFX102" s="6"/>
+      <c r="AFZ102" s="6"/>
+      <c r="AGB102" s="6"/>
+      <c r="AGD102" s="6"/>
+      <c r="AGF102" s="6"/>
+      <c r="AGH102" s="6"/>
+      <c r="AGJ102" s="6"/>
+      <c r="AGL102" s="6"/>
+      <c r="AGN102" s="6"/>
+      <c r="AGP102" s="6"/>
+      <c r="AGR102" s="6"/>
+      <c r="AGT102" s="6"/>
+      <c r="AGV102" s="6"/>
+      <c r="AGX102" s="6"/>
+      <c r="AGZ102" s="6"/>
+      <c r="AHB102" s="6"/>
+      <c r="AHD102" s="6"/>
+      <c r="AHF102" s="6"/>
+      <c r="AHH102" s="6"/>
+      <c r="AHJ102" s="6"/>
+      <c r="AHL102" s="6"/>
+      <c r="AHN102" s="6"/>
+      <c r="AHP102" s="6"/>
+      <c r="AHR102" s="6"/>
+      <c r="AHT102" s="6"/>
+      <c r="AHV102" s="6"/>
+      <c r="AHX102" s="6"/>
+      <c r="AHZ102" s="6"/>
+      <c r="AIB102" s="6"/>
+      <c r="AID102" s="6"/>
+      <c r="AIF102" s="6"/>
+      <c r="AIH102" s="6"/>
+      <c r="AIJ102" s="6"/>
+      <c r="AIL102" s="6"/>
+      <c r="AIN102" s="6"/>
+      <c r="AIP102" s="6"/>
+      <c r="AIR102" s="6"/>
+      <c r="AIT102" s="6"/>
+      <c r="AIV102" s="6"/>
+      <c r="AIX102" s="6"/>
+      <c r="AIZ102" s="6"/>
+      <c r="AJB102" s="6"/>
+      <c r="AJD102" s="6"/>
+      <c r="AJF102" s="6"/>
+      <c r="AJH102" s="6"/>
+      <c r="AJJ102" s="6"/>
+      <c r="AJL102" s="6"/>
+      <c r="AJN102" s="6"/>
+      <c r="AJP102" s="6"/>
+      <c r="AJR102" s="6"/>
+      <c r="AJT102" s="6"/>
+      <c r="AJV102" s="6"/>
+      <c r="AJX102" s="6"/>
+      <c r="AJZ102" s="6"/>
+      <c r="AKB102" s="6"/>
+      <c r="AKD102" s="6"/>
+      <c r="AKF102" s="6"/>
+      <c r="AKH102" s="6"/>
+      <c r="AKJ102" s="6"/>
+      <c r="AKL102" s="6"/>
+      <c r="AKN102" s="6"/>
+      <c r="AKP102" s="6"/>
+      <c r="AKR102" s="6"/>
+      <c r="AKT102" s="6"/>
+      <c r="AKV102" s="6"/>
+      <c r="AKX102" s="6"/>
+      <c r="AKZ102" s="6"/>
+      <c r="ALB102" s="6"/>
+      <c r="ALD102" s="6"/>
+      <c r="ALF102" s="6"/>
+      <c r="ALH102" s="6"/>
+      <c r="ALJ102" s="6"/>
+      <c r="ALL102" s="6"/>
+      <c r="ALN102" s="6"/>
+      <c r="ALP102" s="6"/>
+      <c r="ALR102" s="6"/>
+      <c r="ALT102" s="6"/>
+      <c r="ALV102" s="6"/>
+      <c r="ALX102" s="6"/>
+      <c r="ALZ102" s="6"/>
+      <c r="AMB102" s="6"/>
+      <c r="AMD102" s="6"/>
+      <c r="AMF102" s="6"/>
+      <c r="AMH102" s="6"/>
+      <c r="AMJ102" s="6"/>
+      <c r="AML102" s="6"/>
+      <c r="AMN102" s="6"/>
+      <c r="AMP102" s="6"/>
+      <c r="AMR102" s="6"/>
+      <c r="AMT102" s="6"/>
+      <c r="AMV102" s="6"/>
+      <c r="AMX102" s="6"/>
+      <c r="AMZ102" s="6"/>
+      <c r="ANB102" s="6"/>
+      <c r="AND102" s="6"/>
+      <c r="ANF102" s="6"/>
+      <c r="ANH102" s="6"/>
+      <c r="ANJ102" s="6"/>
+      <c r="ANL102" s="6"/>
+      <c r="ANN102" s="6"/>
+      <c r="ANP102" s="6"/>
+      <c r="ANR102" s="6"/>
+      <c r="ANT102" s="6"/>
+      <c r="ANV102" s="6"/>
+      <c r="ANX102" s="6"/>
+      <c r="ANZ102" s="6"/>
+      <c r="AOB102" s="6"/>
+      <c r="AOD102" s="6"/>
+      <c r="AOF102" s="6"/>
+      <c r="AOH102" s="6"/>
+      <c r="AOJ102" s="6"/>
+      <c r="AOL102" s="6"/>
+      <c r="AON102" s="6"/>
+      <c r="AOP102" s="6"/>
+      <c r="AOR102" s="6"/>
+      <c r="AOT102" s="6"/>
+      <c r="AOV102" s="6"/>
+      <c r="AOX102" s="6"/>
+      <c r="AOZ102" s="6"/>
+      <c r="APB102" s="6"/>
+      <c r="APD102" s="6"/>
+      <c r="APF102" s="6"/>
+      <c r="APH102" s="6"/>
+      <c r="APJ102" s="6"/>
+      <c r="APL102" s="6"/>
+      <c r="APN102" s="6"/>
+      <c r="APP102" s="6"/>
+      <c r="APR102" s="6"/>
+      <c r="APT102" s="6"/>
+      <c r="APV102" s="6"/>
+      <c r="APX102" s="6"/>
+      <c r="APZ102" s="6"/>
+      <c r="AQB102" s="6"/>
+      <c r="AQD102" s="6"/>
+      <c r="AQF102" s="6"/>
+      <c r="AQH102" s="6"/>
+      <c r="AQJ102" s="6"/>
+      <c r="AQL102" s="6"/>
+      <c r="AQN102" s="6"/>
+      <c r="AQP102" s="6"/>
+      <c r="AQR102" s="6"/>
+      <c r="AQT102" s="6"/>
+      <c r="AQV102" s="6"/>
+      <c r="AQX102" s="6"/>
+      <c r="AQZ102" s="6"/>
+      <c r="ARB102" s="6"/>
+      <c r="ARD102" s="6"/>
+      <c r="ARF102" s="6"/>
+      <c r="ARH102" s="6"/>
+      <c r="ARJ102" s="6"/>
+      <c r="ARL102" s="6"/>
+      <c r="ARN102" s="6"/>
+      <c r="ARP102" s="6"/>
+      <c r="ARR102" s="6"/>
+      <c r="ART102" s="6"/>
+      <c r="ARV102" s="6"/>
+      <c r="ARX102" s="6"/>
+      <c r="ARZ102" s="6"/>
+      <c r="ASB102" s="6"/>
+      <c r="ASD102" s="6"/>
+      <c r="ASF102" s="6"/>
+      <c r="ASH102" s="6"/>
+      <c r="ASJ102" s="6"/>
+      <c r="ASL102" s="6"/>
+      <c r="ASN102" s="6"/>
+      <c r="ASP102" s="6"/>
+      <c r="ASR102" s="6"/>
+      <c r="AST102" s="6"/>
+      <c r="ASV102" s="6"/>
+      <c r="ASX102" s="6"/>
+      <c r="ASZ102" s="6"/>
+      <c r="ATB102" s="6"/>
+      <c r="ATD102" s="6"/>
+      <c r="ATF102" s="6"/>
+      <c r="ATH102" s="6"/>
+      <c r="ATJ102" s="6"/>
+      <c r="ATL102" s="6"/>
+      <c r="ATN102" s="6"/>
+      <c r="ATP102" s="6"/>
+      <c r="ATR102" s="6"/>
+      <c r="ATT102" s="6"/>
+      <c r="ATV102" s="6"/>
+      <c r="ATX102" s="6"/>
+      <c r="ATZ102" s="6"/>
+      <c r="AUB102" s="6"/>
+      <c r="AUD102" s="6"/>
+      <c r="AUF102" s="6"/>
+      <c r="AUH102" s="6"/>
+      <c r="AUJ102" s="6"/>
+      <c r="AUL102" s="6"/>
+      <c r="AUN102" s="6"/>
+      <c r="AUP102" s="6"/>
+      <c r="AUR102" s="6"/>
+      <c r="AUT102" s="6"/>
+      <c r="AUV102" s="6"/>
+      <c r="AUX102" s="6"/>
+      <c r="AUZ102" s="6"/>
+      <c r="AVB102" s="6"/>
+      <c r="AVD102" s="6"/>
+      <c r="AVF102" s="6"/>
+      <c r="AVH102" s="6"/>
+      <c r="AVJ102" s="6"/>
+      <c r="AVL102" s="6"/>
+      <c r="AVN102" s="6"/>
+      <c r="AVP102" s="6"/>
+      <c r="AVR102" s="6"/>
+      <c r="AVT102" s="6"/>
+      <c r="AVV102" s="6"/>
+      <c r="AVX102" s="6"/>
+      <c r="AVZ102" s="6"/>
+      <c r="AWB102" s="6"/>
+      <c r="AWD102" s="6"/>
+      <c r="AWF102" s="6"/>
+      <c r="AWH102" s="6"/>
+      <c r="AWJ102" s="6"/>
+      <c r="AWL102" s="6"/>
+      <c r="AWN102" s="6"/>
+      <c r="AWP102" s="6"/>
+      <c r="AWR102" s="6"/>
+      <c r="AWT102" s="6"/>
+      <c r="AWV102" s="6"/>
+      <c r="AWX102" s="6"/>
+      <c r="AWZ102" s="6"/>
+      <c r="AXB102" s="6"/>
+      <c r="AXD102" s="6"/>
+      <c r="AXF102" s="6"/>
+      <c r="AXH102" s="6"/>
+      <c r="AXJ102" s="6"/>
+      <c r="AXL102" s="6"/>
+      <c r="AXN102" s="6"/>
+      <c r="AXP102" s="6"/>
+      <c r="AXR102" s="6"/>
+      <c r="AXT102" s="6"/>
+      <c r="AXV102" s="6"/>
+      <c r="AXX102" s="6"/>
+      <c r="AXZ102" s="6"/>
+      <c r="AYB102" s="6"/>
+      <c r="AYD102" s="6"/>
+      <c r="AYF102" s="6"/>
+      <c r="AYH102" s="6"/>
+      <c r="AYJ102" s="6"/>
+      <c r="AYL102" s="6"/>
+      <c r="AYN102" s="6"/>
+      <c r="AYP102" s="6"/>
+      <c r="AYR102" s="6"/>
+      <c r="AYT102" s="6"/>
+      <c r="AYV102" s="6"/>
+      <c r="AYX102" s="6"/>
+      <c r="AYZ102" s="6"/>
+      <c r="AZB102" s="6"/>
+      <c r="AZD102" s="6"/>
+      <c r="AZF102" s="6"/>
+      <c r="AZH102" s="6"/>
+      <c r="AZJ102" s="6"/>
+      <c r="AZL102" s="6"/>
+      <c r="AZN102" s="6"/>
+      <c r="AZP102" s="6"/>
+      <c r="AZR102" s="6"/>
+      <c r="AZT102" s="6"/>
+      <c r="AZV102" s="6"/>
+      <c r="AZX102" s="6"/>
+      <c r="AZZ102" s="6"/>
+      <c r="BAB102" s="6"/>
+      <c r="BAD102" s="6"/>
+      <c r="BAF102" s="6"/>
+      <c r="BAH102" s="6"/>
+      <c r="BAJ102" s="6"/>
+      <c r="BAL102" s="6"/>
+      <c r="BAN102" s="6"/>
+      <c r="BAP102" s="6"/>
+      <c r="BAR102" s="6"/>
+      <c r="BAT102" s="6"/>
+      <c r="BAV102" s="6"/>
+      <c r="BAX102" s="6"/>
+      <c r="BAZ102" s="6"/>
+      <c r="BBB102" s="6"/>
+      <c r="BBD102" s="6"/>
+      <c r="BBF102" s="6"/>
+      <c r="BBH102" s="6"/>
+      <c r="BBJ102" s="6"/>
+      <c r="BBL102" s="6"/>
+      <c r="BBN102" s="6"/>
+      <c r="BBP102" s="6"/>
+      <c r="BBR102" s="6"/>
+      <c r="BBT102" s="6"/>
+      <c r="BBV102" s="6"/>
+      <c r="BBX102" s="6"/>
+      <c r="BBZ102" s="6"/>
+      <c r="BCB102" s="6"/>
+      <c r="BCD102" s="6"/>
+      <c r="BCF102" s="6"/>
+      <c r="BCH102" s="6"/>
+      <c r="BCJ102" s="6"/>
+      <c r="BCL102" s="6"/>
+      <c r="BCN102" s="6"/>
+      <c r="BCP102" s="6"/>
+      <c r="BCR102" s="6"/>
+      <c r="BCT102" s="6"/>
+      <c r="BCV102" s="6"/>
+      <c r="BCX102" s="6"/>
+      <c r="BCZ102" s="6"/>
+      <c r="BDB102" s="6"/>
+      <c r="BDD102" s="6"/>
+      <c r="BDF102" s="6"/>
+      <c r="BDH102" s="6"/>
+      <c r="BDJ102" s="6"/>
+      <c r="BDL102" s="6"/>
+      <c r="BDN102" s="6"/>
+      <c r="BDP102" s="6"/>
+      <c r="BDR102" s="6"/>
+      <c r="BDT102" s="6"/>
+      <c r="BDV102" s="6"/>
+      <c r="BDX102" s="6"/>
+      <c r="BDZ102" s="6"/>
+      <c r="BEB102" s="6"/>
+      <c r="BED102" s="6"/>
+      <c r="BEF102" s="6"/>
+      <c r="BEH102" s="6"/>
+      <c r="BEJ102" s="6"/>
+      <c r="BEL102" s="6"/>
+      <c r="BEN102" s="6"/>
+      <c r="BEP102" s="6"/>
+      <c r="BER102" s="6"/>
+      <c r="BET102" s="6"/>
+      <c r="BEV102" s="6"/>
+      <c r="BEX102" s="6"/>
+      <c r="BEZ102" s="6"/>
+      <c r="BFB102" s="6"/>
+      <c r="BFD102" s="6"/>
+      <c r="BFF102" s="6"/>
+      <c r="BFH102" s="6"/>
+      <c r="BFJ102" s="6"/>
+      <c r="BFL102" s="6"/>
+      <c r="BFN102" s="6"/>
+      <c r="BFP102" s="6"/>
+      <c r="BFR102" s="6"/>
+      <c r="BFT102" s="6"/>
+      <c r="BFV102" s="6"/>
+      <c r="BFX102" s="6"/>
+      <c r="BFZ102" s="6"/>
+      <c r="BGB102" s="6"/>
+      <c r="BGD102" s="6"/>
+      <c r="BGF102" s="6"/>
+      <c r="BGH102" s="6"/>
+      <c r="BGJ102" s="6"/>
+      <c r="BGL102" s="6"/>
+      <c r="BGN102" s="6"/>
+      <c r="BGP102" s="6"/>
+      <c r="BGR102" s="6"/>
+      <c r="BGT102" s="6"/>
+      <c r="BGV102" s="6"/>
+      <c r="BGX102" s="6"/>
+      <c r="BGZ102" s="6"/>
+      <c r="BHB102" s="6"/>
+      <c r="BHD102" s="6"/>
+      <c r="BHF102" s="6"/>
+      <c r="BHH102" s="6"/>
+      <c r="BHJ102" s="6"/>
+      <c r="BHL102" s="6"/>
+      <c r="BHN102" s="6"/>
+      <c r="BHP102" s="6"/>
+      <c r="BHR102" s="6"/>
+      <c r="BHT102" s="6"/>
+      <c r="BHV102" s="6"/>
+      <c r="BHX102" s="6"/>
+      <c r="BHZ102" s="6"/>
+      <c r="BIB102" s="6"/>
+      <c r="BID102" s="6"/>
+      <c r="BIF102" s="6"/>
+      <c r="BIH102" s="6"/>
+      <c r="BIJ102" s="6"/>
+      <c r="BIL102" s="6"/>
+      <c r="BIN102" s="6"/>
+      <c r="BIP102" s="6"/>
+      <c r="BIR102" s="6"/>
+      <c r="BIT102" s="6"/>
+      <c r="BIV102" s="6"/>
+      <c r="BIX102" s="6"/>
+      <c r="BIZ102" s="6"/>
+      <c r="BJB102" s="6"/>
+      <c r="BJD102" s="6"/>
+      <c r="BJF102" s="6"/>
+      <c r="BJH102" s="6"/>
+      <c r="BJJ102" s="6"/>
+      <c r="BJL102" s="6"/>
+      <c r="BJN102" s="6"/>
+      <c r="BJP102" s="6"/>
+      <c r="BJR102" s="6"/>
+      <c r="BJT102" s="6"/>
+      <c r="BJV102" s="6"/>
+      <c r="BJX102" s="6"/>
+      <c r="BJZ102" s="6"/>
+      <c r="BKB102" s="6"/>
+      <c r="BKD102" s="6"/>
+      <c r="BKF102" s="6"/>
+      <c r="BKH102" s="6"/>
+      <c r="BKJ102" s="6"/>
+      <c r="BKL102" s="6"/>
+      <c r="BKN102" s="6"/>
+      <c r="BKP102" s="6"/>
+      <c r="BKR102" s="6"/>
+      <c r="BKT102" s="6"/>
+      <c r="BKV102" s="6"/>
+      <c r="BKX102" s="6"/>
+      <c r="BKZ102" s="6"/>
+      <c r="BLB102" s="6"/>
+      <c r="BLD102" s="6"/>
+      <c r="BLF102" s="6"/>
+      <c r="BLH102" s="6"/>
+      <c r="BLJ102" s="6"/>
+      <c r="BLL102" s="6"/>
+      <c r="BLN102" s="6"/>
+      <c r="BLP102" s="6"/>
+      <c r="BLR102" s="6"/>
+      <c r="BLT102" s="6"/>
+      <c r="BLV102" s="6"/>
+      <c r="BLX102" s="6"/>
+      <c r="BLZ102" s="6"/>
+      <c r="BMB102" s="6"/>
+      <c r="BMD102" s="6"/>
+      <c r="BMF102" s="6"/>
+      <c r="BMH102" s="6"/>
+      <c r="BMJ102" s="6"/>
+      <c r="BML102" s="6"/>
+      <c r="BMN102" s="6"/>
+      <c r="BMP102" s="6"/>
+      <c r="BMR102" s="6"/>
+      <c r="BMT102" s="6"/>
+      <c r="BMV102" s="6"/>
+      <c r="BMX102" s="6"/>
+      <c r="BMZ102" s="6"/>
+      <c r="BNB102" s="6"/>
+      <c r="BND102" s="6"/>
+      <c r="BNF102" s="6"/>
+      <c r="BNH102" s="6"/>
+      <c r="BNJ102" s="6"/>
+      <c r="BNL102" s="6"/>
+      <c r="BNN102" s="6"/>
+      <c r="BNP102" s="6"/>
+      <c r="BNR102" s="6"/>
+      <c r="BNT102" s="6"/>
+      <c r="BNV102" s="6"/>
+      <c r="BNX102" s="6"/>
+      <c r="BNZ102" s="6"/>
+      <c r="BOB102" s="6"/>
+      <c r="BOD102" s="6"/>
+      <c r="BOF102" s="6"/>
+      <c r="BOH102" s="6"/>
+      <c r="BOJ102" s="6"/>
+      <c r="BOL102" s="6"/>
+      <c r="BON102" s="6"/>
+      <c r="BOP102" s="6"/>
+      <c r="BOR102" s="6"/>
+      <c r="BOT102" s="6"/>
+      <c r="BOV102" s="6"/>
+      <c r="BOX102" s="6"/>
+      <c r="BOZ102" s="6"/>
+      <c r="BPB102" s="6"/>
+      <c r="BPD102" s="6"/>
+      <c r="BPF102" s="6"/>
+      <c r="BPH102" s="6"/>
+      <c r="BPJ102" s="6"/>
+      <c r="BPL102" s="6"/>
+      <c r="BPN102" s="6"/>
+      <c r="BPP102" s="6"/>
+      <c r="BPR102" s="6"/>
+      <c r="BPT102" s="6"/>
+      <c r="BPV102" s="6"/>
+      <c r="BPX102" s="6"/>
+      <c r="BPZ102" s="6"/>
+      <c r="BQB102" s="6"/>
+      <c r="BQD102" s="6"/>
+      <c r="BQF102" s="6"/>
+      <c r="BQH102" s="6"/>
+      <c r="BQJ102" s="6"/>
+      <c r="BQL102" s="6"/>
+      <c r="BQN102" s="6"/>
+      <c r="BQP102" s="6"/>
+      <c r="BQR102" s="6"/>
+      <c r="BQT102" s="6"/>
+      <c r="BQV102" s="6"/>
+      <c r="BQX102" s="6"/>
+      <c r="BQZ102" s="6"/>
+      <c r="BRB102" s="6"/>
+      <c r="BRD102" s="6"/>
+      <c r="BRF102" s="6"/>
+      <c r="BRH102" s="6"/>
+      <c r="BRJ102" s="6"/>
+      <c r="BRL102" s="6"/>
+      <c r="BRN102" s="6"/>
+      <c r="BRP102" s="6"/>
+      <c r="BRR102" s="6"/>
+      <c r="BRT102" s="6"/>
+      <c r="BRV102" s="6"/>
+      <c r="BRX102" s="6"/>
+      <c r="BRZ102" s="6"/>
+      <c r="BSB102" s="6"/>
+      <c r="BSD102" s="6"/>
+      <c r="BSF102" s="6"/>
+      <c r="BSH102" s="6"/>
+      <c r="BSJ102" s="6"/>
+      <c r="BSL102" s="6"/>
+      <c r="BSN102" s="6"/>
+      <c r="BSP102" s="6"/>
+      <c r="BSR102" s="6"/>
+      <c r="BST102" s="6"/>
+      <c r="BSV102" s="6"/>
+      <c r="BSX102" s="6"/>
+      <c r="BSZ102" s="6"/>
+      <c r="BTB102" s="6"/>
+      <c r="BTD102" s="6"/>
+      <c r="BTF102" s="6"/>
+      <c r="BTH102" s="6"/>
+      <c r="BTJ102" s="6"/>
+      <c r="BTL102" s="6"/>
+      <c r="BTN102" s="6"/>
+      <c r="BTP102" s="6"/>
+      <c r="BTR102" s="6"/>
+      <c r="BTT102" s="6"/>
+      <c r="BTV102" s="6"/>
+      <c r="BTX102" s="6"/>
+      <c r="BTZ102" s="6"/>
+      <c r="BUB102" s="6"/>
+      <c r="BUD102" s="6"/>
+      <c r="BUF102" s="6"/>
+      <c r="BUH102" s="6"/>
+      <c r="BUJ102" s="6"/>
+      <c r="BUL102" s="6"/>
+      <c r="BUN102" s="6"/>
+      <c r="BUP102" s="6"/>
+      <c r="BUR102" s="6"/>
+      <c r="BUT102" s="6"/>
+      <c r="BUV102" s="6"/>
+      <c r="BUX102" s="6"/>
+      <c r="BUZ102" s="6"/>
+      <c r="BVB102" s="6"/>
+      <c r="BVD102" s="6"/>
+      <c r="BVF102" s="6"/>
+      <c r="BVH102" s="6"/>
+      <c r="BVJ102" s="6"/>
+      <c r="BVL102" s="6"/>
+      <c r="BVN102" s="6"/>
+      <c r="BVP102" s="6"/>
+      <c r="BVR102" s="6"/>
+      <c r="BVT102" s="6"/>
+      <c r="BVV102" s="6"/>
+      <c r="BVX102" s="6"/>
+      <c r="BVZ102" s="6"/>
+      <c r="BWB102" s="6"/>
+      <c r="BWD102" s="6"/>
+      <c r="BWF102" s="6"/>
+      <c r="BWH102" s="6"/>
+      <c r="BWJ102" s="6"/>
+      <c r="BWL102" s="6"/>
+      <c r="BWN102" s="6"/>
+      <c r="BWP102" s="6"/>
+      <c r="BWR102" s="6"/>
+      <c r="BWT102" s="6"/>
+      <c r="BWV102" s="6"/>
+      <c r="BWX102" s="6"/>
+      <c r="BWZ102" s="6"/>
+      <c r="BXB102" s="6"/>
+      <c r="BXD102" s="6"/>
+      <c r="BXF102" s="6"/>
+      <c r="BXH102" s="6"/>
+      <c r="BXJ102" s="6"/>
+      <c r="BXL102" s="6"/>
+      <c r="BXN102" s="6"/>
+      <c r="BXP102" s="6"/>
+      <c r="BXR102" s="6"/>
+      <c r="BXT102" s="6"/>
+      <c r="BXV102" s="6"/>
+      <c r="BXX102" s="6"/>
+      <c r="BXZ102" s="6"/>
+      <c r="BYB102" s="6"/>
+      <c r="BYD102" s="6"/>
+      <c r="BYF102" s="6"/>
+      <c r="BYH102" s="6"/>
+      <c r="BYJ102" s="6"/>
+      <c r="BYL102" s="6"/>
+      <c r="BYN102" s="6"/>
+      <c r="BYP102" s="6"/>
+      <c r="BYR102" s="6"/>
+      <c r="BYT102" s="6"/>
+      <c r="BYV102" s="6"/>
+      <c r="BYX102" s="6"/>
+      <c r="BYZ102" s="6"/>
+      <c r="BZB102" s="6"/>
+      <c r="BZD102" s="6"/>
+      <c r="BZF102" s="6"/>
+      <c r="BZH102" s="6"/>
+      <c r="BZJ102" s="6"/>
+      <c r="BZL102" s="6"/>
+      <c r="BZN102" s="6"/>
+      <c r="BZP102" s="6"/>
+      <c r="BZR102" s="6"/>
+      <c r="BZT102" s="6"/>
+      <c r="BZV102" s="6"/>
+      <c r="BZX102" s="6"/>
+      <c r="BZZ102" s="6"/>
+      <c r="CAB102" s="6"/>
+      <c r="CAD102" s="6"/>
+      <c r="CAF102" s="6"/>
+      <c r="CAH102" s="6"/>
+      <c r="CAJ102" s="6"/>
+      <c r="CAL102" s="6"/>
+      <c r="CAN102" s="6"/>
+      <c r="CAP102" s="6"/>
+      <c r="CAR102" s="6"/>
+      <c r="CAT102" s="6"/>
+      <c r="CAV102" s="6"/>
+      <c r="CAX102" s="6"/>
+      <c r="CAZ102" s="6"/>
+      <c r="CBB102" s="6"/>
+      <c r="CBD102" s="6"/>
+      <c r="CBF102" s="6"/>
+      <c r="CBH102" s="6"/>
+      <c r="CBJ102" s="6"/>
+      <c r="CBL102" s="6"/>
+      <c r="CBN102" s="6"/>
+      <c r="CBP102" s="6"/>
+      <c r="CBR102" s="6"/>
+      <c r="CBT102" s="6"/>
+      <c r="CBV102" s="6"/>
+      <c r="CBX102" s="6"/>
+      <c r="CBZ102" s="6"/>
+      <c r="CCB102" s="6"/>
+      <c r="CCD102" s="6"/>
+      <c r="CCF102" s="6"/>
+      <c r="CCH102" s="6"/>
+      <c r="CCJ102" s="6"/>
+      <c r="CCL102" s="6"/>
+      <c r="CCN102" s="6"/>
+      <c r="CCP102" s="6"/>
+      <c r="CCR102" s="6"/>
+      <c r="CCT102" s="6"/>
+      <c r="CCV102" s="6"/>
+      <c r="CCX102" s="6"/>
+      <c r="CCZ102" s="6"/>
+      <c r="CDB102" s="6"/>
+      <c r="CDD102" s="6"/>
+      <c r="CDF102" s="6"/>
+      <c r="CDH102" s="6"/>
+      <c r="CDJ102" s="6"/>
+      <c r="CDL102" s="6"/>
+      <c r="CDN102" s="6"/>
+      <c r="CDP102" s="6"/>
+      <c r="CDR102" s="6"/>
+      <c r="CDT102" s="6"/>
+      <c r="CDV102" s="6"/>
+      <c r="CDX102" s="6"/>
+      <c r="CDZ102" s="6"/>
+      <c r="CEB102" s="6"/>
+      <c r="CED102" s="6"/>
+      <c r="CEF102" s="6"/>
+      <c r="CEH102" s="6"/>
+      <c r="CEJ102" s="6"/>
+      <c r="CEL102" s="6"/>
+      <c r="CEN102" s="6"/>
+      <c r="CEP102" s="6"/>
+      <c r="CER102" s="6"/>
+      <c r="CET102" s="6"/>
+      <c r="CEV102" s="6"/>
+      <c r="CEX102" s="6"/>
+      <c r="CEZ102" s="6"/>
+      <c r="CFB102" s="6"/>
+      <c r="CFD102" s="6"/>
+      <c r="CFF102" s="6"/>
+      <c r="CFH102" s="6"/>
+      <c r="CFJ102" s="6"/>
+      <c r="CFL102" s="6"/>
+      <c r="CFN102" s="6"/>
+      <c r="CFP102" s="6"/>
+      <c r="CFR102" s="6"/>
+      <c r="CFT102" s="6"/>
+      <c r="CFV102" s="6"/>
+      <c r="CFX102" s="6"/>
+      <c r="CFZ102" s="6"/>
+      <c r="CGB102" s="6"/>
+      <c r="CGD102" s="6"/>
+      <c r="CGF102" s="6"/>
+      <c r="CGH102" s="6"/>
+      <c r="CGJ102" s="6"/>
+      <c r="CGL102" s="6"/>
+      <c r="CGN102" s="6"/>
+      <c r="CGP102" s="6"/>
+      <c r="CGR102" s="6"/>
+      <c r="CGT102" s="6"/>
+      <c r="CGV102" s="6"/>
+      <c r="CGX102" s="6"/>
+      <c r="CGZ102" s="6"/>
+      <c r="CHB102" s="6"/>
+      <c r="CHD102" s="6"/>
+      <c r="CHF102" s="6"/>
+      <c r="CHH102" s="6"/>
+      <c r="CHJ102" s="6"/>
+      <c r="CHL102" s="6"/>
+      <c r="CHN102" s="6"/>
+      <c r="CHP102" s="6"/>
+      <c r="CHR102" s="6"/>
+      <c r="CHT102" s="6"/>
+      <c r="CHV102" s="6"/>
+      <c r="CHX102" s="6"/>
+      <c r="CHZ102" s="6"/>
+      <c r="CIB102" s="6"/>
+      <c r="CID102" s="6"/>
+      <c r="CIF102" s="6"/>
+      <c r="CIH102" s="6"/>
+      <c r="CIJ102" s="6"/>
+      <c r="CIL102" s="6"/>
+      <c r="CIN102" s="6"/>
+      <c r="CIP102" s="6"/>
+      <c r="CIR102" s="6"/>
+      <c r="CIT102" s="6"/>
+      <c r="CIV102" s="6"/>
+      <c r="CIX102" s="6"/>
+      <c r="CIZ102" s="6"/>
+      <c r="CJB102" s="6"/>
+      <c r="CJD102" s="6"/>
+      <c r="CJF102" s="6"/>
+      <c r="CJH102" s="6"/>
+      <c r="CJJ102" s="6"/>
+      <c r="CJL102" s="6"/>
+      <c r="CJN102" s="6"/>
+      <c r="CJP102" s="6"/>
+      <c r="CJR102" s="6"/>
+      <c r="CJT102" s="6"/>
+      <c r="CJV102" s="6"/>
+      <c r="CJX102" s="6"/>
+      <c r="CJZ102" s="6"/>
+      <c r="CKB102" s="6"/>
+      <c r="CKD102" s="6"/>
+      <c r="CKF102" s="6"/>
+      <c r="CKH102" s="6"/>
+      <c r="CKJ102" s="6"/>
+      <c r="CKL102" s="6"/>
+      <c r="CKN102" s="6"/>
+      <c r="CKP102" s="6"/>
+      <c r="CKR102" s="6"/>
+      <c r="CKT102" s="6"/>
+      <c r="CKV102" s="6"/>
+      <c r="CKX102" s="6"/>
+      <c r="CKZ102" s="6"/>
+      <c r="CLB102" s="6"/>
+      <c r="CLD102" s="6"/>
+      <c r="CLF102" s="6"/>
+      <c r="CLH102" s="6"/>
+      <c r="CLJ102" s="6"/>
+      <c r="CLL102" s="6"/>
+      <c r="CLN102" s="6"/>
+      <c r="CLP102" s="6"/>
+      <c r="CLR102" s="6"/>
+      <c r="CLT102" s="6"/>
+      <c r="CLV102" s="6"/>
+      <c r="CLX102" s="6"/>
+      <c r="CLZ102" s="6"/>
+      <c r="CMB102" s="6"/>
+      <c r="CMD102" s="6"/>
+      <c r="CMF102" s="6"/>
+      <c r="CMH102" s="6"/>
+      <c r="CMJ102" s="6"/>
+      <c r="CML102" s="6"/>
+      <c r="CMN102" s="6"/>
+      <c r="CMP102" s="6"/>
+      <c r="CMR102" s="6"/>
+      <c r="CMT102" s="6"/>
+      <c r="CMV102" s="6"/>
+      <c r="CMX102" s="6"/>
+      <c r="CMZ102" s="6"/>
+      <c r="CNB102" s="6"/>
+      <c r="CND102" s="6"/>
+      <c r="CNF102" s="6"/>
+      <c r="CNH102" s="6"/>
+      <c r="CNJ102" s="6"/>
+      <c r="CNL102" s="6"/>
+      <c r="CNN102" s="6"/>
+      <c r="CNP102" s="6"/>
+      <c r="CNR102" s="6"/>
+      <c r="CNT102" s="6"/>
+      <c r="CNV102" s="6"/>
+      <c r="CNX102" s="6"/>
+      <c r="CNZ102" s="6"/>
+      <c r="COB102" s="6"/>
+      <c r="COD102" s="6"/>
+      <c r="COF102" s="6"/>
+      <c r="COH102" s="6"/>
+      <c r="COJ102" s="6"/>
+      <c r="COL102" s="6"/>
+      <c r="CON102" s="6"/>
+      <c r="COP102" s="6"/>
+      <c r="COR102" s="6"/>
+      <c r="COT102" s="6"/>
+      <c r="COV102" s="6"/>
+      <c r="COX102" s="6"/>
+      <c r="COZ102" s="6"/>
+      <c r="CPB102" s="6"/>
+      <c r="CPD102" s="6"/>
+      <c r="CPF102" s="6"/>
+      <c r="CPH102" s="6"/>
+      <c r="CPJ102" s="6"/>
+      <c r="CPL102" s="6"/>
+      <c r="CPN102" s="6"/>
+      <c r="CPP102" s="6"/>
+      <c r="CPR102" s="6"/>
+      <c r="CPT102" s="6"/>
+      <c r="CPV102" s="6"/>
+      <c r="CPX102" s="6"/>
+      <c r="CPZ102" s="6"/>
+      <c r="CQB102" s="6"/>
+      <c r="CQD102" s="6"/>
+      <c r="CQF102" s="6"/>
+      <c r="CQH102" s="6"/>
+      <c r="CQJ102" s="6"/>
+      <c r="CQL102" s="6"/>
+      <c r="CQN102" s="6"/>
+      <c r="CQP102" s="6"/>
+      <c r="CQR102" s="6"/>
+      <c r="CQT102" s="6"/>
+      <c r="CQV102" s="6"/>
+      <c r="CQX102" s="6"/>
+      <c r="CQZ102" s="6"/>
+      <c r="CRB102" s="6"/>
+      <c r="CRD102" s="6"/>
+      <c r="CRF102" s="6"/>
+      <c r="CRH102" s="6"/>
+      <c r="CRJ102" s="6"/>
+      <c r="CRL102" s="6"/>
+      <c r="CRN102" s="6"/>
+      <c r="CRP102" s="6"/>
+      <c r="CRR102" s="6"/>
+      <c r="CRT102" s="6"/>
+      <c r="CRV102" s="6"/>
+      <c r="CRX102" s="6"/>
+      <c r="CRZ102" s="6"/>
+      <c r="CSB102" s="6"/>
+      <c r="CSD102" s="6"/>
+      <c r="CSF102" s="6"/>
+      <c r="CSH102" s="6"/>
+      <c r="CSJ102" s="6"/>
+      <c r="CSL102" s="6"/>
+      <c r="CSN102" s="6"/>
+      <c r="CSP102" s="6"/>
+      <c r="CSR102" s="6"/>
+      <c r="CST102" s="6"/>
+      <c r="CSV102" s="6"/>
+      <c r="CSX102" s="6"/>
+      <c r="CSZ102" s="6"/>
+      <c r="CTB102" s="6"/>
+      <c r="CTD102" s="6"/>
+      <c r="CTF102" s="6"/>
+      <c r="CTH102" s="6"/>
+      <c r="CTJ102" s="6"/>
+      <c r="CTL102" s="6"/>
+      <c r="CTN102" s="6"/>
+      <c r="CTP102" s="6"/>
+      <c r="CTR102" s="6"/>
+      <c r="CTT102" s="6"/>
+      <c r="CTV102" s="6"/>
+      <c r="CTX102" s="6"/>
+      <c r="CTZ102" s="6"/>
+      <c r="CUB102" s="6"/>
+      <c r="CUD102" s="6"/>
+      <c r="CUF102" s="6"/>
+      <c r="CUH102" s="6"/>
+      <c r="CUJ102" s="6"/>
+      <c r="CUL102" s="6"/>
+      <c r="CUN102" s="6"/>
+      <c r="CUP102" s="6"/>
+      <c r="CUR102" s="6"/>
+      <c r="CUT102" s="6"/>
+      <c r="CUV102" s="6"/>
+      <c r="CUX102" s="6"/>
+      <c r="CUZ102" s="6"/>
+      <c r="CVB102" s="6"/>
+      <c r="CVD102" s="6"/>
+      <c r="CVF102" s="6"/>
+      <c r="CVH102" s="6"/>
+      <c r="CVJ102" s="6"/>
+      <c r="CVL102" s="6"/>
+      <c r="CVN102" s="6"/>
+      <c r="CVP102" s="6"/>
+      <c r="CVR102" s="6"/>
+      <c r="CVT102" s="6"/>
+      <c r="CVV102" s="6"/>
+      <c r="CVX102" s="6"/>
+      <c r="CVZ102" s="6"/>
+      <c r="CWB102" s="6"/>
+      <c r="CWD102" s="6"/>
+      <c r="CWF102" s="6"/>
+      <c r="CWH102" s="6"/>
+      <c r="CWJ102" s="6"/>
+      <c r="CWL102" s="6"/>
+      <c r="CWN102" s="6"/>
+      <c r="CWP102" s="6"/>
+      <c r="CWR102" s="6"/>
+      <c r="CWT102" s="6"/>
+      <c r="CWV102" s="6"/>
+      <c r="CWX102" s="6"/>
+      <c r="CWZ102" s="6"/>
+      <c r="CXB102" s="6"/>
+      <c r="CXD102" s="6"/>
+      <c r="CXF102" s="6"/>
+      <c r="CXH102" s="6"/>
+      <c r="CXJ102" s="6"/>
+      <c r="CXL102" s="6"/>
+      <c r="CXN102" s="6"/>
+      <c r="CXP102" s="6"/>
+      <c r="CXR102" s="6"/>
+      <c r="CXT102" s="6"/>
+      <c r="CXV102" s="6"/>
+      <c r="CXX102" s="6"/>
+      <c r="CXZ102" s="6"/>
+      <c r="CYB102" s="6"/>
+      <c r="CYD102" s="6"/>
+      <c r="CYF102" s="6"/>
+      <c r="CYH102" s="6"/>
+      <c r="CYJ102" s="6"/>
+      <c r="CYL102" s="6"/>
+      <c r="CYN102" s="6"/>
+      <c r="CYP102" s="6"/>
+      <c r="CYR102" s="6"/>
+      <c r="CYT102" s="6"/>
+      <c r="CYV102" s="6"/>
+      <c r="CYX102" s="6"/>
+      <c r="CYZ102" s="6"/>
+      <c r="CZB102" s="6"/>
+      <c r="CZD102" s="6"/>
+      <c r="CZF102" s="6"/>
+      <c r="CZH102" s="6"/>
+      <c r="CZJ102" s="6"/>
+      <c r="CZL102" s="6"/>
+      <c r="CZN102" s="6"/>
+      <c r="CZP102" s="6"/>
+      <c r="CZR102" s="6"/>
+      <c r="CZT102" s="6"/>
+      <c r="CZV102" s="6"/>
+      <c r="CZX102" s="6"/>
+      <c r="CZZ102" s="6"/>
+      <c r="DAB102" s="6"/>
+      <c r="DAD102" s="6"/>
+      <c r="DAF102" s="6"/>
+      <c r="DAH102" s="6"/>
+      <c r="DAJ102" s="6"/>
+      <c r="DAL102" s="6"/>
+      <c r="DAN102" s="6"/>
+      <c r="DAP102" s="6"/>
+      <c r="DAR102" s="6"/>
+      <c r="DAT102" s="6"/>
+      <c r="DAV102" s="6"/>
+      <c r="DAX102" s="6"/>
+      <c r="DAZ102" s="6"/>
+      <c r="DBB102" s="6"/>
+      <c r="DBD102" s="6"/>
+      <c r="DBF102" s="6"/>
+      <c r="DBH102" s="6"/>
+      <c r="DBJ102" s="6"/>
+      <c r="DBL102" s="6"/>
+      <c r="DBN102" s="6"/>
+      <c r="DBP102" s="6"/>
+      <c r="DBR102" s="6"/>
+      <c r="DBT102" s="6"/>
+      <c r="DBV102" s="6"/>
+      <c r="DBX102" s="6"/>
+      <c r="DBZ102" s="6"/>
+      <c r="DCB102" s="6"/>
+      <c r="DCD102" s="6"/>
+      <c r="DCF102" s="6"/>
+      <c r="DCH102" s="6"/>
+      <c r="DCJ102" s="6"/>
+      <c r="DCL102" s="6"/>
+      <c r="DCN102" s="6"/>
+      <c r="DCP102" s="6"/>
+      <c r="DCR102" s="6"/>
+      <c r="DCT102" s="6"/>
+      <c r="DCV102" s="6"/>
+      <c r="DCX102" s="6"/>
+      <c r="DCZ102" s="6"/>
+      <c r="DDB102" s="6"/>
+      <c r="DDD102" s="6"/>
+      <c r="DDF102" s="6"/>
+      <c r="DDH102" s="6"/>
+      <c r="DDJ102" s="6"/>
+      <c r="DDL102" s="6"/>
+      <c r="DDN102" s="6"/>
+      <c r="DDP102" s="6"/>
+      <c r="DDR102" s="6"/>
+      <c r="DDT102" s="6"/>
+      <c r="DDV102" s="6"/>
+      <c r="DDX102" s="6"/>
+      <c r="DDZ102" s="6"/>
+      <c r="DEB102" s="6"/>
+      <c r="DED102" s="6"/>
+      <c r="DEF102" s="6"/>
+      <c r="DEH102" s="6"/>
+      <c r="DEJ102" s="6"/>
+      <c r="DEL102" s="6"/>
+      <c r="DEN102" s="6"/>
+      <c r="DEP102" s="6"/>
+      <c r="DER102" s="6"/>
+      <c r="DET102" s="6"/>
+      <c r="DEV102" s="6"/>
+      <c r="DEX102" s="6"/>
+      <c r="DEZ102" s="6"/>
+      <c r="DFB102" s="6"/>
+      <c r="DFD102" s="6"/>
+      <c r="DFF102" s="6"/>
+      <c r="DFH102" s="6"/>
+      <c r="DFJ102" s="6"/>
+      <c r="DFL102" s="6"/>
+      <c r="DFN102" s="6"/>
+      <c r="DFP102" s="6"/>
+      <c r="DFR102" s="6"/>
+      <c r="DFT102" s="6"/>
+      <c r="DFV102" s="6"/>
+      <c r="DFX102" s="6"/>
+      <c r="DFZ102" s="6"/>
+      <c r="DGB102" s="6"/>
+      <c r="DGD102" s="6"/>
+      <c r="DGF102" s="6"/>
+      <c r="DGH102" s="6"/>
+      <c r="DGJ102" s="6"/>
+      <c r="DGL102" s="6"/>
+      <c r="DGN102" s="6"/>
+      <c r="DGP102" s="6"/>
+      <c r="DGR102" s="6"/>
+      <c r="DGT102" s="6"/>
+      <c r="DGV102" s="6"/>
+      <c r="DGX102" s="6"/>
+      <c r="DGZ102" s="6"/>
+      <c r="DHB102" s="6"/>
+      <c r="DHD102" s="6"/>
+      <c r="DHF102" s="6"/>
+      <c r="DHH102" s="6"/>
+      <c r="DHJ102" s="6"/>
+      <c r="DHL102" s="6"/>
+      <c r="DHN102" s="6"/>
+      <c r="DHP102" s="6"/>
+      <c r="DHR102" s="6"/>
+      <c r="DHT102" s="6"/>
+      <c r="DHV102" s="6"/>
+      <c r="DHX102" s="6"/>
+      <c r="DHZ102" s="6"/>
+      <c r="DIB102" s="6"/>
+      <c r="DID102" s="6"/>
+      <c r="DIF102" s="6"/>
+      <c r="DIH102" s="6"/>
+      <c r="DIJ102" s="6"/>
+      <c r="DIL102" s="6"/>
+      <c r="DIN102" s="6"/>
+      <c r="DIP102" s="6"/>
+      <c r="DIR102" s="6"/>
+      <c r="DIT102" s="6"/>
+      <c r="DIV102" s="6"/>
+      <c r="DIX102" s="6"/>
+      <c r="DIZ102" s="6"/>
+      <c r="DJB102" s="6"/>
+      <c r="DJD102" s="6"/>
+      <c r="DJF102" s="6"/>
+      <c r="DJH102" s="6"/>
+      <c r="DJJ102" s="6"/>
+      <c r="DJL102" s="6"/>
+      <c r="DJN102" s="6"/>
+      <c r="DJP102" s="6"/>
+      <c r="DJR102" s="6"/>
+      <c r="DJT102" s="6"/>
+      <c r="DJV102" s="6"/>
+      <c r="DJX102" s="6"/>
+      <c r="DJZ102" s="6"/>
+      <c r="DKB102" s="6"/>
+      <c r="DKD102" s="6"/>
+      <c r="DKF102" s="6"/>
+      <c r="DKH102" s="6"/>
+      <c r="DKJ102" s="6"/>
+      <c r="DKL102" s="6"/>
+      <c r="DKN102" s="6"/>
+      <c r="DKP102" s="6"/>
+      <c r="DKR102" s="6"/>
+      <c r="DKT102" s="6"/>
+      <c r="DKV102" s="6"/>
+      <c r="DKX102" s="6"/>
+      <c r="DKZ102" s="6"/>
+      <c r="DLB102" s="6"/>
+      <c r="DLD102" s="6"/>
+      <c r="DLF102" s="6"/>
+      <c r="DLH102" s="6"/>
+      <c r="DLJ102" s="6"/>
+      <c r="DLL102" s="6"/>
+      <c r="DLN102" s="6"/>
+      <c r="DLP102" s="6"/>
+      <c r="DLR102" s="6"/>
+      <c r="DLT102" s="6"/>
+      <c r="DLV102" s="6"/>
+      <c r="DLX102" s="6"/>
+      <c r="DLZ102" s="6"/>
+      <c r="DMB102" s="6"/>
+      <c r="DMD102" s="6"/>
+      <c r="DMF102" s="6"/>
+      <c r="DMH102" s="6"/>
+      <c r="DMJ102" s="6"/>
+      <c r="DML102" s="6"/>
+      <c r="DMN102" s="6"/>
+      <c r="DMP102" s="6"/>
+      <c r="DMR102" s="6"/>
+      <c r="DMT102" s="6"/>
+      <c r="DMV102" s="6"/>
+      <c r="DMX102" s="6"/>
+      <c r="DMZ102" s="6"/>
+      <c r="DNB102" s="6"/>
+      <c r="DND102" s="6"/>
+      <c r="DNF102" s="6"/>
+      <c r="DNH102" s="6"/>
+      <c r="DNJ102" s="6"/>
+      <c r="DNL102" s="6"/>
+      <c r="DNN102" s="6"/>
+      <c r="DNP102" s="6"/>
+      <c r="DNR102" s="6"/>
+      <c r="DNT102" s="6"/>
+      <c r="DNV102" s="6"/>
+      <c r="DNX102" s="6"/>
+      <c r="DNZ102" s="6"/>
+      <c r="DOB102" s="6"/>
+      <c r="DOD102" s="6"/>
+      <c r="DOF102" s="6"/>
+      <c r="DOH102" s="6"/>
+      <c r="DOJ102" s="6"/>
+      <c r="DOL102" s="6"/>
+      <c r="DON102" s="6"/>
+      <c r="DOP102" s="6"/>
+      <c r="DOR102" s="6"/>
+      <c r="DOT102" s="6"/>
+      <c r="DOV102" s="6"/>
+      <c r="DOX102" s="6"/>
+      <c r="DOZ102" s="6"/>
+      <c r="DPB102" s="6"/>
+      <c r="DPD102" s="6"/>
+      <c r="DPF102" s="6"/>
+      <c r="DPH102" s="6"/>
+      <c r="DPJ102" s="6"/>
+      <c r="DPL102" s="6"/>
+      <c r="DPN102" s="6"/>
+      <c r="DPP102" s="6"/>
+      <c r="DPR102" s="6"/>
+      <c r="DPT102" s="6"/>
+      <c r="DPV102" s="6"/>
+      <c r="DPX102" s="6"/>
+      <c r="DPZ102" s="6"/>
+      <c r="DQB102" s="6"/>
+      <c r="DQD102" s="6"/>
+      <c r="DQF102" s="6"/>
+      <c r="DQH102" s="6"/>
+      <c r="DQJ102" s="6"/>
+      <c r="DQL102" s="6"/>
+      <c r="DQN102" s="6"/>
+      <c r="DQP102" s="6"/>
+      <c r="DQR102" s="6"/>
+      <c r="DQT102" s="6"/>
+      <c r="DQV102" s="6"/>
+      <c r="DQX102" s="6"/>
+      <c r="DQZ102" s="6"/>
+      <c r="DRB102" s="6"/>
+      <c r="DRD102" s="6"/>
+      <c r="DRF102" s="6"/>
+      <c r="DRH102" s="6"/>
+      <c r="DRJ102" s="6"/>
+      <c r="DRL102" s="6"/>
+      <c r="DRN102" s="6"/>
+      <c r="DRP102" s="6"/>
+      <c r="DRR102" s="6"/>
+      <c r="DRT102" s="6"/>
+      <c r="DRV102" s="6"/>
+      <c r="DRX102" s="6"/>
+      <c r="DRZ102" s="6"/>
+      <c r="DSB102" s="6"/>
+      <c r="DSD102" s="6"/>
+      <c r="DSF102" s="6"/>
+      <c r="DSH102" s="6"/>
+      <c r="DSJ102" s="6"/>
+      <c r="DSL102" s="6"/>
+      <c r="DSN102" s="6"/>
+      <c r="DSP102" s="6"/>
+      <c r="DSR102" s="6"/>
+      <c r="DST102" s="6"/>
+      <c r="DSV102" s="6"/>
+      <c r="DSX102" s="6"/>
+      <c r="DSZ102" s="6"/>
+      <c r="DTB102" s="6"/>
+      <c r="DTD102" s="6"/>
+      <c r="DTF102" s="6"/>
+      <c r="DTH102" s="6"/>
+      <c r="DTJ102" s="6"/>
+      <c r="DTL102" s="6"/>
+      <c r="DTN102" s="6"/>
+      <c r="DTP102" s="6"/>
+      <c r="DTR102" s="6"/>
+      <c r="DTT102" s="6"/>
+      <c r="DTV102" s="6"/>
+      <c r="DTX102" s="6"/>
+      <c r="DTZ102" s="6"/>
+      <c r="DUB102" s="6"/>
+      <c r="DUD102" s="6"/>
+      <c r="DUF102" s="6"/>
+      <c r="DUH102" s="6"/>
+      <c r="DUJ102" s="6"/>
+      <c r="DUL102" s="6"/>
+      <c r="DUN102" s="6"/>
+      <c r="DUP102" s="6"/>
+      <c r="DUR102" s="6"/>
+      <c r="DUT102" s="6"/>
+      <c r="DUV102" s="6"/>
+      <c r="DUX102" s="6"/>
+      <c r="DUZ102" s="6"/>
+      <c r="DVB102" s="6"/>
+      <c r="DVD102" s="6"/>
+      <c r="DVF102" s="6"/>
+      <c r="DVH102" s="6"/>
+      <c r="DVJ102" s="6"/>
+      <c r="DVL102" s="6"/>
+      <c r="DVN102" s="6"/>
+      <c r="DVP102" s="6"/>
+      <c r="DVR102" s="6"/>
+      <c r="DVT102" s="6"/>
+      <c r="DVV102" s="6"/>
+      <c r="DVX102" s="6"/>
+      <c r="DVZ102" s="6"/>
+      <c r="DWB102" s="6"/>
+      <c r="DWD102" s="6"/>
+      <c r="DWF102" s="6"/>
+      <c r="DWH102" s="6"/>
+      <c r="DWJ102" s="6"/>
+      <c r="DWL102" s="6"/>
+      <c r="DWN102" s="6"/>
+      <c r="DWP102" s="6"/>
+      <c r="DWR102" s="6"/>
+      <c r="DWT102" s="6"/>
+      <c r="DWV102" s="6"/>
+      <c r="DWX102" s="6"/>
+      <c r="DWZ102" s="6"/>
+      <c r="DXB102" s="6"/>
+      <c r="DXD102" s="6"/>
+      <c r="DXF102" s="6"/>
+      <c r="DXH102" s="6"/>
+      <c r="DXJ102" s="6"/>
+      <c r="DXL102" s="6"/>
+      <c r="DXN102" s="6"/>
+      <c r="DXP102" s="6"/>
+      <c r="DXR102" s="6"/>
+      <c r="DXT102" s="6"/>
+      <c r="DXV102" s="6"/>
+      <c r="DXX102" s="6"/>
+      <c r="DXZ102" s="6"/>
+      <c r="DYB102" s="6"/>
+      <c r="DYD102" s="6"/>
+      <c r="DYF102" s="6"/>
+      <c r="DYH102" s="6"/>
+      <c r="DYJ102" s="6"/>
+      <c r="DYL102" s="6"/>
+      <c r="DYN102" s="6"/>
+      <c r="DYP102" s="6"/>
+      <c r="DYR102" s="6"/>
+      <c r="DYT102" s="6"/>
+      <c r="DYV102" s="6"/>
+      <c r="DYX102" s="6"/>
+      <c r="DYZ102" s="6"/>
+      <c r="DZB102" s="6"/>
+      <c r="DZD102" s="6"/>
+      <c r="DZF102" s="6"/>
+      <c r="DZH102" s="6"/>
+      <c r="DZJ102" s="6"/>
+      <c r="DZL102" s="6"/>
+      <c r="DZN102" s="6"/>
+      <c r="DZP102" s="6"/>
+      <c r="DZR102" s="6"/>
+      <c r="DZT102" s="6"/>
+      <c r="DZV102" s="6"/>
+      <c r="DZX102" s="6"/>
+      <c r="DZZ102" s="6"/>
+      <c r="EAB102" s="6"/>
+      <c r="EAD102" s="6"/>
+      <c r="EAF102" s="6"/>
+      <c r="EAH102" s="6"/>
+      <c r="EAJ102" s="6"/>
+      <c r="EAL102" s="6"/>
+      <c r="EAN102" s="6"/>
+      <c r="EAP102" s="6"/>
+      <c r="EAR102" s="6"/>
+      <c r="EAT102" s="6"/>
+      <c r="EAV102" s="6"/>
+      <c r="EAX102" s="6"/>
+      <c r="EAZ102" s="6"/>
+      <c r="EBB102" s="6"/>
+      <c r="EBD102" s="6"/>
+      <c r="EBF102" s="6"/>
+      <c r="EBH102" s="6"/>
+      <c r="EBJ102" s="6"/>
+      <c r="EBL102" s="6"/>
+      <c r="EBN102" s="6"/>
+      <c r="EBP102" s="6"/>
+      <c r="EBR102" s="6"/>
+      <c r="EBT102" s="6"/>
+      <c r="EBV102" s="6"/>
+      <c r="EBX102" s="6"/>
+      <c r="EBZ102" s="6"/>
+      <c r="ECB102" s="6"/>
+      <c r="ECD102" s="6"/>
+      <c r="ECF102" s="6"/>
+      <c r="ECH102" s="6"/>
+      <c r="ECJ102" s="6"/>
+      <c r="ECL102" s="6"/>
+      <c r="ECN102" s="6"/>
+      <c r="ECP102" s="6"/>
+      <c r="ECR102" s="6"/>
+      <c r="ECT102" s="6"/>
+      <c r="ECV102" s="6"/>
+      <c r="ECX102" s="6"/>
+      <c r="ECZ102" s="6"/>
+      <c r="EDB102" s="6"/>
+      <c r="EDD102" s="6"/>
+      <c r="EDF102" s="6"/>
+      <c r="EDH102" s="6"/>
+      <c r="EDJ102" s="6"/>
+      <c r="EDL102" s="6"/>
+      <c r="EDN102" s="6"/>
+      <c r="EDP102" s="6"/>
+      <c r="EDR102" s="6"/>
+      <c r="EDT102" s="6"/>
+      <c r="EDV102" s="6"/>
+      <c r="EDX102" s="6"/>
+      <c r="EDZ102" s="6"/>
+      <c r="EEB102" s="6"/>
+      <c r="EED102" s="6"/>
+      <c r="EEF102" s="6"/>
+      <c r="EEH102" s="6"/>
+      <c r="EEJ102" s="6"/>
+      <c r="EEL102" s="6"/>
+      <c r="EEN102" s="6"/>
+      <c r="EEP102" s="6"/>
+      <c r="EER102" s="6"/>
+      <c r="EET102" s="6"/>
+      <c r="EEV102" s="6"/>
+      <c r="EEX102" s="6"/>
+      <c r="EEZ102" s="6"/>
+      <c r="EFB102" s="6"/>
+      <c r="EFD102" s="6"/>
+      <c r="EFF102" s="6"/>
+      <c r="EFH102" s="6"/>
+      <c r="EFJ102" s="6"/>
+      <c r="EFL102" s="6"/>
+      <c r="EFN102" s="6"/>
+      <c r="EFP102" s="6"/>
+      <c r="EFR102" s="6"/>
+      <c r="EFT102" s="6"/>
+      <c r="EFV102" s="6"/>
+      <c r="EFX102" s="6"/>
+      <c r="EFZ102" s="6"/>
+      <c r="EGB102" s="6"/>
+      <c r="EGD102" s="6"/>
+      <c r="EGF102" s="6"/>
+      <c r="EGH102" s="6"/>
+      <c r="EGJ102" s="6"/>
+      <c r="EGL102" s="6"/>
+      <c r="EGN102" s="6"/>
+      <c r="EGP102" s="6"/>
+      <c r="EGR102" s="6"/>
+      <c r="EGT102" s="6"/>
+      <c r="EGV102" s="6"/>
+      <c r="EGX102" s="6"/>
+      <c r="EGZ102" s="6"/>
+      <c r="EHB102" s="6"/>
+      <c r="EHD102" s="6"/>
+      <c r="EHF102" s="6"/>
+      <c r="EHH102" s="6"/>
+      <c r="EHJ102" s="6"/>
+      <c r="EHL102" s="6"/>
+      <c r="EHN102" s="6"/>
+      <c r="EHP102" s="6"/>
+      <c r="EHR102" s="6"/>
+      <c r="EHT102" s="6"/>
+      <c r="EHV102" s="6"/>
+      <c r="EHX102" s="6"/>
+      <c r="EHZ102" s="6"/>
+      <c r="EIB102" s="6"/>
+      <c r="EID102" s="6"/>
+      <c r="EIF102" s="6"/>
+      <c r="EIH102" s="6"/>
+      <c r="EIJ102" s="6"/>
+      <c r="EIL102" s="6"/>
+      <c r="EIN102" s="6"/>
+      <c r="EIP102" s="6"/>
+      <c r="EIR102" s="6"/>
+      <c r="EIT102" s="6"/>
+      <c r="EIV102" s="6"/>
+      <c r="EIX102" s="6"/>
+      <c r="EIZ102" s="6"/>
+      <c r="EJB102" s="6"/>
+      <c r="EJD102" s="6"/>
+      <c r="EJF102" s="6"/>
+      <c r="EJH102" s="6"/>
+      <c r="EJJ102" s="6"/>
+      <c r="EJL102" s="6"/>
+      <c r="EJN102" s="6"/>
+      <c r="EJP102" s="6"/>
+      <c r="EJR102" s="6"/>
+      <c r="EJT102" s="6"/>
+      <c r="EJV102" s="6"/>
+      <c r="EJX102" s="6"/>
+      <c r="EJZ102" s="6"/>
+      <c r="EKB102" s="6"/>
+      <c r="EKD102" s="6"/>
+      <c r="EKF102" s="6"/>
+      <c r="EKH102" s="6"/>
+      <c r="EKJ102" s="6"/>
+      <c r="EKL102" s="6"/>
+      <c r="EKN102" s="6"/>
+      <c r="EKP102" s="6"/>
+      <c r="EKR102" s="6"/>
+      <c r="EKT102" s="6"/>
+      <c r="EKV102" s="6"/>
+      <c r="EKX102" s="6"/>
+      <c r="EKZ102" s="6"/>
+      <c r="ELB102" s="6"/>
+      <c r="ELD102" s="6"/>
+      <c r="ELF102" s="6"/>
+      <c r="ELH102" s="6"/>
+      <c r="ELJ102" s="6"/>
+      <c r="ELL102" s="6"/>
+      <c r="ELN102" s="6"/>
+      <c r="ELP102" s="6"/>
+      <c r="ELR102" s="6"/>
+      <c r="ELT102" s="6"/>
+      <c r="ELV102" s="6"/>
+      <c r="ELX102" s="6"/>
+      <c r="ELZ102" s="6"/>
+      <c r="EMB102" s="6"/>
+      <c r="EMD102" s="6"/>
+      <c r="EMF102" s="6"/>
+      <c r="EMH102" s="6"/>
+      <c r="EMJ102" s="6"/>
+      <c r="EML102" s="6"/>
+      <c r="EMN102" s="6"/>
+      <c r="EMP102" s="6"/>
+      <c r="EMR102" s="6"/>
+      <c r="EMT102" s="6"/>
+      <c r="EMV102" s="6"/>
+      <c r="EMX102" s="6"/>
+      <c r="EMZ102" s="6"/>
+      <c r="ENB102" s="6"/>
+      <c r="END102" s="6"/>
+      <c r="ENF102" s="6"/>
+      <c r="ENH102" s="6"/>
+      <c r="ENJ102" s="6"/>
+      <c r="ENL102" s="6"/>
+      <c r="ENN102" s="6"/>
+      <c r="ENP102" s="6"/>
+      <c r="ENR102" s="6"/>
+      <c r="ENT102" s="6"/>
+      <c r="ENV102" s="6"/>
+      <c r="ENX102" s="6"/>
+      <c r="ENZ102" s="6"/>
+      <c r="EOB102" s="6"/>
+      <c r="EOD102" s="6"/>
+      <c r="EOF102" s="6"/>
+      <c r="EOH102" s="6"/>
+      <c r="EOJ102" s="6"/>
+      <c r="EOL102" s="6"/>
+      <c r="EON102" s="6"/>
+      <c r="EOP102" s="6"/>
+      <c r="EOR102" s="6"/>
+      <c r="EOT102" s="6"/>
+      <c r="EOV102" s="6"/>
+      <c r="EOX102" s="6"/>
+      <c r="EOZ102" s="6"/>
+      <c r="EPB102" s="6"/>
+      <c r="EPD102" s="6"/>
+      <c r="EPF102" s="6"/>
+      <c r="EPH102" s="6"/>
+      <c r="EPJ102" s="6"/>
+      <c r="EPL102" s="6"/>
+      <c r="EPN102" s="6"/>
+      <c r="EPP102" s="6"/>
+      <c r="EPR102" s="6"/>
+      <c r="EPT102" s="6"/>
+      <c r="EPV102" s="6"/>
+      <c r="EPX102" s="6"/>
+      <c r="EPZ102" s="6"/>
+      <c r="EQB102" s="6"/>
+      <c r="EQD102" s="6"/>
+      <c r="EQF102" s="6"/>
+      <c r="EQH102" s="6"/>
+      <c r="EQJ102" s="6"/>
+      <c r="EQL102" s="6"/>
+      <c r="EQN102" s="6"/>
+      <c r="EQP102" s="6"/>
+      <c r="EQR102" s="6"/>
+      <c r="EQT102" s="6"/>
+      <c r="EQV102" s="6"/>
+      <c r="EQX102" s="6"/>
+      <c r="EQZ102" s="6"/>
+      <c r="ERB102" s="6"/>
+      <c r="ERD102" s="6"/>
+      <c r="ERF102" s="6"/>
+      <c r="ERH102" s="6"/>
+      <c r="ERJ102" s="6"/>
+      <c r="ERL102" s="6"/>
+      <c r="ERN102" s="6"/>
+      <c r="ERP102" s="6"/>
+      <c r="ERR102" s="6"/>
+      <c r="ERT102" s="6"/>
+      <c r="ERV102" s="6"/>
+      <c r="ERX102" s="6"/>
+      <c r="ERZ102" s="6"/>
+      <c r="ESB102" s="6"/>
+      <c r="ESD102" s="6"/>
+      <c r="ESF102" s="6"/>
+      <c r="ESH102" s="6"/>
+      <c r="ESJ102" s="6"/>
+      <c r="ESL102" s="6"/>
+      <c r="ESN102" s="6"/>
+      <c r="ESP102" s="6"/>
+      <c r="ESR102" s="6"/>
+      <c r="EST102" s="6"/>
+      <c r="ESV102" s="6"/>
+      <c r="ESX102" s="6"/>
+      <c r="ESZ102" s="6"/>
+      <c r="ETB102" s="6"/>
+      <c r="ETD102" s="6"/>
+      <c r="ETF102" s="6"/>
+      <c r="ETH102" s="6"/>
+      <c r="ETJ102" s="6"/>
+      <c r="ETL102" s="6"/>
+      <c r="ETN102" s="6"/>
+      <c r="ETP102" s="6"/>
+      <c r="ETR102" s="6"/>
+      <c r="ETT102" s="6"/>
+      <c r="ETV102" s="6"/>
+      <c r="ETX102" s="6"/>
+      <c r="ETZ102" s="6"/>
+      <c r="EUB102" s="6"/>
+      <c r="EUD102" s="6"/>
+      <c r="EUF102" s="6"/>
+      <c r="EUH102" s="6"/>
+      <c r="EUJ102" s="6"/>
+      <c r="EUL102" s="6"/>
+      <c r="EUN102" s="6"/>
+      <c r="EUP102" s="6"/>
+      <c r="EUR102" s="6"/>
+      <c r="EUT102" s="6"/>
+      <c r="EUV102" s="6"/>
+      <c r="EUX102" s="6"/>
+      <c r="EUZ102" s="6"/>
+      <c r="EVB102" s="6"/>
+      <c r="EVD102" s="6"/>
+      <c r="EVF102" s="6"/>
+      <c r="EVH102" s="6"/>
+      <c r="EVJ102" s="6"/>
+      <c r="EVL102" s="6"/>
+      <c r="EVN102" s="6"/>
+      <c r="EVP102" s="6"/>
+      <c r="EVR102" s="6"/>
+      <c r="EVT102" s="6"/>
+      <c r="EVV102" s="6"/>
+      <c r="EVX102" s="6"/>
+      <c r="EVZ102" s="6"/>
+      <c r="EWB102" s="6"/>
+      <c r="EWD102" s="6"/>
+      <c r="EWF102" s="6"/>
+      <c r="EWH102" s="6"/>
+      <c r="EWJ102" s="6"/>
+      <c r="EWL102" s="6"/>
+      <c r="EWN102" s="6"/>
+      <c r="EWP102" s="6"/>
+      <c r="EWR102" s="6"/>
+      <c r="EWT102" s="6"/>
+      <c r="EWV102" s="6"/>
+      <c r="EWX102" s="6"/>
+      <c r="EWZ102" s="6"/>
+      <c r="EXB102" s="6"/>
+      <c r="EXD102" s="6"/>
+      <c r="EXF102" s="6"/>
+      <c r="EXH102" s="6"/>
+      <c r="EXJ102" s="6"/>
+      <c r="EXL102" s="6"/>
+      <c r="EXN102" s="6"/>
+      <c r="EXP102" s="6"/>
+      <c r="EXR102" s="6"/>
+      <c r="EXT102" s="6"/>
+      <c r="EXV102" s="6"/>
+      <c r="EXX102" s="6"/>
+      <c r="EXZ102" s="6"/>
+      <c r="EYB102" s="6"/>
+      <c r="EYD102" s="6"/>
+      <c r="EYF102" s="6"/>
+      <c r="EYH102" s="6"/>
+      <c r="EYJ102" s="6"/>
+      <c r="EYL102" s="6"/>
+      <c r="EYN102" s="6"/>
+      <c r="EYP102" s="6"/>
+      <c r="EYR102" s="6"/>
+      <c r="EYT102" s="6"/>
+      <c r="EYV102" s="6"/>
+      <c r="EYX102" s="6"/>
+      <c r="EYZ102" s="6"/>
+      <c r="EZB102" s="6"/>
+      <c r="EZD102" s="6"/>
+      <c r="EZF102" s="6"/>
+      <c r="EZH102" s="6"/>
+      <c r="EZJ102" s="6"/>
+      <c r="EZL102" s="6"/>
+      <c r="EZN102" s="6"/>
+      <c r="EZP102" s="6"/>
+      <c r="EZR102" s="6"/>
+      <c r="EZT102" s="6"/>
+      <c r="EZV102" s="6"/>
+      <c r="EZX102" s="6"/>
+      <c r="EZZ102" s="6"/>
+      <c r="FAB102" s="6"/>
+      <c r="FAD102" s="6"/>
+      <c r="FAF102" s="6"/>
+      <c r="FAH102" s="6"/>
+      <c r="FAJ102" s="6"/>
+      <c r="FAL102" s="6"/>
+      <c r="FAN102" s="6"/>
+      <c r="FAP102" s="6"/>
+      <c r="FAR102" s="6"/>
+      <c r="FAT102" s="6"/>
+      <c r="FAV102" s="6"/>
+      <c r="FAX102" s="6"/>
+      <c r="FAZ102" s="6"/>
+      <c r="FBB102" s="6"/>
+      <c r="FBD102" s="6"/>
+      <c r="FBF102" s="6"/>
+      <c r="FBH102" s="6"/>
+      <c r="FBJ102" s="6"/>
+      <c r="FBL102" s="6"/>
+      <c r="FBN102" s="6"/>
+      <c r="FBP102" s="6"/>
+      <c r="FBR102" s="6"/>
+      <c r="FBT102" s="6"/>
+      <c r="FBV102" s="6"/>
+      <c r="FBX102" s="6"/>
+      <c r="FBZ102" s="6"/>
+      <c r="FCB102" s="6"/>
+      <c r="FCD102" s="6"/>
+      <c r="FCF102" s="6"/>
+      <c r="FCH102" s="6"/>
+      <c r="FCJ102" s="6"/>
+      <c r="FCL102" s="6"/>
+      <c r="FCN102" s="6"/>
+      <c r="FCP102" s="6"/>
+      <c r="FCR102" s="6"/>
+      <c r="FCT102" s="6"/>
+      <c r="FCV102" s="6"/>
+      <c r="FCX102" s="6"/>
+      <c r="FCZ102" s="6"/>
+      <c r="FDB102" s="6"/>
+      <c r="FDD102" s="6"/>
+      <c r="FDF102" s="6"/>
+      <c r="FDH102" s="6"/>
+      <c r="FDJ102" s="6"/>
+      <c r="FDL102" s="6"/>
+      <c r="FDN102" s="6"/>
+      <c r="FDP102" s="6"/>
+      <c r="FDR102" s="6"/>
+      <c r="FDT102" s="6"/>
+      <c r="FDV102" s="6"/>
+      <c r="FDX102" s="6"/>
+      <c r="FDZ102" s="6"/>
+      <c r="FEB102" s="6"/>
+      <c r="FED102" s="6"/>
+      <c r="FEF102" s="6"/>
+      <c r="FEH102" s="6"/>
+      <c r="FEJ102" s="6"/>
+      <c r="FEL102" s="6"/>
+      <c r="FEN102" s="6"/>
+      <c r="FEP102" s="6"/>
+      <c r="FER102" s="6"/>
+      <c r="FET102" s="6"/>
+      <c r="FEV102" s="6"/>
+      <c r="FEX102" s="6"/>
+      <c r="FEZ102" s="6"/>
+      <c r="FFB102" s="6"/>
+      <c r="FFD102" s="6"/>
+      <c r="FFF102" s="6"/>
+      <c r="FFH102" s="6"/>
+      <c r="FFJ102" s="6"/>
+      <c r="FFL102" s="6"/>
+      <c r="FFN102" s="6"/>
+      <c r="FFP102" s="6"/>
+      <c r="FFR102" s="6"/>
+      <c r="FFT102" s="6"/>
+      <c r="FFV102" s="6"/>
+      <c r="FFX102" s="6"/>
+      <c r="FFZ102" s="6"/>
+      <c r="FGB102" s="6"/>
+      <c r="FGD102" s="6"/>
+      <c r="FGF102" s="6"/>
+      <c r="FGH102" s="6"/>
+      <c r="FGJ102" s="6"/>
+      <c r="FGL102" s="6"/>
+      <c r="FGN102" s="6"/>
+      <c r="FGP102" s="6"/>
+      <c r="FGR102" s="6"/>
+      <c r="FGT102" s="6"/>
+      <c r="FGV102" s="6"/>
+      <c r="FGX102" s="6"/>
+      <c r="FGZ102" s="6"/>
+      <c r="FHB102" s="6"/>
+      <c r="FHD102" s="6"/>
+      <c r="FHF102" s="6"/>
+      <c r="FHH102" s="6"/>
+      <c r="FHJ102" s="6"/>
+      <c r="FHL102" s="6"/>
+      <c r="FHN102" s="6"/>
+      <c r="FHP102" s="6"/>
+      <c r="FHR102" s="6"/>
+      <c r="FHT102" s="6"/>
+      <c r="FHV102" s="6"/>
+      <c r="FHX102" s="6"/>
+      <c r="FHZ102" s="6"/>
+      <c r="FIB102" s="6"/>
+      <c r="FID102" s="6"/>
+      <c r="FIF102" s="6"/>
+      <c r="FIH102" s="6"/>
+      <c r="FIJ102" s="6"/>
+      <c r="FIL102" s="6"/>
+      <c r="FIN102" s="6"/>
+      <c r="FIP102" s="6"/>
+      <c r="FIR102" s="6"/>
+      <c r="FIT102" s="6"/>
+      <c r="FIV102" s="6"/>
+      <c r="FIX102" s="6"/>
+      <c r="FIZ102" s="6"/>
+      <c r="FJB102" s="6"/>
+      <c r="FJD102" s="6"/>
+      <c r="FJF102" s="6"/>
+      <c r="FJH102" s="6"/>
+      <c r="FJJ102" s="6"/>
+      <c r="FJL102" s="6"/>
+      <c r="FJN102" s="6"/>
+      <c r="FJP102" s="6"/>
+      <c r="FJR102" s="6"/>
+      <c r="FJT102" s="6"/>
+      <c r="FJV102" s="6"/>
+      <c r="FJX102" s="6"/>
+      <c r="FJZ102" s="6"/>
+      <c r="FKB102" s="6"/>
+      <c r="FKD102" s="6"/>
+      <c r="FKF102" s="6"/>
+      <c r="FKH102" s="6"/>
+      <c r="FKJ102" s="6"/>
+      <c r="FKL102" s="6"/>
+      <c r="FKN102" s="6"/>
+      <c r="FKP102" s="6"/>
+      <c r="FKR102" s="6"/>
+      <c r="FKT102" s="6"/>
+      <c r="FKV102" s="6"/>
+      <c r="FKX102" s="6"/>
+      <c r="FKZ102" s="6"/>
+      <c r="FLB102" s="6"/>
+      <c r="FLD102" s="6"/>
+      <c r="FLF102" s="6"/>
+      <c r="FLH102" s="6"/>
+      <c r="FLJ102" s="6"/>
+      <c r="FLL102" s="6"/>
+      <c r="FLN102" s="6"/>
+      <c r="FLP102" s="6"/>
+      <c r="FLR102" s="6"/>
+      <c r="FLT102" s="6"/>
+      <c r="FLV102" s="6"/>
+      <c r="FLX102" s="6"/>
+      <c r="FLZ102" s="6"/>
+      <c r="FMB102" s="6"/>
+      <c r="FMD102" s="6"/>
+      <c r="FMF102" s="6"/>
+      <c r="FMH102" s="6"/>
+      <c r="FMJ102" s="6"/>
+      <c r="FML102" s="6"/>
+      <c r="FMN102" s="6"/>
+      <c r="FMP102" s="6"/>
+      <c r="FMR102" s="6"/>
+      <c r="FMT102" s="6"/>
+      <c r="FMV102" s="6"/>
+      <c r="FMX102" s="6"/>
+      <c r="FMZ102" s="6"/>
+      <c r="FNB102" s="6"/>
+      <c r="FND102" s="6"/>
+      <c r="FNF102" s="6"/>
+      <c r="FNH102" s="6"/>
+      <c r="FNJ102" s="6"/>
+      <c r="FNL102" s="6"/>
+      <c r="FNN102" s="6"/>
+      <c r="FNP102" s="6"/>
+      <c r="FNR102" s="6"/>
+      <c r="FNT102" s="6"/>
+      <c r="FNV102" s="6"/>
+      <c r="FNX102" s="6"/>
+      <c r="FNZ102" s="6"/>
+      <c r="FOB102" s="6"/>
+      <c r="FOD102" s="6"/>
+      <c r="FOF102" s="6"/>
+      <c r="FOH102" s="6"/>
+      <c r="FOJ102" s="6"/>
+      <c r="FOL102" s="6"/>
+      <c r="FON102" s="6"/>
+      <c r="FOP102" s="6"/>
+      <c r="FOR102" s="6"/>
+      <c r="FOT102" s="6"/>
+      <c r="FOV102" s="6"/>
+      <c r="FOX102" s="6"/>
+      <c r="FOZ102" s="6"/>
+      <c r="FPB102" s="6"/>
+      <c r="FPD102" s="6"/>
+      <c r="FPF102" s="6"/>
+      <c r="FPH102" s="6"/>
+      <c r="FPJ102" s="6"/>
+      <c r="FPL102" s="6"/>
+      <c r="FPN102" s="6"/>
+      <c r="FPP102" s="6"/>
+      <c r="FPR102" s="6"/>
+      <c r="FPT102" s="6"/>
+      <c r="FPV102" s="6"/>
+      <c r="FPX102" s="6"/>
+      <c r="FPZ102" s="6"/>
+      <c r="FQB102" s="6"/>
+      <c r="FQD102" s="6"/>
+      <c r="FQF102" s="6"/>
+      <c r="FQH102" s="6"/>
+      <c r="FQJ102" s="6"/>
+      <c r="FQL102" s="6"/>
+      <c r="FQN102" s="6"/>
+      <c r="FQP102" s="6"/>
+      <c r="FQR102" s="6"/>
+      <c r="FQT102" s="6"/>
+      <c r="FQV102" s="6"/>
+      <c r="FQX102" s="6"/>
+      <c r="FQZ102" s="6"/>
+      <c r="FRB102" s="6"/>
+      <c r="FRD102" s="6"/>
+      <c r="FRF102" s="6"/>
+      <c r="FRH102" s="6"/>
+      <c r="FRJ102" s="6"/>
+      <c r="FRL102" s="6"/>
+      <c r="FRN102" s="6"/>
+      <c r="FRP102" s="6"/>
+      <c r="FRR102" s="6"/>
+      <c r="FRT102" s="6"/>
+      <c r="FRV102" s="6"/>
+      <c r="FRX102" s="6"/>
+      <c r="FRZ102" s="6"/>
+      <c r="FSB102" s="6"/>
+      <c r="FSD102" s="6"/>
+      <c r="FSF102" s="6"/>
+      <c r="FSH102" s="6"/>
+      <c r="FSJ102" s="6"/>
+      <c r="FSL102" s="6"/>
+      <c r="FSN102" s="6"/>
+      <c r="FSP102" s="6"/>
+      <c r="FSR102" s="6"/>
+      <c r="FST102" s="6"/>
+      <c r="FSV102" s="6"/>
+      <c r="FSX102" s="6"/>
+      <c r="FSZ102" s="6"/>
+      <c r="FTB102" s="6"/>
+      <c r="FTD102" s="6"/>
+      <c r="FTF102" s="6"/>
+      <c r="FTH102" s="6"/>
+      <c r="FTJ102" s="6"/>
+      <c r="FTL102" s="6"/>
+      <c r="FTN102" s="6"/>
+      <c r="FTP102" s="6"/>
+      <c r="FTR102" s="6"/>
+      <c r="FTT102" s="6"/>
+      <c r="FTV102" s="6"/>
+      <c r="FTX102" s="6"/>
+      <c r="FTZ102" s="6"/>
+      <c r="FUB102" s="6"/>
+      <c r="FUD102" s="6"/>
+      <c r="FUF102" s="6"/>
+      <c r="FUH102" s="6"/>
+      <c r="FUJ102" s="6"/>
+      <c r="FUL102" s="6"/>
+      <c r="FUN102" s="6"/>
+      <c r="FUP102" s="6"/>
+      <c r="FUR102" s="6"/>
+      <c r="FUT102" s="6"/>
+      <c r="FUV102" s="6"/>
+      <c r="FUX102" s="6"/>
+      <c r="FUZ102" s="6"/>
+      <c r="FVB102" s="6"/>
+      <c r="FVD102" s="6"/>
+      <c r="FVF102" s="6"/>
+      <c r="FVH102" s="6"/>
+      <c r="FVJ102" s="6"/>
+      <c r="FVL102" s="6"/>
+      <c r="FVN102" s="6"/>
+      <c r="FVP102" s="6"/>
+      <c r="FVR102" s="6"/>
+      <c r="FVT102" s="6"/>
+      <c r="FVV102" s="6"/>
+      <c r="FVX102" s="6"/>
+      <c r="FVZ102" s="6"/>
+      <c r="FWB102" s="6"/>
+      <c r="FWD102" s="6"/>
+      <c r="FWF102" s="6"/>
+      <c r="FWH102" s="6"/>
+      <c r="FWJ102" s="6"/>
+      <c r="FWL102" s="6"/>
+      <c r="FWN102" s="6"/>
+      <c r="FWP102" s="6"/>
+      <c r="FWR102" s="6"/>
+      <c r="FWT102" s="6"/>
+      <c r="FWV102" s="6"/>
+      <c r="FWX102" s="6"/>
+      <c r="FWZ102" s="6"/>
+      <c r="FXB102" s="6"/>
+      <c r="FXD102" s="6"/>
+      <c r="FXF102" s="6"/>
+      <c r="FXH102" s="6"/>
+      <c r="FXJ102" s="6"/>
+      <c r="FXL102" s="6"/>
+      <c r="FXN102" s="6"/>
+      <c r="FXP102" s="6"/>
+      <c r="FXR102" s="6"/>
+      <c r="FXT102" s="6"/>
+      <c r="FXV102" s="6"/>
+      <c r="FXX102" s="6"/>
+      <c r="FXZ102" s="6"/>
+      <c r="FYB102" s="6"/>
+      <c r="FYD102" s="6"/>
+      <c r="FYF102" s="6"/>
+      <c r="FYH102" s="6"/>
+      <c r="FYJ102" s="6"/>
+      <c r="FYL102" s="6"/>
+      <c r="FYN102" s="6"/>
+      <c r="FYP102" s="6"/>
+      <c r="FYR102" s="6"/>
+      <c r="FYT102" s="6"/>
+      <c r="FYV102" s="6"/>
+      <c r="FYX102" s="6"/>
+      <c r="FYZ102" s="6"/>
+      <c r="FZB102" s="6"/>
+      <c r="FZD102" s="6"/>
+      <c r="FZF102" s="6"/>
+      <c r="FZH102" s="6"/>
+      <c r="FZJ102" s="6"/>
+      <c r="FZL102" s="6"/>
+      <c r="FZN102" s="6"/>
+      <c r="FZP102" s="6"/>
+      <c r="FZR102" s="6"/>
+      <c r="FZT102" s="6"/>
+      <c r="FZV102" s="6"/>
+      <c r="FZX102" s="6"/>
+      <c r="FZZ102" s="6"/>
+      <c r="GAB102" s="6"/>
+      <c r="GAD102" s="6"/>
+      <c r="GAF102" s="6"/>
+      <c r="GAH102" s="6"/>
+      <c r="GAJ102" s="6"/>
+      <c r="GAL102" s="6"/>
+      <c r="GAN102" s="6"/>
+      <c r="GAP102" s="6"/>
+      <c r="GAR102" s="6"/>
+      <c r="GAT102" s="6"/>
+      <c r="GAV102" s="6"/>
+      <c r="GAX102" s="6"/>
+      <c r="GAZ102" s="6"/>
+      <c r="GBB102" s="6"/>
+      <c r="GBD102" s="6"/>
+      <c r="GBF102" s="6"/>
+      <c r="GBH102" s="6"/>
+      <c r="GBJ102" s="6"/>
+      <c r="GBL102" s="6"/>
+      <c r="GBN102" s="6"/>
+      <c r="GBP102" s="6"/>
+      <c r="GBR102" s="6"/>
+      <c r="GBT102" s="6"/>
+      <c r="GBV102" s="6"/>
+      <c r="GBX102" s="6"/>
+      <c r="GBZ102" s="6"/>
+      <c r="GCB102" s="6"/>
+      <c r="GCD102" s="6"/>
+      <c r="GCF102" s="6"/>
+      <c r="GCH102" s="6"/>
+      <c r="GCJ102" s="6"/>
+      <c r="GCL102" s="6"/>
+      <c r="GCN102" s="6"/>
+      <c r="GCP102" s="6"/>
+      <c r="GCR102" s="6"/>
+      <c r="GCT102" s="6"/>
+      <c r="GCV102" s="6"/>
+      <c r="GCX102" s="6"/>
+      <c r="GCZ102" s="6"/>
+      <c r="GDB102" s="6"/>
+      <c r="GDD102" s="6"/>
+      <c r="GDF102" s="6"/>
+      <c r="GDH102" s="6"/>
+      <c r="GDJ102" s="6"/>
+      <c r="GDL102" s="6"/>
+      <c r="GDN102" s="6"/>
+      <c r="GDP102" s="6"/>
+      <c r="GDR102" s="6"/>
+      <c r="GDT102" s="6"/>
+      <c r="GDV102" s="6"/>
+      <c r="GDX102" s="6"/>
+      <c r="GDZ102" s="6"/>
+      <c r="GEB102" s="6"/>
+      <c r="GED102" s="6"/>
+      <c r="GEF102" s="6"/>
+      <c r="GEH102" s="6"/>
+      <c r="GEJ102" s="6"/>
+      <c r="GEL102" s="6"/>
+      <c r="GEN102" s="6"/>
+      <c r="GEP102" s="6"/>
+      <c r="GER102" s="6"/>
+      <c r="GET102" s="6"/>
+      <c r="GEV102" s="6"/>
+      <c r="GEX102" s="6"/>
+      <c r="GEZ102" s="6"/>
+      <c r="GFB102" s="6"/>
+      <c r="GFD102" s="6"/>
+      <c r="GFF102" s="6"/>
+      <c r="GFH102" s="6"/>
+      <c r="GFJ102" s="6"/>
+      <c r="GFL102" s="6"/>
+      <c r="GFN102" s="6"/>
+      <c r="GFP102" s="6"/>
+      <c r="GFR102" s="6"/>
+      <c r="GFT102" s="6"/>
+      <c r="GFV102" s="6"/>
+      <c r="GFX102" s="6"/>
+      <c r="GFZ102" s="6"/>
+      <c r="GGB102" s="6"/>
+      <c r="GGD102" s="6"/>
+      <c r="GGF102" s="6"/>
+      <c r="GGH102" s="6"/>
+      <c r="GGJ102" s="6"/>
+      <c r="GGL102" s="6"/>
+      <c r="GGN102" s="6"/>
+      <c r="GGP102" s="6"/>
+      <c r="GGR102" s="6"/>
+      <c r="GGT102" s="6"/>
+      <c r="GGV102" s="6"/>
+      <c r="GGX102" s="6"/>
+      <c r="GGZ102" s="6"/>
+      <c r="GHB102" s="6"/>
+      <c r="GHD102" s="6"/>
+      <c r="GHF102" s="6"/>
+      <c r="GHH102" s="6"/>
+      <c r="GHJ102" s="6"/>
+      <c r="GHL102" s="6"/>
+      <c r="GHN102" s="6"/>
+      <c r="GHP102" s="6"/>
+      <c r="GHR102" s="6"/>
+      <c r="GHT102" s="6"/>
+      <c r="GHV102" s="6"/>
+      <c r="GHX102" s="6"/>
+      <c r="GHZ102" s="6"/>
+      <c r="GIB102" s="6"/>
+      <c r="GID102" s="6"/>
+      <c r="GIF102" s="6"/>
+      <c r="GIH102" s="6"/>
+      <c r="GIJ102" s="6"/>
+      <c r="GIL102" s="6"/>
+      <c r="GIN102" s="6"/>
+      <c r="GIP102" s="6"/>
+      <c r="GIR102" s="6"/>
+      <c r="GIT102" s="6"/>
+      <c r="GIV102" s="6"/>
+      <c r="GIX102" s="6"/>
+      <c r="GIZ102" s="6"/>
+      <c r="GJB102" s="6"/>
+      <c r="GJD102" s="6"/>
+      <c r="GJF102" s="6"/>
+      <c r="GJH102" s="6"/>
+      <c r="GJJ102" s="6"/>
+      <c r="GJL102" s="6"/>
+      <c r="GJN102" s="6"/>
+      <c r="GJP102" s="6"/>
+      <c r="GJR102" s="6"/>
+      <c r="GJT102" s="6"/>
+      <c r="GJV102" s="6"/>
+      <c r="GJX102" s="6"/>
+      <c r="GJZ102" s="6"/>
+      <c r="GKB102" s="6"/>
+      <c r="GKD102" s="6"/>
+      <c r="GKF102" s="6"/>
+      <c r="GKH102" s="6"/>
+      <c r="GKJ102" s="6"/>
+      <c r="GKL102" s="6"/>
+      <c r="GKN102" s="6"/>
+      <c r="GKP102" s="6"/>
+      <c r="GKR102" s="6"/>
+      <c r="GKT102" s="6"/>
+      <c r="GKV102" s="6"/>
+      <c r="GKX102" s="6"/>
+      <c r="GKZ102" s="6"/>
+      <c r="GLB102" s="6"/>
+      <c r="GLD102" s="6"/>
+      <c r="GLF102" s="6"/>
+      <c r="GLH102" s="6"/>
+      <c r="GLJ102" s="6"/>
+      <c r="GLL102" s="6"/>
+      <c r="GLN102" s="6"/>
+      <c r="GLP102" s="6"/>
+      <c r="GLR102" s="6"/>
+      <c r="GLT102" s="6"/>
+      <c r="GLV102" s="6"/>
+      <c r="GLX102" s="6"/>
+      <c r="GLZ102" s="6"/>
+      <c r="GMB102" s="6"/>
+      <c r="GMD102" s="6"/>
+      <c r="GMF102" s="6"/>
+      <c r="GMH102" s="6"/>
+      <c r="GMJ102" s="6"/>
+      <c r="GML102" s="6"/>
+      <c r="GMN102" s="6"/>
+      <c r="GMP102" s="6"/>
+      <c r="GMR102" s="6"/>
+      <c r="GMT102" s="6"/>
+      <c r="GMV102" s="6"/>
+      <c r="GMX102" s="6"/>
+      <c r="GMZ102" s="6"/>
+      <c r="GNB102" s="6"/>
+      <c r="GND102" s="6"/>
+      <c r="GNF102" s="6"/>
+      <c r="GNH102" s="6"/>
+      <c r="GNJ102" s="6"/>
+      <c r="GNL102" s="6"/>
+      <c r="GNN102" s="6"/>
+      <c r="GNP102" s="6"/>
+      <c r="GNR102" s="6"/>
+      <c r="GNT102" s="6"/>
+      <c r="GNV102" s="6"/>
+      <c r="GNX102" s="6"/>
+      <c r="GNZ102" s="6"/>
+      <c r="GOB102" s="6"/>
+      <c r="GOD102" s="6"/>
+      <c r="GOF102" s="6"/>
+      <c r="GOH102" s="6"/>
+      <c r="GOJ102" s="6"/>
+      <c r="GOL102" s="6"/>
+      <c r="GON102" s="6"/>
+      <c r="GOP102" s="6"/>
+      <c r="GOR102" s="6"/>
+      <c r="GOT102" s="6"/>
+      <c r="GOV102" s="6"/>
+      <c r="GOX102" s="6"/>
+      <c r="GOZ102" s="6"/>
+      <c r="GPB102" s="6"/>
+      <c r="GPD102" s="6"/>
+      <c r="GPF102" s="6"/>
+      <c r="GPH102" s="6"/>
+      <c r="GPJ102" s="6"/>
+      <c r="GPL102" s="6"/>
+      <c r="GPN102" s="6"/>
+      <c r="GPP102" s="6"/>
+      <c r="GPR102" s="6"/>
+      <c r="GPT102" s="6"/>
+      <c r="GPV102" s="6"/>
+      <c r="GPX102" s="6"/>
+      <c r="GPZ102" s="6"/>
+      <c r="GQB102" s="6"/>
+      <c r="GQD102" s="6"/>
+      <c r="GQF102" s="6"/>
+      <c r="GQH102" s="6"/>
+      <c r="GQJ102" s="6"/>
+      <c r="GQL102" s="6"/>
+      <c r="GQN102" s="6"/>
+      <c r="GQP102" s="6"/>
+      <c r="GQR102" s="6"/>
+      <c r="GQT102" s="6"/>
+      <c r="GQV102" s="6"/>
+      <c r="GQX102" s="6"/>
+      <c r="GQZ102" s="6"/>
+      <c r="GRB102" s="6"/>
+      <c r="GRD102" s="6"/>
+      <c r="GRF102" s="6"/>
+      <c r="GRH102" s="6"/>
+      <c r="GRJ102" s="6"/>
+      <c r="GRL102" s="6"/>
+      <c r="GRN102" s="6"/>
+      <c r="GRP102" s="6"/>
+      <c r="GRR102" s="6"/>
+      <c r="GRT102" s="6"/>
+      <c r="GRV102" s="6"/>
+      <c r="GRX102" s="6"/>
+      <c r="GRZ102" s="6"/>
+      <c r="GSB102" s="6"/>
+      <c r="GSD102" s="6"/>
+      <c r="GSF102" s="6"/>
+      <c r="GSH102" s="6"/>
+      <c r="GSJ102" s="6"/>
+      <c r="GSL102" s="6"/>
+      <c r="GSN102" s="6"/>
+      <c r="GSP102" s="6"/>
+      <c r="GSR102" s="6"/>
+      <c r="GST102" s="6"/>
+      <c r="GSV102" s="6"/>
+      <c r="GSX102" s="6"/>
+      <c r="GSZ102" s="6"/>
+      <c r="GTB102" s="6"/>
+      <c r="GTD102" s="6"/>
+      <c r="GTF102" s="6"/>
+      <c r="GTH102" s="6"/>
+      <c r="GTJ102" s="6"/>
+      <c r="GTL102" s="6"/>
+      <c r="GTN102" s="6"/>
+      <c r="GTP102" s="6"/>
+      <c r="GTR102" s="6"/>
+      <c r="GTT102" s="6"/>
+      <c r="GTV102" s="6"/>
+      <c r="GTX102" s="6"/>
+      <c r="GTZ102" s="6"/>
+      <c r="GUB102" s="6"/>
+      <c r="GUD102" s="6"/>
+      <c r="GUF102" s="6"/>
+      <c r="GUH102" s="6"/>
+      <c r="GUJ102" s="6"/>
+      <c r="GUL102" s="6"/>
+      <c r="GUN102" s="6"/>
+      <c r="GUP102" s="6"/>
+      <c r="GUR102" s="6"/>
+      <c r="GUT102" s="6"/>
+      <c r="GUV102" s="6"/>
+      <c r="GUX102" s="6"/>
+      <c r="GUZ102" s="6"/>
+      <c r="GVB102" s="6"/>
+      <c r="GVD102" s="6"/>
+      <c r="GVF102" s="6"/>
+      <c r="GVH102" s="6"/>
+      <c r="GVJ102" s="6"/>
+      <c r="GVL102" s="6"/>
+      <c r="GVN102" s="6"/>
+      <c r="GVP102" s="6"/>
+      <c r="GVR102" s="6"/>
+      <c r="GVT102" s="6"/>
+      <c r="GVV102" s="6"/>
+      <c r="GVX102" s="6"/>
+      <c r="GVZ102" s="6"/>
+      <c r="GWB102" s="6"/>
+      <c r="GWD102" s="6"/>
+      <c r="GWF102" s="6"/>
+      <c r="GWH102" s="6"/>
+      <c r="GWJ102" s="6"/>
+      <c r="GWL102" s="6"/>
+      <c r="GWN102" s="6"/>
+      <c r="GWP102" s="6"/>
+      <c r="GWR102" s="6"/>
+      <c r="GWT102" s="6"/>
+      <c r="GWV102" s="6"/>
+      <c r="GWX102" s="6"/>
+      <c r="GWZ102" s="6"/>
+      <c r="GXB102" s="6"/>
+      <c r="GXD102" s="6"/>
+      <c r="GXF102" s="6"/>
+      <c r="GXH102" s="6"/>
+      <c r="GXJ102" s="6"/>
+      <c r="GXL102" s="6"/>
+      <c r="GXN102" s="6"/>
+      <c r="GXP102" s="6"/>
+      <c r="GXR102" s="6"/>
+      <c r="GXT102" s="6"/>
+      <c r="GXV102" s="6"/>
+      <c r="GXX102" s="6"/>
+      <c r="GXZ102" s="6"/>
+      <c r="GYB102" s="6"/>
+      <c r="GYD102" s="6"/>
+      <c r="GYF102" s="6"/>
+      <c r="GYH102" s="6"/>
+      <c r="GYJ102" s="6"/>
+      <c r="GYL102" s="6"/>
+      <c r="GYN102" s="6"/>
+      <c r="GYP102" s="6"/>
+      <c r="GYR102" s="6"/>
+      <c r="GYT102" s="6"/>
+      <c r="GYV102" s="6"/>
+      <c r="GYX102" s="6"/>
+      <c r="GYZ102" s="6"/>
+      <c r="GZB102" s="6"/>
+      <c r="GZD102" s="6"/>
+      <c r="GZF102" s="6"/>
+      <c r="GZH102" s="6"/>
+      <c r="GZJ102" s="6"/>
+      <c r="GZL102" s="6"/>
+      <c r="GZN102" s="6"/>
+      <c r="GZP102" s="6"/>
+      <c r="GZR102" s="6"/>
+      <c r="GZT102" s="6"/>
+      <c r="GZV102" s="6"/>
+      <c r="GZX102" s="6"/>
+      <c r="GZZ102" s="6"/>
+      <c r="HAB102" s="6"/>
+      <c r="HAD102" s="6"/>
+      <c r="HAF102" s="6"/>
+      <c r="HAH102" s="6"/>
+      <c r="HAJ102" s="6"/>
+      <c r="HAL102" s="6"/>
+      <c r="HAN102" s="6"/>
+      <c r="HAP102" s="6"/>
+      <c r="HAR102" s="6"/>
+      <c r="HAT102" s="6"/>
+      <c r="HAV102" s="6"/>
+      <c r="HAX102" s="6"/>
+      <c r="HAZ102" s="6"/>
+      <c r="HBB102" s="6"/>
+      <c r="HBD102" s="6"/>
+      <c r="HBF102" s="6"/>
+      <c r="HBH102" s="6"/>
+      <c r="HBJ102" s="6"/>
+      <c r="HBL102" s="6"/>
+      <c r="HBN102" s="6"/>
+      <c r="HBP102" s="6"/>
+      <c r="HBR102" s="6"/>
+      <c r="HBT102" s="6"/>
+      <c r="HBV102" s="6"/>
+      <c r="HBX102" s="6"/>
+      <c r="HBZ102" s="6"/>
+      <c r="HCB102" s="6"/>
+      <c r="HCD102" s="6"/>
+      <c r="HCF102" s="6"/>
+      <c r="HCH102" s="6"/>
+      <c r="HCJ102" s="6"/>
+      <c r="HCL102" s="6"/>
+      <c r="HCN102" s="6"/>
+      <c r="HCP102" s="6"/>
+      <c r="HCR102" s="6"/>
+      <c r="HCT102" s="6"/>
+      <c r="HCV102" s="6"/>
+      <c r="HCX102" s="6"/>
+      <c r="HCZ102" s="6"/>
+      <c r="HDB102" s="6"/>
+      <c r="HDD102" s="6"/>
+      <c r="HDF102" s="6"/>
+      <c r="HDH102" s="6"/>
+      <c r="HDJ102" s="6"/>
+      <c r="HDL102" s="6"/>
+      <c r="HDN102" s="6"/>
+      <c r="HDP102" s="6"/>
+      <c r="HDR102" s="6"/>
+      <c r="HDT102" s="6"/>
+      <c r="HDV102" s="6"/>
+      <c r="HDX102" s="6"/>
+      <c r="HDZ102" s="6"/>
+      <c r="HEB102" s="6"/>
+      <c r="HED102" s="6"/>
+      <c r="HEF102" s="6"/>
+      <c r="HEH102" s="6"/>
+      <c r="HEJ102" s="6"/>
+      <c r="HEL102" s="6"/>
+      <c r="HEN102" s="6"/>
+      <c r="HEP102" s="6"/>
+      <c r="HER102" s="6"/>
+      <c r="HET102" s="6"/>
+      <c r="HEV102" s="6"/>
+      <c r="HEX102" s="6"/>
+      <c r="HEZ102" s="6"/>
+      <c r="HFB102" s="6"/>
+      <c r="HFD102" s="6"/>
+      <c r="HFF102" s="6"/>
+      <c r="HFH102" s="6"/>
+      <c r="HFJ102" s="6"/>
+      <c r="HFL102" s="6"/>
+      <c r="HFN102" s="6"/>
+      <c r="HFP102" s="6"/>
+      <c r="HFR102" s="6"/>
+      <c r="HFT102" s="6"/>
+      <c r="HFV102" s="6"/>
+      <c r="HFX102" s="6"/>
+      <c r="HFZ102" s="6"/>
+      <c r="HGB102" s="6"/>
+      <c r="HGD102" s="6"/>
+      <c r="HGF102" s="6"/>
+      <c r="HGH102" s="6"/>
+      <c r="HGJ102" s="6"/>
+      <c r="HGL102" s="6"/>
+      <c r="HGN102" s="6"/>
+      <c r="HGP102" s="6"/>
+      <c r="HGR102" s="6"/>
+      <c r="HGT102" s="6"/>
+      <c r="HGV102" s="6"/>
+      <c r="HGX102" s="6"/>
+      <c r="HGZ102" s="6"/>
+      <c r="HHB102" s="6"/>
+      <c r="HHD102" s="6"/>
+      <c r="HHF102" s="6"/>
+      <c r="HHH102" s="6"/>
+      <c r="HHJ102" s="6"/>
+      <c r="HHL102" s="6"/>
+      <c r="HHN102" s="6"/>
+      <c r="HHP102" s="6"/>
+      <c r="HHR102" s="6"/>
+      <c r="HHT102" s="6"/>
+      <c r="HHV102" s="6"/>
+      <c r="HHX102" s="6"/>
+      <c r="HHZ102" s="6"/>
+      <c r="HIB102" s="6"/>
+      <c r="HID102" s="6"/>
+      <c r="HIF102" s="6"/>
+      <c r="HIH102" s="6"/>
+      <c r="HIJ102" s="6"/>
+      <c r="HIL102" s="6"/>
+      <c r="HIN102" s="6"/>
+      <c r="HIP102" s="6"/>
+      <c r="HIR102" s="6"/>
+      <c r="HIT102" s="6"/>
+      <c r="HIV102" s="6"/>
+      <c r="HIX102" s="6"/>
+      <c r="HIZ102" s="6"/>
+      <c r="HJB102" s="6"/>
+      <c r="HJD102" s="6"/>
+      <c r="HJF102" s="6"/>
+      <c r="HJH102" s="6"/>
+      <c r="HJJ102" s="6"/>
+      <c r="HJL102" s="6"/>
+      <c r="HJN102" s="6"/>
+      <c r="HJP102" s="6"/>
+      <c r="HJR102" s="6"/>
+      <c r="HJT102" s="6"/>
+      <c r="HJV102" s="6"/>
+      <c r="HJX102" s="6"/>
+      <c r="HJZ102" s="6"/>
+      <c r="HKB102" s="6"/>
+      <c r="HKD102" s="6"/>
+      <c r="HKF102" s="6"/>
+      <c r="HKH102" s="6"/>
+      <c r="HKJ102" s="6"/>
+      <c r="HKL102" s="6"/>
+      <c r="HKN102" s="6"/>
+      <c r="HKP102" s="6"/>
+      <c r="HKR102" s="6"/>
+      <c r="HKT102" s="6"/>
+      <c r="HKV102" s="6"/>
+      <c r="HKX102" s="6"/>
+      <c r="HKZ102" s="6"/>
+      <c r="HLB102" s="6"/>
+      <c r="HLD102" s="6"/>
+      <c r="HLF102" s="6"/>
+      <c r="HLH102" s="6"/>
+      <c r="HLJ102" s="6"/>
+      <c r="HLL102" s="6"/>
+      <c r="HLN102" s="6"/>
+      <c r="HLP102" s="6"/>
+      <c r="HLR102" s="6"/>
+      <c r="HLT102" s="6"/>
+      <c r="HLV102" s="6"/>
+      <c r="HLX102" s="6"/>
+      <c r="HLZ102" s="6"/>
+      <c r="HMB102" s="6"/>
+      <c r="HMD102" s="6"/>
+      <c r="HMF102" s="6"/>
+      <c r="HMH102" s="6"/>
+      <c r="HMJ102" s="6"/>
+      <c r="HML102" s="6"/>
+      <c r="HMN102" s="6"/>
+      <c r="HMP102" s="6"/>
+      <c r="HMR102" s="6"/>
+      <c r="HMT102" s="6"/>
+      <c r="HMV102" s="6"/>
+      <c r="HMX102" s="6"/>
+      <c r="HMZ102" s="6"/>
+      <c r="HNB102" s="6"/>
+      <c r="HND102" s="6"/>
+      <c r="HNF102" s="6"/>
+      <c r="HNH102" s="6"/>
+      <c r="HNJ102" s="6"/>
+      <c r="HNL102" s="6"/>
+      <c r="HNN102" s="6"/>
+      <c r="HNP102" s="6"/>
+      <c r="HNR102" s="6"/>
+      <c r="HNT102" s="6"/>
+      <c r="HNV102" s="6"/>
+      <c r="HNX102" s="6"/>
+      <c r="HNZ102" s="6"/>
+      <c r="HOB102" s="6"/>
+      <c r="HOD102" s="6"/>
+      <c r="HOF102" s="6"/>
+      <c r="HOH102" s="6"/>
+      <c r="HOJ102" s="6"/>
+      <c r="HOL102" s="6"/>
+      <c r="HON102" s="6"/>
+      <c r="HOP102" s="6"/>
+      <c r="HOR102" s="6"/>
+      <c r="HOT102" s="6"/>
+      <c r="HOV102" s="6"/>
+      <c r="HOX102" s="6"/>
+      <c r="HOZ102" s="6"/>
+      <c r="HPB102" s="6"/>
+      <c r="HPD102" s="6"/>
+      <c r="HPF102" s="6"/>
+      <c r="HPH102" s="6"/>
+      <c r="HPJ102" s="6"/>
+      <c r="HPL102" s="6"/>
+      <c r="HPN102" s="6"/>
+      <c r="HPP102" s="6"/>
+      <c r="HPR102" s="6"/>
+      <c r="HPT102" s="6"/>
+      <c r="HPV102" s="6"/>
+      <c r="HPX102" s="6"/>
+      <c r="HPZ102" s="6"/>
+      <c r="HQB102" s="6"/>
+      <c r="HQD102" s="6"/>
+      <c r="HQF102" s="6"/>
+      <c r="HQH102" s="6"/>
+      <c r="HQJ102" s="6"/>
+      <c r="HQL102" s="6"/>
+      <c r="HQN102" s="6"/>
+      <c r="HQP102" s="6"/>
+      <c r="HQR102" s="6"/>
+      <c r="HQT102" s="6"/>
+      <c r="HQV102" s="6"/>
+      <c r="HQX102" s="6"/>
+      <c r="HQZ102" s="6"/>
+      <c r="HRB102" s="6"/>
+      <c r="HRD102" s="6"/>
+      <c r="HRF102" s="6"/>
+      <c r="HRH102" s="6"/>
+      <c r="HRJ102" s="6"/>
+      <c r="HRL102" s="6"/>
+      <c r="HRN102" s="6"/>
+      <c r="HRP102" s="6"/>
+      <c r="HRR102" s="6"/>
+      <c r="HRT102" s="6"/>
+      <c r="HRV102" s="6"/>
+      <c r="HRX102" s="6"/>
+      <c r="HRZ102" s="6"/>
+      <c r="HSB102" s="6"/>
+      <c r="HSD102" s="6"/>
+      <c r="HSF102" s="6"/>
+      <c r="HSH102" s="6"/>
+      <c r="HSJ102" s="6"/>
+      <c r="HSL102" s="6"/>
+      <c r="HSN102" s="6"/>
+      <c r="HSP102" s="6"/>
+      <c r="HSR102" s="6"/>
+      <c r="HST102" s="6"/>
+      <c r="HSV102" s="6"/>
+      <c r="HSX102" s="6"/>
+      <c r="HSZ102" s="6"/>
+      <c r="HTB102" s="6"/>
+      <c r="HTD102" s="6"/>
+      <c r="HTF102" s="6"/>
+      <c r="HTH102" s="6"/>
+      <c r="HTJ102" s="6"/>
+      <c r="HTL102" s="6"/>
+      <c r="HTN102" s="6"/>
+      <c r="HTP102" s="6"/>
+      <c r="HTR102" s="6"/>
+      <c r="HTT102" s="6"/>
+      <c r="HTV102" s="6"/>
+      <c r="HTX102" s="6"/>
+      <c r="HTZ102" s="6"/>
+      <c r="HUB102" s="6"/>
+      <c r="HUD102" s="6"/>
+      <c r="HUF102" s="6"/>
+      <c r="HUH102" s="6"/>
+      <c r="HUJ102" s="6"/>
+      <c r="HUL102" s="6"/>
+      <c r="HUN102" s="6"/>
+      <c r="HUP102" s="6"/>
+      <c r="HUR102" s="6"/>
+      <c r="HUT102" s="6"/>
+      <c r="HUV102" s="6"/>
+      <c r="HUX102" s="6"/>
+      <c r="HUZ102" s="6"/>
+      <c r="HVB102" s="6"/>
+      <c r="HVD102" s="6"/>
+      <c r="HVF102" s="6"/>
+      <c r="HVH102" s="6"/>
+      <c r="HVJ102" s="6"/>
+      <c r="HVL102" s="6"/>
+      <c r="HVN102" s="6"/>
+      <c r="HVP102" s="6"/>
+      <c r="HVR102" s="6"/>
+      <c r="HVT102" s="6"/>
+      <c r="HVV102" s="6"/>
+      <c r="HVX102" s="6"/>
+      <c r="HVZ102" s="6"/>
+      <c r="HWB102" s="6"/>
+      <c r="HWD102" s="6"/>
+      <c r="HWF102" s="6"/>
+      <c r="HWH102" s="6"/>
+      <c r="HWJ102" s="6"/>
+      <c r="HWL102" s="6"/>
+      <c r="HWN102" s="6"/>
+      <c r="HWP102" s="6"/>
+      <c r="HWR102" s="6"/>
+      <c r="HWT102" s="6"/>
+      <c r="HWV102" s="6"/>
+      <c r="HWX102" s="6"/>
+      <c r="HWZ102" s="6"/>
+      <c r="HXB102" s="6"/>
+      <c r="HXD102" s="6"/>
+      <c r="HXF102" s="6"/>
+      <c r="HXH102" s="6"/>
+      <c r="HXJ102" s="6"/>
+      <c r="HXL102" s="6"/>
+      <c r="HXN102" s="6"/>
+      <c r="HXP102" s="6"/>
+      <c r="HXR102" s="6"/>
+      <c r="HXT102" s="6"/>
+      <c r="HXV102" s="6"/>
+      <c r="HXX102" s="6"/>
+      <c r="HXZ102" s="6"/>
+      <c r="HYB102" s="6"/>
+      <c r="HYD102" s="6"/>
+      <c r="HYF102" s="6"/>
+      <c r="HYH102" s="6"/>
+      <c r="HYJ102" s="6"/>
+      <c r="HYL102" s="6"/>
+      <c r="HYN102" s="6"/>
+      <c r="HYP102" s="6"/>
+      <c r="HYR102" s="6"/>
+      <c r="HYT102" s="6"/>
+      <c r="HYV102" s="6"/>
+      <c r="HYX102" s="6"/>
+      <c r="HYZ102" s="6"/>
+      <c r="HZB102" s="6"/>
+      <c r="HZD102" s="6"/>
+      <c r="HZF102" s="6"/>
+      <c r="HZH102" s="6"/>
+      <c r="HZJ102" s="6"/>
+      <c r="HZL102" s="6"/>
+      <c r="HZN102" s="6"/>
+      <c r="HZP102" s="6"/>
+      <c r="HZR102" s="6"/>
+      <c r="HZT102" s="6"/>
+      <c r="HZV102" s="6"/>
+      <c r="HZX102" s="6"/>
+      <c r="HZZ102" s="6"/>
+      <c r="IAB102" s="6"/>
+      <c r="IAD102" s="6"/>
+      <c r="IAF102" s="6"/>
+      <c r="IAH102" s="6"/>
+      <c r="IAJ102" s="6"/>
+      <c r="IAL102" s="6"/>
+      <c r="IAN102" s="6"/>
+      <c r="IAP102" s="6"/>
+      <c r="IAR102" s="6"/>
+      <c r="IAT102" s="6"/>
+      <c r="IAV102" s="6"/>
+      <c r="IAX102" s="6"/>
+      <c r="IAZ102" s="6"/>
+      <c r="IBB102" s="6"/>
+      <c r="IBD102" s="6"/>
+      <c r="IBF102" s="6"/>
+      <c r="IBH102" s="6"/>
+      <c r="IBJ102" s="6"/>
+      <c r="IBL102" s="6"/>
+      <c r="IBN102" s="6"/>
+      <c r="IBP102" s="6"/>
+      <c r="IBR102" s="6"/>
+      <c r="IBT102" s="6"/>
+      <c r="IBV102" s="6"/>
+      <c r="IBX102" s="6"/>
+      <c r="IBZ102" s="6"/>
+      <c r="ICB102" s="6"/>
+      <c r="ICD102" s="6"/>
+      <c r="ICF102" s="6"/>
+      <c r="ICH102" s="6"/>
+      <c r="ICJ102" s="6"/>
+      <c r="ICL102" s="6"/>
+      <c r="ICN102" s="6"/>
+      <c r="ICP102" s="6"/>
+      <c r="ICR102" s="6"/>
+      <c r="ICT102" s="6"/>
+      <c r="ICV102" s="6"/>
+      <c r="ICX102" s="6"/>
+      <c r="ICZ102" s="6"/>
+      <c r="IDB102" s="6"/>
+      <c r="IDD102" s="6"/>
+      <c r="IDF102" s="6"/>
+      <c r="IDH102" s="6"/>
+      <c r="IDJ102" s="6"/>
+      <c r="IDL102" s="6"/>
+      <c r="IDN102" s="6"/>
+      <c r="IDP102" s="6"/>
+      <c r="IDR102" s="6"/>
+      <c r="IDT102" s="6"/>
+      <c r="IDV102" s="6"/>
+      <c r="IDX102" s="6"/>
+      <c r="IDZ102" s="6"/>
+      <c r="IEB102" s="6"/>
+      <c r="IED102" s="6"/>
+      <c r="IEF102" s="6"/>
+      <c r="IEH102" s="6"/>
+      <c r="IEJ102" s="6"/>
+      <c r="IEL102" s="6"/>
+      <c r="IEN102" s="6"/>
+      <c r="IEP102" s="6"/>
+      <c r="IER102" s="6"/>
+      <c r="IET102" s="6"/>
+      <c r="IEV102" s="6"/>
+      <c r="IEX102" s="6"/>
+      <c r="IEZ102" s="6"/>
+      <c r="IFB102" s="6"/>
+      <c r="IFD102" s="6"/>
+      <c r="IFF102" s="6"/>
+      <c r="IFH102" s="6"/>
+      <c r="IFJ102" s="6"/>
+      <c r="IFL102" s="6"/>
+      <c r="IFN102" s="6"/>
+      <c r="IFP102" s="6"/>
+      <c r="IFR102" s="6"/>
+      <c r="IFT102" s="6"/>
+      <c r="IFV102" s="6"/>
+      <c r="IFX102" s="6"/>
+      <c r="IFZ102" s="6"/>
+      <c r="IGB102" s="6"/>
+      <c r="IGD102" s="6"/>
+      <c r="IGF102" s="6"/>
+      <c r="IGH102" s="6"/>
+      <c r="IGJ102" s="6"/>
+      <c r="IGL102" s="6"/>
+      <c r="IGN102" s="6"/>
+      <c r="IGP102" s="6"/>
+      <c r="IGR102" s="6"/>
+      <c r="IGT102" s="6"/>
+      <c r="IGV102" s="6"/>
+      <c r="IGX102" s="6"/>
+      <c r="IGZ102" s="6"/>
+      <c r="IHB102" s="6"/>
+      <c r="IHD102" s="6"/>
+      <c r="IHF102" s="6"/>
+      <c r="IHH102" s="6"/>
+      <c r="IHJ102" s="6"/>
+      <c r="IHL102" s="6"/>
+      <c r="IHN102" s="6"/>
+      <c r="IHP102" s="6"/>
+      <c r="IHR102" s="6"/>
+      <c r="IHT102" s="6"/>
+      <c r="IHV102" s="6"/>
+      <c r="IHX102" s="6"/>
+      <c r="IHZ102" s="6"/>
+      <c r="IIB102" s="6"/>
+      <c r="IID102" s="6"/>
+      <c r="IIF102" s="6"/>
+      <c r="IIH102" s="6"/>
+      <c r="IIJ102" s="6"/>
+      <c r="IIL102" s="6"/>
+      <c r="IIN102" s="6"/>
+      <c r="IIP102" s="6"/>
+      <c r="IIR102" s="6"/>
+      <c r="IIT102" s="6"/>
+      <c r="IIV102" s="6"/>
+      <c r="IIX102" s="6"/>
+      <c r="IIZ102" s="6"/>
+      <c r="IJB102" s="6"/>
+      <c r="IJD102" s="6"/>
+      <c r="IJF102" s="6"/>
+      <c r="IJH102" s="6"/>
+      <c r="IJJ102" s="6"/>
+      <c r="IJL102" s="6"/>
+      <c r="IJN102" s="6"/>
+      <c r="IJP102" s="6"/>
+      <c r="IJR102" s="6"/>
+      <c r="IJT102" s="6"/>
+      <c r="IJV102" s="6"/>
+      <c r="IJX102" s="6"/>
+      <c r="IJZ102" s="6"/>
+      <c r="IKB102" s="6"/>
+      <c r="IKD102" s="6"/>
+      <c r="IKF102" s="6"/>
+      <c r="IKH102" s="6"/>
+      <c r="IKJ102" s="6"/>
+      <c r="IKL102" s="6"/>
+      <c r="IKN102" s="6"/>
+      <c r="IKP102" s="6"/>
+      <c r="IKR102" s="6"/>
+      <c r="IKT102" s="6"/>
+      <c r="IKV102" s="6"/>
+      <c r="IKX102" s="6"/>
+      <c r="IKZ102" s="6"/>
+      <c r="ILB102" s="6"/>
+      <c r="ILD102" s="6"/>
+      <c r="ILF102" s="6"/>
+      <c r="ILH102" s="6"/>
+      <c r="ILJ102" s="6"/>
+      <c r="ILL102" s="6"/>
+      <c r="ILN102" s="6"/>
+      <c r="ILP102" s="6"/>
+      <c r="ILR102" s="6"/>
+      <c r="ILT102" s="6"/>
+      <c r="ILV102" s="6"/>
+      <c r="ILX102" s="6"/>
+      <c r="ILZ102" s="6"/>
+      <c r="IMB102" s="6"/>
+      <c r="IMD102" s="6"/>
+      <c r="IMF102" s="6"/>
+      <c r="IMH102" s="6"/>
+      <c r="IMJ102" s="6"/>
+      <c r="IML102" s="6"/>
+      <c r="IMN102" s="6"/>
+      <c r="IMP102" s="6"/>
+      <c r="IMR102" s="6"/>
+      <c r="IMT102" s="6"/>
+      <c r="IMV102" s="6"/>
+      <c r="IMX102" s="6"/>
+      <c r="IMZ102" s="6"/>
+      <c r="INB102" s="6"/>
+      <c r="IND102" s="6"/>
+      <c r="INF102" s="6"/>
+      <c r="INH102" s="6"/>
+      <c r="INJ102" s="6"/>
+      <c r="INL102" s="6"/>
+      <c r="INN102" s="6"/>
+      <c r="INP102" s="6"/>
+      <c r="INR102" s="6"/>
+      <c r="INT102" s="6"/>
+      <c r="INV102" s="6"/>
+      <c r="INX102" s="6"/>
+      <c r="INZ102" s="6"/>
+      <c r="IOB102" s="6"/>
+      <c r="IOD102" s="6"/>
+      <c r="IOF102" s="6"/>
+      <c r="IOH102" s="6"/>
+      <c r="IOJ102" s="6"/>
+      <c r="IOL102" s="6"/>
+      <c r="ION102" s="6"/>
+      <c r="IOP102" s="6"/>
+      <c r="IOR102" s="6"/>
+      <c r="IOT102" s="6"/>
+      <c r="IOV102" s="6"/>
+      <c r="IOX102" s="6"/>
+      <c r="IOZ102" s="6"/>
+      <c r="IPB102" s="6"/>
+      <c r="IPD102" s="6"/>
+      <c r="IPF102" s="6"/>
+      <c r="IPH102" s="6"/>
+      <c r="IPJ102" s="6"/>
+      <c r="IPL102" s="6"/>
+      <c r="IPN102" s="6"/>
+      <c r="IPP102" s="6"/>
+      <c r="IPR102" s="6"/>
+      <c r="IPT102" s="6"/>
+      <c r="IPV102" s="6"/>
+      <c r="IPX102" s="6"/>
+      <c r="IPZ102" s="6"/>
+      <c r="IQB102" s="6"/>
+      <c r="IQD102" s="6"/>
+      <c r="IQF102" s="6"/>
+      <c r="IQH102" s="6"/>
+      <c r="IQJ102" s="6"/>
+      <c r="IQL102" s="6"/>
+      <c r="IQN102" s="6"/>
+      <c r="IQP102" s="6"/>
+      <c r="IQR102" s="6"/>
+      <c r="IQT102" s="6"/>
+      <c r="IQV102" s="6"/>
+      <c r="IQX102" s="6"/>
+      <c r="IQZ102" s="6"/>
+      <c r="IRB102" s="6"/>
+      <c r="IRD102" s="6"/>
+      <c r="IRF102" s="6"/>
+      <c r="IRH102" s="6"/>
+      <c r="IRJ102" s="6"/>
+      <c r="IRL102" s="6"/>
+      <c r="IRN102" s="6"/>
+      <c r="IRP102" s="6"/>
+      <c r="IRR102" s="6"/>
+      <c r="IRT102" s="6"/>
+      <c r="IRV102" s="6"/>
+      <c r="IRX102" s="6"/>
+      <c r="IRZ102" s="6"/>
+      <c r="ISB102" s="6"/>
+      <c r="ISD102" s="6"/>
+      <c r="ISF102" s="6"/>
+      <c r="ISH102" s="6"/>
+      <c r="ISJ102" s="6"/>
+      <c r="ISL102" s="6"/>
+      <c r="ISN102" s="6"/>
+      <c r="ISP102" s="6"/>
+      <c r="ISR102" s="6"/>
+      <c r="IST102" s="6"/>
+      <c r="ISV102" s="6"/>
+      <c r="ISX102" s="6"/>
+      <c r="ISZ102" s="6"/>
+      <c r="ITB102" s="6"/>
+      <c r="ITD102" s="6"/>
+      <c r="ITF102" s="6"/>
+      <c r="ITH102" s="6"/>
+      <c r="ITJ102" s="6"/>
+      <c r="ITL102" s="6"/>
+      <c r="ITN102" s="6"/>
+      <c r="ITP102" s="6"/>
+      <c r="ITR102" s="6"/>
+      <c r="ITT102" s="6"/>
+      <c r="ITV102" s="6"/>
+      <c r="ITX102" s="6"/>
+      <c r="ITZ102" s="6"/>
+      <c r="IUB102" s="6"/>
+      <c r="IUD102" s="6"/>
+      <c r="IUF102" s="6"/>
+      <c r="IUH102" s="6"/>
+      <c r="IUJ102" s="6"/>
+      <c r="IUL102" s="6"/>
+      <c r="IUN102" s="6"/>
+      <c r="IUP102" s="6"/>
+      <c r="IUR102" s="6"/>
+      <c r="IUT102" s="6"/>
+      <c r="IUV102" s="6"/>
+      <c r="IUX102" s="6"/>
+      <c r="IUZ102" s="6"/>
+      <c r="IVB102" s="6"/>
+      <c r="IVD102" s="6"/>
+      <c r="IVF102" s="6"/>
+      <c r="IVH102" s="6"/>
+      <c r="IVJ102" s="6"/>
+      <c r="IVL102" s="6"/>
+      <c r="IVN102" s="6"/>
+      <c r="IVP102" s="6"/>
+      <c r="IVR102" s="6"/>
+      <c r="IVT102" s="6"/>
+      <c r="IVV102" s="6"/>
+      <c r="IVX102" s="6"/>
+      <c r="IVZ102" s="6"/>
+      <c r="IWB102" s="6"/>
+      <c r="IWD102" s="6"/>
+      <c r="IWF102" s="6"/>
+      <c r="IWH102" s="6"/>
+      <c r="IWJ102" s="6"/>
+      <c r="IWL102" s="6"/>
+      <c r="IWN102" s="6"/>
+      <c r="IWP102" s="6"/>
+      <c r="IWR102" s="6"/>
+      <c r="IWT102" s="6"/>
+      <c r="IWV102" s="6"/>
+      <c r="IWX102" s="6"/>
+      <c r="IWZ102" s="6"/>
+      <c r="IXB102" s="6"/>
+      <c r="IXD102" s="6"/>
+      <c r="IXF102" s="6"/>
+      <c r="IXH102" s="6"/>
+      <c r="IXJ102" s="6"/>
+      <c r="IXL102" s="6"/>
+      <c r="IXN102" s="6"/>
+      <c r="IXP102" s="6"/>
+      <c r="IXR102" s="6"/>
+      <c r="IXT102" s="6"/>
+      <c r="IXV102" s="6"/>
+      <c r="IXX102" s="6"/>
+      <c r="IXZ102" s="6"/>
+      <c r="IYB102" s="6"/>
+      <c r="IYD102" s="6"/>
+      <c r="IYF102" s="6"/>
+      <c r="IYH102" s="6"/>
+      <c r="IYJ102" s="6"/>
+      <c r="IYL102" s="6"/>
+      <c r="IYN102" s="6"/>
+      <c r="IYP102" s="6"/>
+      <c r="IYR102" s="6"/>
+      <c r="IYT102" s="6"/>
+      <c r="IYV102" s="6"/>
+      <c r="IYX102" s="6"/>
+      <c r="IYZ102" s="6"/>
+      <c r="IZB102" s="6"/>
+      <c r="IZD102" s="6"/>
+      <c r="IZF102" s="6"/>
+      <c r="IZH102" s="6"/>
+      <c r="IZJ102" s="6"/>
+      <c r="IZL102" s="6"/>
+      <c r="IZN102" s="6"/>
+      <c r="IZP102" s="6"/>
+      <c r="IZR102" s="6"/>
+      <c r="IZT102" s="6"/>
+      <c r="IZV102" s="6"/>
+      <c r="IZX102" s="6"/>
+      <c r="IZZ102" s="6"/>
+      <c r="JAB102" s="6"/>
+      <c r="JAD102" s="6"/>
+      <c r="JAF102" s="6"/>
+      <c r="JAH102" s="6"/>
+      <c r="JAJ102" s="6"/>
+      <c r="JAL102" s="6"/>
+      <c r="JAN102" s="6"/>
+      <c r="JAP102" s="6"/>
+      <c r="JAR102" s="6"/>
+      <c r="JAT102" s="6"/>
+      <c r="JAV102" s="6"/>
+      <c r="JAX102" s="6"/>
+      <c r="JAZ102" s="6"/>
+      <c r="JBB102" s="6"/>
+      <c r="JBD102" s="6"/>
+      <c r="JBF102" s="6"/>
+      <c r="JBH102" s="6"/>
+      <c r="JBJ102" s="6"/>
+      <c r="JBL102" s="6"/>
+      <c r="JBN102" s="6"/>
+      <c r="JBP102" s="6"/>
+      <c r="JBR102" s="6"/>
+      <c r="JBT102" s="6"/>
+      <c r="JBV102" s="6"/>
+      <c r="JBX102" s="6"/>
+      <c r="JBZ102" s="6"/>
+      <c r="JCB102" s="6"/>
+      <c r="JCD102" s="6"/>
+      <c r="JCF102" s="6"/>
+      <c r="JCH102" s="6"/>
+      <c r="JCJ102" s="6"/>
+      <c r="JCL102" s="6"/>
+      <c r="JCN102" s="6"/>
+      <c r="JCP102" s="6"/>
+      <c r="JCR102" s="6"/>
+      <c r="JCT102" s="6"/>
+      <c r="JCV102" s="6"/>
+      <c r="JCX102" s="6"/>
+      <c r="JCZ102" s="6"/>
+      <c r="JDB102" s="6"/>
+      <c r="JDD102" s="6"/>
+      <c r="JDF102" s="6"/>
+      <c r="JDH102" s="6"/>
+      <c r="JDJ102" s="6"/>
+      <c r="JDL102" s="6"/>
+      <c r="JDN102" s="6"/>
+      <c r="JDP102" s="6"/>
+      <c r="JDR102" s="6"/>
+      <c r="JDT102" s="6"/>
+      <c r="JDV102" s="6"/>
+      <c r="JDX102" s="6"/>
+      <c r="JDZ102" s="6"/>
+      <c r="JEB102" s="6"/>
+      <c r="JED102" s="6"/>
+      <c r="JEF102" s="6"/>
+      <c r="JEH102" s="6"/>
+      <c r="JEJ102" s="6"/>
+      <c r="JEL102" s="6"/>
+      <c r="JEN102" s="6"/>
+      <c r="JEP102" s="6"/>
+      <c r="JER102" s="6"/>
+      <c r="JET102" s="6"/>
+      <c r="JEV102" s="6"/>
+      <c r="JEX102" s="6"/>
+      <c r="JEZ102" s="6"/>
+      <c r="JFB102" s="6"/>
+      <c r="JFD102" s="6"/>
+      <c r="JFF102" s="6"/>
+      <c r="JFH102" s="6"/>
+      <c r="JFJ102" s="6"/>
+      <c r="JFL102" s="6"/>
+      <c r="JFN102" s="6"/>
+      <c r="JFP102" s="6"/>
+      <c r="JFR102" s="6"/>
+      <c r="JFT102" s="6"/>
+      <c r="JFV102" s="6"/>
+      <c r="JFX102" s="6"/>
+      <c r="JFZ102" s="6"/>
+      <c r="JGB102" s="6"/>
+      <c r="JGD102" s="6"/>
+      <c r="JGF102" s="6"/>
+      <c r="JGH102" s="6"/>
+      <c r="JGJ102" s="6"/>
+      <c r="JGL102" s="6"/>
+      <c r="JGN102" s="6"/>
+      <c r="JGP102" s="6"/>
+      <c r="JGR102" s="6"/>
+      <c r="JGT102" s="6"/>
+      <c r="JGV102" s="6"/>
+      <c r="JGX102" s="6"/>
+      <c r="JGZ102" s="6"/>
+      <c r="JHB102" s="6"/>
+      <c r="JHD102" s="6"/>
+      <c r="JHF102" s="6"/>
+      <c r="JHH102" s="6"/>
+      <c r="JHJ102" s="6"/>
+      <c r="JHL102" s="6"/>
+      <c r="JHN102" s="6"/>
+      <c r="JHP102" s="6"/>
+      <c r="JHR102" s="6"/>
+      <c r="JHT102" s="6"/>
+      <c r="JHV102" s="6"/>
+      <c r="JHX102" s="6"/>
+      <c r="JHZ102" s="6"/>
+      <c r="JIB102" s="6"/>
+      <c r="JID102" s="6"/>
+      <c r="JIF102" s="6"/>
+      <c r="JIH102" s="6"/>
+      <c r="JIJ102" s="6"/>
+      <c r="JIL102" s="6"/>
+      <c r="JIN102" s="6"/>
+      <c r="JIP102" s="6"/>
+      <c r="JIR102" s="6"/>
+      <c r="JIT102" s="6"/>
+      <c r="JIV102" s="6"/>
+      <c r="JIX102" s="6"/>
+      <c r="JIZ102" s="6"/>
+      <c r="JJB102" s="6"/>
+      <c r="JJD102" s="6"/>
+      <c r="JJF102" s="6"/>
+      <c r="JJH102" s="6"/>
+      <c r="JJJ102" s="6"/>
+      <c r="JJL102" s="6"/>
+      <c r="JJN102" s="6"/>
+      <c r="JJP102" s="6"/>
+      <c r="JJR102" s="6"/>
+      <c r="JJT102" s="6"/>
+      <c r="JJV102" s="6"/>
+      <c r="JJX102" s="6"/>
+      <c r="JJZ102" s="6"/>
+      <c r="JKB102" s="6"/>
+      <c r="JKD102" s="6"/>
+      <c r="JKF102" s="6"/>
+      <c r="JKH102" s="6"/>
+      <c r="JKJ102" s="6"/>
+      <c r="JKL102" s="6"/>
+      <c r="JKN102" s="6"/>
+      <c r="JKP102" s="6"/>
+      <c r="JKR102" s="6"/>
+      <c r="JKT102" s="6"/>
+      <c r="JKV102" s="6"/>
+      <c r="JKX102" s="6"/>
+      <c r="JKZ102" s="6"/>
+      <c r="JLB102" s="6"/>
+      <c r="JLD102" s="6"/>
+      <c r="JLF102" s="6"/>
+      <c r="JLH102" s="6"/>
+      <c r="JLJ102" s="6"/>
+      <c r="JLL102" s="6"/>
+      <c r="JLN102" s="6"/>
+      <c r="JLP102" s="6"/>
+      <c r="JLR102" s="6"/>
+      <c r="JLT102" s="6"/>
+      <c r="JLV102" s="6"/>
+      <c r="JLX102" s="6"/>
+      <c r="JLZ102" s="6"/>
+      <c r="JMB102" s="6"/>
+      <c r="JMD102" s="6"/>
+      <c r="JMF102" s="6"/>
+      <c r="JMH102" s="6"/>
+      <c r="JMJ102" s="6"/>
+      <c r="JML102" s="6"/>
+      <c r="JMN102" s="6"/>
+      <c r="JMP102" s="6"/>
+      <c r="JMR102" s="6"/>
+      <c r="JMT102" s="6"/>
+      <c r="JMV102" s="6"/>
+      <c r="JMX102" s="6"/>
+      <c r="JMZ102" s="6"/>
+      <c r="JNB102" s="6"/>
+      <c r="JND102" s="6"/>
+      <c r="JNF102" s="6"/>
+      <c r="JNH102" s="6"/>
+      <c r="JNJ102" s="6"/>
+      <c r="JNL102" s="6"/>
+      <c r="JNN102" s="6"/>
+      <c r="JNP102" s="6"/>
+      <c r="JNR102" s="6"/>
+      <c r="JNT102" s="6"/>
+      <c r="JNV102" s="6"/>
+      <c r="JNX102" s="6"/>
+      <c r="JNZ102" s="6"/>
+      <c r="JOB102" s="6"/>
+      <c r="JOD102" s="6"/>
+      <c r="JOF102" s="6"/>
+      <c r="JOH102" s="6"/>
+      <c r="JOJ102" s="6"/>
+      <c r="JOL102" s="6"/>
+      <c r="JON102" s="6"/>
+      <c r="JOP102" s="6"/>
+      <c r="JOR102" s="6"/>
+      <c r="JOT102" s="6"/>
+      <c r="JOV102" s="6"/>
+      <c r="JOX102" s="6"/>
+      <c r="JOZ102" s="6"/>
+      <c r="JPB102" s="6"/>
+      <c r="JPD102" s="6"/>
+      <c r="JPF102" s="6"/>
+      <c r="JPH102" s="6"/>
+      <c r="JPJ102" s="6"/>
+      <c r="JPL102" s="6"/>
+      <c r="JPN102" s="6"/>
+      <c r="JPP102" s="6"/>
+      <c r="JPR102" s="6"/>
+      <c r="JPT102" s="6"/>
+      <c r="JPV102" s="6"/>
+      <c r="JPX102" s="6"/>
+      <c r="JPZ102" s="6"/>
+      <c r="JQB102" s="6"/>
+      <c r="JQD102" s="6"/>
+      <c r="JQF102" s="6"/>
+      <c r="JQH102" s="6"/>
+      <c r="JQJ102" s="6"/>
+      <c r="JQL102" s="6"/>
+      <c r="JQN102" s="6"/>
+      <c r="JQP102" s="6"/>
+      <c r="JQR102" s="6"/>
+      <c r="JQT102" s="6"/>
+      <c r="JQV102" s="6"/>
+      <c r="JQX102" s="6"/>
+      <c r="JQZ102" s="6"/>
+      <c r="JRB102" s="6"/>
+      <c r="JRD102" s="6"/>
+      <c r="JRF102" s="6"/>
+      <c r="JRH102" s="6"/>
+      <c r="JRJ102" s="6"/>
+      <c r="JRL102" s="6"/>
+      <c r="JRN102" s="6"/>
+      <c r="JRP102" s="6"/>
+      <c r="JRR102" s="6"/>
+      <c r="JRT102" s="6"/>
+      <c r="JRV102" s="6"/>
+      <c r="JRX102" s="6"/>
+      <c r="JRZ102" s="6"/>
+      <c r="JSB102" s="6"/>
+      <c r="JSD102" s="6"/>
+      <c r="JSF102" s="6"/>
+      <c r="JSH102" s="6"/>
+      <c r="JSJ102" s="6"/>
+      <c r="JSL102" s="6"/>
+      <c r="JSN102" s="6"/>
+      <c r="JSP102" s="6"/>
+      <c r="JSR102" s="6"/>
+      <c r="JST102" s="6"/>
+      <c r="JSV102" s="6"/>
+      <c r="JSX102" s="6"/>
+      <c r="JSZ102" s="6"/>
+      <c r="JTB102" s="6"/>
+      <c r="JTD102" s="6"/>
+      <c r="JTF102" s="6"/>
+      <c r="JTH102" s="6"/>
+      <c r="JTJ102" s="6"/>
+      <c r="JTL102" s="6"/>
+      <c r="JTN102" s="6"/>
+      <c r="JTP102" s="6"/>
+      <c r="JTR102" s="6"/>
+      <c r="JTT102" s="6"/>
+      <c r="JTV102" s="6"/>
+      <c r="JTX102" s="6"/>
+      <c r="JTZ102" s="6"/>
+      <c r="JUB102" s="6"/>
+      <c r="JUD102" s="6"/>
+      <c r="JUF102" s="6"/>
+      <c r="JUH102" s="6"/>
+      <c r="JUJ102" s="6"/>
+      <c r="JUL102" s="6"/>
+      <c r="JUN102" s="6"/>
+      <c r="JUP102" s="6"/>
+      <c r="JUR102" s="6"/>
+      <c r="JUT102" s="6"/>
+      <c r="JUV102" s="6"/>
+      <c r="JUX102" s="6"/>
+      <c r="JUZ102" s="6"/>
+      <c r="JVB102" s="6"/>
+      <c r="JVD102" s="6"/>
+      <c r="JVF102" s="6"/>
+      <c r="JVH102" s="6"/>
+      <c r="JVJ102" s="6"/>
+      <c r="JVL102" s="6"/>
+      <c r="JVN102" s="6"/>
+      <c r="JVP102" s="6"/>
+      <c r="JVR102" s="6"/>
+      <c r="JVT102" s="6"/>
+      <c r="JVV102" s="6"/>
+      <c r="JVX102" s="6"/>
+      <c r="JVZ102" s="6"/>
+      <c r="JWB102" s="6"/>
+      <c r="JWD102" s="6"/>
+      <c r="JWF102" s="6"/>
+      <c r="JWH102" s="6"/>
+      <c r="JWJ102" s="6"/>
+      <c r="JWL102" s="6"/>
+      <c r="JWN102" s="6"/>
+      <c r="JWP102" s="6"/>
+      <c r="JWR102" s="6"/>
+      <c r="JWT102" s="6"/>
+      <c r="JWV102" s="6"/>
+      <c r="JWX102" s="6"/>
+      <c r="JWZ102" s="6"/>
+      <c r="JXB102" s="6"/>
+      <c r="JXD102" s="6"/>
+      <c r="JXF102" s="6"/>
+      <c r="JXH102" s="6"/>
+      <c r="JXJ102" s="6"/>
+      <c r="JXL102" s="6"/>
+      <c r="JXN102" s="6"/>
+      <c r="JXP102" s="6"/>
+      <c r="JXR102" s="6"/>
+      <c r="JXT102" s="6"/>
+      <c r="JXV102" s="6"/>
+      <c r="JXX102" s="6"/>
+      <c r="JXZ102" s="6"/>
+      <c r="JYB102" s="6"/>
+      <c r="JYD102" s="6"/>
+      <c r="JYF102" s="6"/>
+      <c r="JYH102" s="6"/>
+      <c r="JYJ102" s="6"/>
+      <c r="JYL102" s="6"/>
+      <c r="JYN102" s="6"/>
+      <c r="JYP102" s="6"/>
+      <c r="JYR102" s="6"/>
+      <c r="JYT102" s="6"/>
+      <c r="JYV102" s="6"/>
+      <c r="JYX102" s="6"/>
+      <c r="JYZ102" s="6"/>
+      <c r="JZB102" s="6"/>
+      <c r="JZD102" s="6"/>
+      <c r="JZF102" s="6"/>
+      <c r="JZH102" s="6"/>
+      <c r="JZJ102" s="6"/>
+      <c r="JZL102" s="6"/>
+      <c r="JZN102" s="6"/>
+      <c r="JZP102" s="6"/>
+      <c r="JZR102" s="6"/>
+      <c r="JZT102" s="6"/>
+      <c r="JZV102" s="6"/>
+      <c r="JZX102" s="6"/>
+      <c r="JZZ102" s="6"/>
+      <c r="KAB102" s="6"/>
+      <c r="KAD102" s="6"/>
+      <c r="KAF102" s="6"/>
+      <c r="KAH102" s="6"/>
+      <c r="KAJ102" s="6"/>
+      <c r="KAL102" s="6"/>
+      <c r="KAN102" s="6"/>
+      <c r="KAP102" s="6"/>
+      <c r="KAR102" s="6"/>
+      <c r="KAT102" s="6"/>
+      <c r="KAV102" s="6"/>
+      <c r="KAX102" s="6"/>
+      <c r="KAZ102" s="6"/>
+      <c r="KBB102" s="6"/>
+      <c r="KBD102" s="6"/>
+      <c r="KBF102" s="6"/>
+      <c r="KBH102" s="6"/>
+      <c r="KBJ102" s="6"/>
+      <c r="KBL102" s="6"/>
+      <c r="KBN102" s="6"/>
+      <c r="KBP102" s="6"/>
+      <c r="KBR102" s="6"/>
+      <c r="KBT102" s="6"/>
+      <c r="KBV102" s="6"/>
+      <c r="KBX102" s="6"/>
+      <c r="KBZ102" s="6"/>
+      <c r="KCB102" s="6"/>
+      <c r="KCD102" s="6"/>
+      <c r="KCF102" s="6"/>
+      <c r="KCH102" s="6"/>
+      <c r="KCJ102" s="6"/>
+      <c r="KCL102" s="6"/>
+      <c r="KCN102" s="6"/>
+      <c r="KCP102" s="6"/>
+      <c r="KCR102" s="6"/>
+      <c r="KCT102" s="6"/>
+      <c r="KCV102" s="6"/>
+      <c r="KCX102" s="6"/>
+      <c r="KCZ102" s="6"/>
+      <c r="KDB102" s="6"/>
+      <c r="KDD102" s="6"/>
+      <c r="KDF102" s="6"/>
+      <c r="KDH102" s="6"/>
+      <c r="KDJ102" s="6"/>
+      <c r="KDL102" s="6"/>
+      <c r="KDN102" s="6"/>
+      <c r="KDP102" s="6"/>
+      <c r="KDR102" s="6"/>
+      <c r="KDT102" s="6"/>
+      <c r="KDV102" s="6"/>
+      <c r="KDX102" s="6"/>
+      <c r="KDZ102" s="6"/>
+      <c r="KEB102" s="6"/>
+      <c r="KED102" s="6"/>
+      <c r="KEF102" s="6"/>
+      <c r="KEH102" s="6"/>
+      <c r="KEJ102" s="6"/>
+      <c r="KEL102" s="6"/>
+      <c r="KEN102" s="6"/>
+      <c r="KEP102" s="6"/>
+      <c r="KER102" s="6"/>
+      <c r="KET102" s="6"/>
+      <c r="KEV102" s="6"/>
+      <c r="KEX102" s="6"/>
+      <c r="KEZ102" s="6"/>
+      <c r="KFB102" s="6"/>
+      <c r="KFD102" s="6"/>
+      <c r="KFF102" s="6"/>
+      <c r="KFH102" s="6"/>
+      <c r="KFJ102" s="6"/>
+      <c r="KFL102" s="6"/>
+      <c r="KFN102" s="6"/>
+      <c r="KFP102" s="6"/>
+      <c r="KFR102" s="6"/>
+      <c r="KFT102" s="6"/>
+      <c r="KFV102" s="6"/>
+      <c r="KFX102" s="6"/>
+      <c r="KFZ102" s="6"/>
+      <c r="KGB102" s="6"/>
+      <c r="KGD102" s="6"/>
+      <c r="KGF102" s="6"/>
+      <c r="KGH102" s="6"/>
+      <c r="KGJ102" s="6"/>
+      <c r="KGL102" s="6"/>
+      <c r="KGN102" s="6"/>
+      <c r="KGP102" s="6"/>
+      <c r="KGR102" s="6"/>
+      <c r="KGT102" s="6"/>
+      <c r="KGV102" s="6"/>
+      <c r="KGX102" s="6"/>
+      <c r="KGZ102" s="6"/>
+      <c r="KHB102" s="6"/>
+      <c r="KHD102" s="6"/>
+      <c r="KHF102" s="6"/>
+      <c r="KHH102" s="6"/>
+      <c r="KHJ102" s="6"/>
+      <c r="KHL102" s="6"/>
+      <c r="KHN102" s="6"/>
+      <c r="KHP102" s="6"/>
+      <c r="KHR102" s="6"/>
+      <c r="KHT102" s="6"/>
+      <c r="KHV102" s="6"/>
+      <c r="KHX102" s="6"/>
+      <c r="KHZ102" s="6"/>
+      <c r="KIB102" s="6"/>
+      <c r="KID102" s="6"/>
+      <c r="KIF102" s="6"/>
+      <c r="KIH102" s="6"/>
+      <c r="KIJ102" s="6"/>
+      <c r="KIL102" s="6"/>
+      <c r="KIN102" s="6"/>
+      <c r="KIP102" s="6"/>
+      <c r="KIR102" s="6"/>
+      <c r="KIT102" s="6"/>
+      <c r="KIV102" s="6"/>
+      <c r="KIX102" s="6"/>
+      <c r="KIZ102" s="6"/>
+      <c r="KJB102" s="6"/>
+      <c r="KJD102" s="6"/>
+      <c r="KJF102" s="6"/>
+      <c r="KJH102" s="6"/>
+      <c r="KJJ102" s="6"/>
+      <c r="KJL102" s="6"/>
+      <c r="KJN102" s="6"/>
+      <c r="KJP102" s="6"/>
+      <c r="KJR102" s="6"/>
+      <c r="KJT102" s="6"/>
+      <c r="KJV102" s="6"/>
+      <c r="KJX102" s="6"/>
+      <c r="KJZ102" s="6"/>
+      <c r="KKB102" s="6"/>
+      <c r="KKD102" s="6"/>
+      <c r="KKF102" s="6"/>
+      <c r="KKH102" s="6"/>
+      <c r="KKJ102" s="6"/>
+      <c r="KKL102" s="6"/>
+      <c r="KKN102" s="6"/>
+      <c r="KKP102" s="6"/>
+      <c r="KKR102" s="6"/>
+      <c r="KKT102" s="6"/>
+      <c r="KKV102" s="6"/>
+      <c r="KKX102" s="6"/>
+      <c r="KKZ102" s="6"/>
+      <c r="KLB102" s="6"/>
+      <c r="KLD102" s="6"/>
+      <c r="KLF102" s="6"/>
+      <c r="KLH102" s="6"/>
+      <c r="KLJ102" s="6"/>
+      <c r="KLL102" s="6"/>
+      <c r="KLN102" s="6"/>
+      <c r="KLP102" s="6"/>
+      <c r="KLR102" s="6"/>
+      <c r="KLT102" s="6"/>
+      <c r="KLV102" s="6"/>
+      <c r="KLX102" s="6"/>
+      <c r="KLZ102" s="6"/>
+      <c r="KMB102" s="6"/>
+      <c r="KMD102" s="6"/>
+      <c r="KMF102" s="6"/>
+      <c r="KMH102" s="6"/>
+      <c r="KMJ102" s="6"/>
+      <c r="KML102" s="6"/>
+      <c r="KMN102" s="6"/>
+      <c r="KMP102" s="6"/>
+      <c r="KMR102" s="6"/>
+      <c r="KMT102" s="6"/>
+      <c r="KMV102" s="6"/>
+      <c r="KMX102" s="6"/>
+      <c r="KMZ102" s="6"/>
+      <c r="KNB102" s="6"/>
+      <c r="KND102" s="6"/>
+      <c r="KNF102" s="6"/>
+      <c r="KNH102" s="6"/>
+      <c r="KNJ102" s="6"/>
+      <c r="KNL102" s="6"/>
+      <c r="KNN102" s="6"/>
+      <c r="KNP102" s="6"/>
+      <c r="KNR102" s="6"/>
+      <c r="KNT102" s="6"/>
+      <c r="KNV102" s="6"/>
+      <c r="KNX102" s="6"/>
+      <c r="KNZ102" s="6"/>
+      <c r="KOB102" s="6"/>
+      <c r="KOD102" s="6"/>
+      <c r="KOF102" s="6"/>
+      <c r="KOH102" s="6"/>
+      <c r="KOJ102" s="6"/>
+      <c r="KOL102" s="6"/>
+      <c r="KON102" s="6"/>
+      <c r="KOP102" s="6"/>
+      <c r="KOR102" s="6"/>
+      <c r="KOT102" s="6"/>
+      <c r="KOV102" s="6"/>
+      <c r="KOX102" s="6"/>
+      <c r="KOZ102" s="6"/>
+      <c r="KPB102" s="6"/>
+      <c r="KPD102" s="6"/>
+      <c r="KPF102" s="6"/>
+      <c r="KPH102" s="6"/>
+      <c r="KPJ102" s="6"/>
+      <c r="KPL102" s="6"/>
+      <c r="KPN102" s="6"/>
+      <c r="KPP102" s="6"/>
+      <c r="KPR102" s="6"/>
+      <c r="KPT102" s="6"/>
+      <c r="KPV102" s="6"/>
+      <c r="KPX102" s="6"/>
+      <c r="KPZ102" s="6"/>
+      <c r="KQB102" s="6"/>
+      <c r="KQD102" s="6"/>
+      <c r="KQF102" s="6"/>
+      <c r="KQH102" s="6"/>
+      <c r="KQJ102" s="6"/>
+      <c r="KQL102" s="6"/>
+      <c r="KQN102" s="6"/>
+      <c r="KQP102" s="6"/>
+      <c r="KQR102" s="6"/>
+      <c r="KQT102" s="6"/>
+      <c r="KQV102" s="6"/>
+      <c r="KQX102" s="6"/>
+      <c r="KQZ102" s="6"/>
+      <c r="KRB102" s="6"/>
+      <c r="KRD102" s="6"/>
+      <c r="KRF102" s="6"/>
+      <c r="KRH102" s="6"/>
+      <c r="KRJ102" s="6"/>
+      <c r="KRL102" s="6"/>
+      <c r="KRN102" s="6"/>
+      <c r="KRP102" s="6"/>
+      <c r="KRR102" s="6"/>
+      <c r="KRT102" s="6"/>
+      <c r="KRV102" s="6"/>
+      <c r="KRX102" s="6"/>
+      <c r="KRZ102" s="6"/>
+      <c r="KSB102" s="6"/>
+      <c r="KSD102" s="6"/>
+      <c r="KSF102" s="6"/>
+      <c r="KSH102" s="6"/>
+      <c r="KSJ102" s="6"/>
+      <c r="KSL102" s="6"/>
+      <c r="KSN102" s="6"/>
+      <c r="KSP102" s="6"/>
+      <c r="KSR102" s="6"/>
+      <c r="KST102" s="6"/>
+      <c r="KSV102" s="6"/>
+      <c r="KSX102" s="6"/>
+      <c r="KSZ102" s="6"/>
+      <c r="KTB102" s="6"/>
+      <c r="KTD102" s="6"/>
+      <c r="KTF102" s="6"/>
+      <c r="KTH102" s="6"/>
+      <c r="KTJ102" s="6"/>
+      <c r="KTL102" s="6"/>
+      <c r="KTN102" s="6"/>
+      <c r="KTP102" s="6"/>
+      <c r="KTR102" s="6"/>
+      <c r="KTT102" s="6"/>
+      <c r="KTV102" s="6"/>
+      <c r="KTX102" s="6"/>
+      <c r="KTZ102" s="6"/>
+      <c r="KUB102" s="6"/>
+      <c r="KUD102" s="6"/>
+      <c r="KUF102" s="6"/>
+      <c r="KUH102" s="6"/>
+      <c r="KUJ102" s="6"/>
+      <c r="KUL102" s="6"/>
+      <c r="KUN102" s="6"/>
+      <c r="KUP102" s="6"/>
+      <c r="KUR102" s="6"/>
+      <c r="KUT102" s="6"/>
+      <c r="KUV102" s="6"/>
+      <c r="KUX102" s="6"/>
+      <c r="KUZ102" s="6"/>
+      <c r="KVB102" s="6"/>
+      <c r="KVD102" s="6"/>
+      <c r="KVF102" s="6"/>
+      <c r="KVH102" s="6"/>
+      <c r="KVJ102" s="6"/>
+      <c r="KVL102" s="6"/>
+      <c r="KVN102" s="6"/>
+      <c r="KVP102" s="6"/>
+      <c r="KVR102" s="6"/>
+      <c r="KVT102" s="6"/>
+      <c r="KVV102" s="6"/>
+      <c r="KVX102" s="6"/>
+      <c r="KVZ102" s="6"/>
+      <c r="KWB102" s="6"/>
+      <c r="KWD102" s="6"/>
+      <c r="KWF102" s="6"/>
+      <c r="KWH102" s="6"/>
+      <c r="KWJ102" s="6"/>
+      <c r="KWL102" s="6"/>
+      <c r="KWN102" s="6"/>
+      <c r="KWP102" s="6"/>
+      <c r="KWR102" s="6"/>
+      <c r="KWT102" s="6"/>
+      <c r="KWV102" s="6"/>
+      <c r="KWX102" s="6"/>
+      <c r="KWZ102" s="6"/>
+      <c r="KXB102" s="6"/>
+      <c r="KXD102" s="6"/>
+      <c r="KXF102" s="6"/>
+      <c r="KXH102" s="6"/>
+      <c r="KXJ102" s="6"/>
+      <c r="KXL102" s="6"/>
+      <c r="KXN102" s="6"/>
+      <c r="KXP102" s="6"/>
+      <c r="KXR102" s="6"/>
+      <c r="KXT102" s="6"/>
+      <c r="KXV102" s="6"/>
+      <c r="KXX102" s="6"/>
+      <c r="KXZ102" s="6"/>
+      <c r="KYB102" s="6"/>
+      <c r="KYD102" s="6"/>
+      <c r="KYF102" s="6"/>
+      <c r="KYH102" s="6"/>
+      <c r="KYJ102" s="6"/>
+      <c r="KYL102" s="6"/>
+      <c r="KYN102" s="6"/>
+      <c r="KYP102" s="6"/>
+      <c r="KYR102" s="6"/>
+      <c r="KYT102" s="6"/>
+      <c r="KYV102" s="6"/>
+      <c r="KYX102" s="6"/>
+      <c r="KYZ102" s="6"/>
+      <c r="KZB102" s="6"/>
+      <c r="KZD102" s="6"/>
+      <c r="KZF102" s="6"/>
+      <c r="KZH102" s="6"/>
+      <c r="KZJ102" s="6"/>
+      <c r="KZL102" s="6"/>
+      <c r="KZN102" s="6"/>
+      <c r="KZP102" s="6"/>
+      <c r="KZR102" s="6"/>
+      <c r="KZT102" s="6"/>
+      <c r="KZV102" s="6"/>
+      <c r="KZX102" s="6"/>
+      <c r="KZZ102" s="6"/>
+      <c r="LAB102" s="6"/>
+      <c r="LAD102" s="6"/>
+      <c r="LAF102" s="6"/>
+      <c r="LAH102" s="6"/>
+      <c r="LAJ102" s="6"/>
+      <c r="LAL102" s="6"/>
+      <c r="LAN102" s="6"/>
+      <c r="LAP102" s="6"/>
+      <c r="LAR102" s="6"/>
+      <c r="LAT102" s="6"/>
+      <c r="LAV102" s="6"/>
+      <c r="LAX102" s="6"/>
+      <c r="LAZ102" s="6"/>
+      <c r="LBB102" s="6"/>
+      <c r="LBD102" s="6"/>
+      <c r="LBF102" s="6"/>
+      <c r="LBH102" s="6"/>
+      <c r="LBJ102" s="6"/>
+      <c r="LBL102" s="6"/>
+      <c r="LBN102" s="6"/>
+      <c r="LBP102" s="6"/>
+      <c r="LBR102" s="6"/>
+      <c r="LBT102" s="6"/>
+      <c r="LBV102" s="6"/>
+      <c r="LBX102" s="6"/>
+      <c r="LBZ102" s="6"/>
+      <c r="LCB102" s="6"/>
+      <c r="LCD102" s="6"/>
+      <c r="LCF102" s="6"/>
+      <c r="LCH102" s="6"/>
+      <c r="LCJ102" s="6"/>
+      <c r="LCL102" s="6"/>
+      <c r="LCN102" s="6"/>
+      <c r="LCP102" s="6"/>
+      <c r="LCR102" s="6"/>
+      <c r="LCT102" s="6"/>
+      <c r="LCV102" s="6"/>
+      <c r="LCX102" s="6"/>
+      <c r="LCZ102" s="6"/>
+      <c r="LDB102" s="6"/>
+      <c r="LDD102" s="6"/>
+      <c r="LDF102" s="6"/>
+      <c r="LDH102" s="6"/>
+      <c r="LDJ102" s="6"/>
+      <c r="LDL102" s="6"/>
+      <c r="LDN102" s="6"/>
+      <c r="LDP102" s="6"/>
+      <c r="LDR102" s="6"/>
+      <c r="LDT102" s="6"/>
+      <c r="LDV102" s="6"/>
+      <c r="LDX102" s="6"/>
+      <c r="LDZ102" s="6"/>
+      <c r="LEB102" s="6"/>
+      <c r="LED102" s="6"/>
+      <c r="LEF102" s="6"/>
+      <c r="LEH102" s="6"/>
+      <c r="LEJ102" s="6"/>
+      <c r="LEL102" s="6"/>
+      <c r="LEN102" s="6"/>
+      <c r="LEP102" s="6"/>
+      <c r="LER102" s="6"/>
+      <c r="LET102" s="6"/>
+      <c r="LEV102" s="6"/>
+      <c r="LEX102" s="6"/>
+      <c r="LEZ102" s="6"/>
+      <c r="LFB102" s="6"/>
+      <c r="LFD102" s="6"/>
+      <c r="LFF102" s="6"/>
+      <c r="LFH102" s="6"/>
+      <c r="LFJ102" s="6"/>
+      <c r="LFL102" s="6"/>
+      <c r="LFN102" s="6"/>
+      <c r="LFP102" s="6"/>
+      <c r="LFR102" s="6"/>
+      <c r="LFT102" s="6"/>
+      <c r="LFV102" s="6"/>
+      <c r="LFX102" s="6"/>
+      <c r="LFZ102" s="6"/>
+      <c r="LGB102" s="6"/>
+      <c r="LGD102" s="6"/>
+      <c r="LGF102" s="6"/>
+      <c r="LGH102" s="6"/>
+      <c r="LGJ102" s="6"/>
+      <c r="LGL102" s="6"/>
+      <c r="LGN102" s="6"/>
+      <c r="LGP102" s="6"/>
+      <c r="LGR102" s="6"/>
+      <c r="LGT102" s="6"/>
+      <c r="LGV102" s="6"/>
+      <c r="LGX102" s="6"/>
+      <c r="LGZ102" s="6"/>
+      <c r="LHB102" s="6"/>
+      <c r="LHD102" s="6"/>
+      <c r="LHF102" s="6"/>
+      <c r="LHH102" s="6"/>
+      <c r="LHJ102" s="6"/>
+      <c r="LHL102" s="6"/>
+      <c r="LHN102" s="6"/>
+      <c r="LHP102" s="6"/>
+      <c r="LHR102" s="6"/>
+      <c r="LHT102" s="6"/>
+      <c r="LHV102" s="6"/>
+      <c r="LHX102" s="6"/>
+      <c r="LHZ102" s="6"/>
+      <c r="LIB102" s="6"/>
+      <c r="LID102" s="6"/>
+      <c r="LIF102" s="6"/>
+      <c r="LIH102" s="6"/>
+      <c r="LIJ102" s="6"/>
+      <c r="LIL102" s="6"/>
+      <c r="LIN102" s="6"/>
+      <c r="LIP102" s="6"/>
+      <c r="LIR102" s="6"/>
+      <c r="LIT102" s="6"/>
+      <c r="LIV102" s="6"/>
+      <c r="LIX102" s="6"/>
+      <c r="LIZ102" s="6"/>
+      <c r="LJB102" s="6"/>
+      <c r="LJD102" s="6"/>
+      <c r="LJF102" s="6"/>
+      <c r="LJH102" s="6"/>
+      <c r="LJJ102" s="6"/>
+      <c r="LJL102" s="6"/>
+      <c r="LJN102" s="6"/>
+      <c r="LJP102" s="6"/>
+      <c r="LJR102" s="6"/>
+      <c r="LJT102" s="6"/>
+      <c r="LJV102" s="6"/>
+      <c r="LJX102" s="6"/>
+      <c r="LJZ102" s="6"/>
+      <c r="LKB102" s="6"/>
+      <c r="LKD102" s="6"/>
+      <c r="LKF102" s="6"/>
+      <c r="LKH102" s="6"/>
+      <c r="LKJ102" s="6"/>
+      <c r="LKL102" s="6"/>
+      <c r="LKN102" s="6"/>
+      <c r="LKP102" s="6"/>
+      <c r="LKR102" s="6"/>
+      <c r="LKT102" s="6"/>
+      <c r="LKV102" s="6"/>
+      <c r="LKX102" s="6"/>
+      <c r="LKZ102" s="6"/>
+      <c r="LLB102" s="6"/>
+      <c r="LLD102" s="6"/>
+      <c r="LLF102" s="6"/>
+      <c r="LLH102" s="6"/>
+      <c r="LLJ102" s="6"/>
+      <c r="LLL102" s="6"/>
+      <c r="LLN102" s="6"/>
+      <c r="LLP102" s="6"/>
+      <c r="LLR102" s="6"/>
+      <c r="LLT102" s="6"/>
+      <c r="LLV102" s="6"/>
+      <c r="LLX102" s="6"/>
+      <c r="LLZ102" s="6"/>
+      <c r="LMB102" s="6"/>
+      <c r="LMD102" s="6"/>
+      <c r="LMF102" s="6"/>
+      <c r="LMH102" s="6"/>
+      <c r="LMJ102" s="6"/>
+      <c r="LML102" s="6"/>
+      <c r="LMN102" s="6"/>
+      <c r="LMP102" s="6"/>
+      <c r="LMR102" s="6"/>
+      <c r="LMT102" s="6"/>
+      <c r="LMV102" s="6"/>
+      <c r="LMX102" s="6"/>
+      <c r="LMZ102" s="6"/>
+      <c r="LNB102" s="6"/>
+      <c r="LND102" s="6"/>
+      <c r="LNF102" s="6"/>
+      <c r="LNH102" s="6"/>
+      <c r="LNJ102" s="6"/>
+      <c r="LNL102" s="6"/>
+      <c r="LNN102" s="6"/>
+      <c r="LNP102" s="6"/>
+      <c r="LNR102" s="6"/>
+      <c r="LNT102" s="6"/>
+      <c r="LNV102" s="6"/>
+      <c r="LNX102" s="6"/>
+      <c r="LNZ102" s="6"/>
+      <c r="LOB102" s="6"/>
+      <c r="LOD102" s="6"/>
+      <c r="LOF102" s="6"/>
+      <c r="LOH102" s="6"/>
+      <c r="LOJ102" s="6"/>
+      <c r="LOL102" s="6"/>
+      <c r="LON102" s="6"/>
+      <c r="LOP102" s="6"/>
+      <c r="LOR102" s="6"/>
+      <c r="LOT102" s="6"/>
+      <c r="LOV102" s="6"/>
+      <c r="LOX102" s="6"/>
+      <c r="LOZ102" s="6"/>
+      <c r="LPB102" s="6"/>
+      <c r="LPD102" s="6"/>
+      <c r="LPF102" s="6"/>
+      <c r="LPH102" s="6"/>
+      <c r="LPJ102" s="6"/>
+      <c r="LPL102" s="6"/>
+      <c r="LPN102" s="6"/>
+      <c r="LPP102" s="6"/>
+      <c r="LPR102" s="6"/>
+      <c r="LPT102" s="6"/>
+      <c r="LPV102" s="6"/>
+      <c r="LPX102" s="6"/>
+      <c r="LPZ102" s="6"/>
+      <c r="LQB102" s="6"/>
+      <c r="LQD102" s="6"/>
+      <c r="LQF102" s="6"/>
+      <c r="LQH102" s="6"/>
+      <c r="LQJ102" s="6"/>
+      <c r="LQL102" s="6"/>
+      <c r="LQN102" s="6"/>
+      <c r="LQP102" s="6"/>
+      <c r="LQR102" s="6"/>
+      <c r="LQT102" s="6"/>
+      <c r="LQV102" s="6"/>
+      <c r="LQX102" s="6"/>
+      <c r="LQZ102" s="6"/>
+      <c r="LRB102" s="6"/>
+      <c r="LRD102" s="6"/>
+      <c r="LRF102" s="6"/>
+      <c r="LRH102" s="6"/>
+      <c r="LRJ102" s="6"/>
+      <c r="LRL102" s="6"/>
+      <c r="LRN102" s="6"/>
+      <c r="LRP102" s="6"/>
+      <c r="LRR102" s="6"/>
+      <c r="LRT102" s="6"/>
+      <c r="LRV102" s="6"/>
+      <c r="LRX102" s="6"/>
+      <c r="LRZ102" s="6"/>
+      <c r="LSB102" s="6"/>
+      <c r="LSD102" s="6"/>
+      <c r="LSF102" s="6"/>
+      <c r="LSH102" s="6"/>
+      <c r="LSJ102" s="6"/>
+      <c r="LSL102" s="6"/>
+      <c r="LSN102" s="6"/>
+      <c r="LSP102" s="6"/>
+      <c r="LSR102" s="6"/>
+      <c r="LST102" s="6"/>
+      <c r="LSV102" s="6"/>
+      <c r="LSX102" s="6"/>
+      <c r="LSZ102" s="6"/>
+      <c r="LTB102" s="6"/>
+      <c r="LTD102" s="6"/>
+      <c r="LTF102" s="6"/>
+      <c r="LTH102" s="6"/>
+      <c r="LTJ102" s="6"/>
+      <c r="LTL102" s="6"/>
+      <c r="LTN102" s="6"/>
+      <c r="LTP102" s="6"/>
+      <c r="LTR102" s="6"/>
+      <c r="LTT102" s="6"/>
+      <c r="LTV102" s="6"/>
+      <c r="LTX102" s="6"/>
+      <c r="LTZ102" s="6"/>
+      <c r="LUB102" s="6"/>
+      <c r="LUD102" s="6"/>
+      <c r="LUF102" s="6"/>
+      <c r="LUH102" s="6"/>
+      <c r="LUJ102" s="6"/>
+      <c r="LUL102" s="6"/>
+      <c r="LUN102" s="6"/>
+      <c r="LUP102" s="6"/>
+      <c r="LUR102" s="6"/>
+      <c r="LUT102" s="6"/>
+      <c r="LUV102" s="6"/>
+      <c r="LUX102" s="6"/>
+      <c r="LUZ102" s="6"/>
+      <c r="LVB102" s="6"/>
+      <c r="LVD102" s="6"/>
+      <c r="LVF102" s="6"/>
+      <c r="LVH102" s="6"/>
+      <c r="LVJ102" s="6"/>
+      <c r="LVL102" s="6"/>
+      <c r="LVN102" s="6"/>
+      <c r="LVP102" s="6"/>
+      <c r="LVR102" s="6"/>
+      <c r="LVT102" s="6"/>
+      <c r="LVV102" s="6"/>
+      <c r="LVX102" s="6"/>
+      <c r="LVZ102" s="6"/>
+      <c r="LWB102" s="6"/>
+      <c r="LWD102" s="6"/>
+      <c r="LWF102" s="6"/>
+      <c r="LWH102" s="6"/>
+      <c r="LWJ102" s="6"/>
+      <c r="LWL102" s="6"/>
+      <c r="LWN102" s="6"/>
+      <c r="LWP102" s="6"/>
+      <c r="LWR102" s="6"/>
+      <c r="LWT102" s="6"/>
+      <c r="LWV102" s="6"/>
+      <c r="LWX102" s="6"/>
+      <c r="LWZ102" s="6"/>
+      <c r="LXB102" s="6"/>
+      <c r="LXD102" s="6"/>
+      <c r="LXF102" s="6"/>
+      <c r="LXH102" s="6"/>
+      <c r="LXJ102" s="6"/>
+      <c r="LXL102" s="6"/>
+      <c r="LXN102" s="6"/>
+      <c r="LXP102" s="6"/>
+      <c r="LXR102" s="6"/>
+      <c r="LXT102" s="6"/>
+      <c r="LXV102" s="6"/>
+      <c r="LXX102" s="6"/>
+      <c r="LXZ102" s="6"/>
+      <c r="LYB102" s="6"/>
+      <c r="LYD102" s="6"/>
+      <c r="LYF102" s="6"/>
+      <c r="LYH102" s="6"/>
+      <c r="LYJ102" s="6"/>
+      <c r="LYL102" s="6"/>
+      <c r="LYN102" s="6"/>
+      <c r="LYP102" s="6"/>
+      <c r="LYR102" s="6"/>
+      <c r="LYT102" s="6"/>
+      <c r="LYV102" s="6"/>
+      <c r="LYX102" s="6"/>
+      <c r="LYZ102" s="6"/>
+      <c r="LZB102" s="6"/>
+      <c r="LZD102" s="6"/>
+      <c r="LZF102" s="6"/>
+      <c r="LZH102" s="6"/>
+      <c r="LZJ102" s="6"/>
+      <c r="LZL102" s="6"/>
+      <c r="LZN102" s="6"/>
+      <c r="LZP102" s="6"/>
+      <c r="LZR102" s="6"/>
+      <c r="LZT102" s="6"/>
+      <c r="LZV102" s="6"/>
+      <c r="LZX102" s="6"/>
+      <c r="LZZ102" s="6"/>
+      <c r="MAB102" s="6"/>
+      <c r="MAD102" s="6"/>
+      <c r="MAF102" s="6"/>
+      <c r="MAH102" s="6"/>
+      <c r="MAJ102" s="6"/>
+      <c r="MAL102" s="6"/>
+      <c r="MAN102" s="6"/>
+      <c r="MAP102" s="6"/>
+      <c r="MAR102" s="6"/>
+      <c r="MAT102" s="6"/>
+      <c r="MAV102" s="6"/>
+      <c r="MAX102" s="6"/>
+      <c r="MAZ102" s="6"/>
+      <c r="MBB102" s="6"/>
+      <c r="MBD102" s="6"/>
+      <c r="MBF102" s="6"/>
+      <c r="MBH102" s="6"/>
+      <c r="MBJ102" s="6"/>
+      <c r="MBL102" s="6"/>
+      <c r="MBN102" s="6"/>
+      <c r="MBP102" s="6"/>
+      <c r="MBR102" s="6"/>
+      <c r="MBT102" s="6"/>
+      <c r="MBV102" s="6"/>
+      <c r="MBX102" s="6"/>
+      <c r="MBZ102" s="6"/>
+      <c r="MCB102" s="6"/>
+      <c r="MCD102" s="6"/>
+      <c r="MCF102" s="6"/>
+      <c r="MCH102" s="6"/>
+      <c r="MCJ102" s="6"/>
+      <c r="MCL102" s="6"/>
+      <c r="MCN102" s="6"/>
+      <c r="MCP102" s="6"/>
+      <c r="MCR102" s="6"/>
+      <c r="MCT102" s="6"/>
+      <c r="MCV102" s="6"/>
+      <c r="MCX102" s="6"/>
+      <c r="MCZ102" s="6"/>
+      <c r="MDB102" s="6"/>
+      <c r="MDD102" s="6"/>
+      <c r="MDF102" s="6"/>
+      <c r="MDH102" s="6"/>
+      <c r="MDJ102" s="6"/>
+      <c r="MDL102" s="6"/>
+      <c r="MDN102" s="6"/>
+      <c r="MDP102" s="6"/>
+      <c r="MDR102" s="6"/>
+      <c r="MDT102" s="6"/>
+      <c r="MDV102" s="6"/>
+      <c r="MDX102" s="6"/>
+      <c r="MDZ102" s="6"/>
+      <c r="MEB102" s="6"/>
+      <c r="MED102" s="6"/>
+      <c r="MEF102" s="6"/>
+      <c r="MEH102" s="6"/>
+      <c r="MEJ102" s="6"/>
+      <c r="MEL102" s="6"/>
+      <c r="MEN102" s="6"/>
+      <c r="MEP102" s="6"/>
+      <c r="MER102" s="6"/>
+      <c r="MET102" s="6"/>
+      <c r="MEV102" s="6"/>
+      <c r="MEX102" s="6"/>
+      <c r="MEZ102" s="6"/>
+      <c r="MFB102" s="6"/>
+      <c r="MFD102" s="6"/>
+      <c r="MFF102" s="6"/>
+      <c r="MFH102" s="6"/>
+      <c r="MFJ102" s="6"/>
+      <c r="MFL102" s="6"/>
+      <c r="MFN102" s="6"/>
+      <c r="MFP102" s="6"/>
+      <c r="MFR102" s="6"/>
+      <c r="MFT102" s="6"/>
+      <c r="MFV102" s="6"/>
+      <c r="MFX102" s="6"/>
+      <c r="MFZ102" s="6"/>
+      <c r="MGB102" s="6"/>
+      <c r="MGD102" s="6"/>
+      <c r="MGF102" s="6"/>
+      <c r="MGH102" s="6"/>
+      <c r="MGJ102" s="6"/>
+      <c r="MGL102" s="6"/>
+      <c r="MGN102" s="6"/>
+      <c r="MGP102" s="6"/>
+      <c r="MGR102" s="6"/>
+      <c r="MGT102" s="6"/>
+      <c r="MGV102" s="6"/>
+      <c r="MGX102" s="6"/>
+      <c r="MGZ102" s="6"/>
+      <c r="MHB102" s="6"/>
+      <c r="MHD102" s="6"/>
+      <c r="MHF102" s="6"/>
+      <c r="MHH102" s="6"/>
+      <c r="MHJ102" s="6"/>
+      <c r="MHL102" s="6"/>
+      <c r="MHN102" s="6"/>
+      <c r="MHP102" s="6"/>
+      <c r="MHR102" s="6"/>
+      <c r="MHT102" s="6"/>
+      <c r="MHV102" s="6"/>
+      <c r="MHX102" s="6"/>
+      <c r="MHZ102" s="6"/>
+      <c r="MIB102" s="6"/>
+      <c r="MID102" s="6"/>
+      <c r="MIF102" s="6"/>
+      <c r="MIH102" s="6"/>
+      <c r="MIJ102" s="6"/>
+      <c r="MIL102" s="6"/>
+      <c r="MIN102" s="6"/>
+      <c r="MIP102" s="6"/>
+      <c r="MIR102" s="6"/>
+      <c r="MIT102" s="6"/>
+      <c r="MIV102" s="6"/>
+      <c r="MIX102" s="6"/>
+      <c r="MIZ102" s="6"/>
+      <c r="MJB102" s="6"/>
+      <c r="MJD102" s="6"/>
+      <c r="MJF102" s="6"/>
+      <c r="MJH102" s="6"/>
+      <c r="MJJ102" s="6"/>
+      <c r="MJL102" s="6"/>
+      <c r="MJN102" s="6"/>
+      <c r="MJP102" s="6"/>
+      <c r="MJR102" s="6"/>
+      <c r="MJT102" s="6"/>
+      <c r="MJV102" s="6"/>
+      <c r="MJX102" s="6"/>
+      <c r="MJZ102" s="6"/>
+      <c r="MKB102" s="6"/>
+      <c r="MKD102" s="6"/>
+      <c r="MKF102" s="6"/>
+      <c r="MKH102" s="6"/>
+      <c r="MKJ102" s="6"/>
+      <c r="MKL102" s="6"/>
+      <c r="MKN102" s="6"/>
+      <c r="MKP102" s="6"/>
+      <c r="MKR102" s="6"/>
+      <c r="MKT102" s="6"/>
+      <c r="MKV102" s="6"/>
+      <c r="MKX102" s="6"/>
+      <c r="MKZ102" s="6"/>
+      <c r="MLB102" s="6"/>
+      <c r="MLD102" s="6"/>
+      <c r="MLF102" s="6"/>
+      <c r="MLH102" s="6"/>
+      <c r="MLJ102" s="6"/>
+      <c r="MLL102" s="6"/>
+      <c r="MLN102" s="6"/>
+      <c r="MLP102" s="6"/>
+      <c r="MLR102" s="6"/>
+      <c r="MLT102" s="6"/>
+      <c r="MLV102" s="6"/>
+      <c r="MLX102" s="6"/>
+      <c r="MLZ102" s="6"/>
+      <c r="MMB102" s="6"/>
+      <c r="MMD102" s="6"/>
+      <c r="MMF102" s="6"/>
+      <c r="MMH102" s="6"/>
+      <c r="MMJ102" s="6"/>
+      <c r="MML102" s="6"/>
+      <c r="MMN102" s="6"/>
+      <c r="MMP102" s="6"/>
+      <c r="MMR102" s="6"/>
+      <c r="MMT102" s="6"/>
+      <c r="MMV102" s="6"/>
+      <c r="MMX102" s="6"/>
+      <c r="MMZ102" s="6"/>
+      <c r="MNB102" s="6"/>
+      <c r="MND102" s="6"/>
+      <c r="MNF102" s="6"/>
+      <c r="MNH102" s="6"/>
+      <c r="MNJ102" s="6"/>
+      <c r="MNL102" s="6"/>
+      <c r="MNN102" s="6"/>
+      <c r="MNP102" s="6"/>
+      <c r="MNR102" s="6"/>
+      <c r="MNT102" s="6"/>
+      <c r="MNV102" s="6"/>
+      <c r="MNX102" s="6"/>
+      <c r="MNZ102" s="6"/>
+      <c r="MOB102" s="6"/>
+      <c r="MOD102" s="6"/>
+      <c r="MOF102" s="6"/>
+      <c r="MOH102" s="6"/>
+      <c r="MOJ102" s="6"/>
+      <c r="MOL102" s="6"/>
+      <c r="MON102" s="6"/>
+      <c r="MOP102" s="6"/>
+      <c r="MOR102" s="6"/>
+      <c r="MOT102" s="6"/>
+      <c r="MOV102" s="6"/>
+      <c r="MOX102" s="6"/>
+      <c r="MOZ102" s="6"/>
+      <c r="MPB102" s="6"/>
+      <c r="MPD102" s="6"/>
+      <c r="MPF102" s="6"/>
+      <c r="MPH102" s="6"/>
+      <c r="MPJ102" s="6"/>
+      <c r="MPL102" s="6"/>
+      <c r="MPN102" s="6"/>
+      <c r="MPP102" s="6"/>
+      <c r="MPR102" s="6"/>
+      <c r="MPT102" s="6"/>
+      <c r="MPV102" s="6"/>
+      <c r="MPX102" s="6"/>
+      <c r="MPZ102" s="6"/>
+      <c r="MQB102" s="6"/>
+      <c r="MQD102" s="6"/>
+      <c r="MQF102" s="6"/>
+      <c r="MQH102" s="6"/>
+      <c r="MQJ102" s="6"/>
+      <c r="MQL102" s="6"/>
+      <c r="MQN102" s="6"/>
+      <c r="MQP102" s="6"/>
+      <c r="MQR102" s="6"/>
+      <c r="MQT102" s="6"/>
+      <c r="MQV102" s="6"/>
+      <c r="MQX102" s="6"/>
+      <c r="MQZ102" s="6"/>
+      <c r="MRB102" s="6"/>
+      <c r="MRD102" s="6"/>
+      <c r="MRF102" s="6"/>
+      <c r="MRH102" s="6"/>
+      <c r="MRJ102" s="6"/>
+      <c r="MRL102" s="6"/>
+      <c r="MRN102" s="6"/>
+      <c r="MRP102" s="6"/>
+      <c r="MRR102" s="6"/>
+      <c r="MRT102" s="6"/>
+      <c r="MRV102" s="6"/>
+      <c r="MRX102" s="6"/>
+      <c r="MRZ102" s="6"/>
+      <c r="MSB102" s="6"/>
+      <c r="MSD102" s="6"/>
+      <c r="MSF102" s="6"/>
+      <c r="MSH102" s="6"/>
+      <c r="MSJ102" s="6"/>
+      <c r="MSL102" s="6"/>
+      <c r="MSN102" s="6"/>
+      <c r="MSP102" s="6"/>
+      <c r="MSR102" s="6"/>
+      <c r="MST102" s="6"/>
+      <c r="MSV102" s="6"/>
+      <c r="MSX102" s="6"/>
+      <c r="MSZ102" s="6"/>
+      <c r="MTB102" s="6"/>
+      <c r="MTD102" s="6"/>
+      <c r="MTF102" s="6"/>
+      <c r="MTH102" s="6"/>
+      <c r="MTJ102" s="6"/>
+      <c r="MTL102" s="6"/>
+      <c r="MTN102" s="6"/>
+      <c r="MTP102" s="6"/>
+      <c r="MTR102" s="6"/>
+      <c r="MTT102" s="6"/>
+      <c r="MTV102" s="6"/>
+      <c r="MTX102" s="6"/>
+      <c r="MTZ102" s="6"/>
+      <c r="MUB102" s="6"/>
+      <c r="MUD102" s="6"/>
+      <c r="MUF102" s="6"/>
+      <c r="MUH102" s="6"/>
+      <c r="MUJ102" s="6"/>
+      <c r="MUL102" s="6"/>
+      <c r="MUN102" s="6"/>
+      <c r="MUP102" s="6"/>
+      <c r="MUR102" s="6"/>
+      <c r="MUT102" s="6"/>
+      <c r="MUV102" s="6"/>
+      <c r="MUX102" s="6"/>
+      <c r="MUZ102" s="6"/>
+      <c r="MVB102" s="6"/>
+      <c r="MVD102" s="6"/>
+      <c r="MVF102" s="6"/>
+      <c r="MVH102" s="6"/>
+      <c r="MVJ102" s="6"/>
+      <c r="MVL102" s="6"/>
+      <c r="MVN102" s="6"/>
+      <c r="MVP102" s="6"/>
+      <c r="MVR102" s="6"/>
+      <c r="MVT102" s="6"/>
+      <c r="MVV102" s="6"/>
+      <c r="MVX102" s="6"/>
+      <c r="MVZ102" s="6"/>
+      <c r="MWB102" s="6"/>
+      <c r="MWD102" s="6"/>
+      <c r="MWF102" s="6"/>
+      <c r="MWH102" s="6"/>
+      <c r="MWJ102" s="6"/>
+      <c r="MWL102" s="6"/>
+      <c r="MWN102" s="6"/>
+      <c r="MWP102" s="6"/>
+      <c r="MWR102" s="6"/>
+      <c r="MWT102" s="6"/>
+      <c r="MWV102" s="6"/>
+      <c r="MWX102" s="6"/>
+      <c r="MWZ102" s="6"/>
+      <c r="MXB102" s="6"/>
+      <c r="MXD102" s="6"/>
+      <c r="MXF102" s="6"/>
+      <c r="MXH102" s="6"/>
+      <c r="MXJ102" s="6"/>
+      <c r="MXL102" s="6"/>
+      <c r="MXN102" s="6"/>
+      <c r="MXP102" s="6"/>
+      <c r="MXR102" s="6"/>
+      <c r="MXT102" s="6"/>
+      <c r="MXV102" s="6"/>
+      <c r="MXX102" s="6"/>
+      <c r="MXZ102" s="6"/>
+      <c r="MYB102" s="6"/>
+      <c r="MYD102" s="6"/>
+      <c r="MYF102" s="6"/>
+      <c r="MYH102" s="6"/>
+      <c r="MYJ102" s="6"/>
+      <c r="MYL102" s="6"/>
+      <c r="MYN102" s="6"/>
+      <c r="MYP102" s="6"/>
+      <c r="MYR102" s="6"/>
+      <c r="MYT102" s="6"/>
+      <c r="MYV102" s="6"/>
+      <c r="MYX102" s="6"/>
+      <c r="MYZ102" s="6"/>
+      <c r="MZB102" s="6"/>
+      <c r="MZD102" s="6"/>
+      <c r="MZF102" s="6"/>
+      <c r="MZH102" s="6"/>
+      <c r="MZJ102" s="6"/>
+      <c r="MZL102" s="6"/>
+      <c r="MZN102" s="6"/>
+      <c r="MZP102" s="6"/>
+      <c r="MZR102" s="6"/>
+      <c r="MZT102" s="6"/>
+      <c r="MZV102" s="6"/>
+      <c r="MZX102" s="6"/>
+      <c r="MZZ102" s="6"/>
+      <c r="NAB102" s="6"/>
+      <c r="NAD102" s="6"/>
+      <c r="NAF102" s="6"/>
+      <c r="NAH102" s="6"/>
+      <c r="NAJ102" s="6"/>
+      <c r="NAL102" s="6"/>
+      <c r="NAN102" s="6"/>
+      <c r="NAP102" s="6"/>
+      <c r="NAR102" s="6"/>
+      <c r="NAT102" s="6"/>
+      <c r="NAV102" s="6"/>
+      <c r="NAX102" s="6"/>
+      <c r="NAZ102" s="6"/>
+      <c r="NBB102" s="6"/>
+      <c r="NBD102" s="6"/>
+      <c r="NBF102" s="6"/>
+      <c r="NBH102" s="6"/>
+      <c r="NBJ102" s="6"/>
+      <c r="NBL102" s="6"/>
+      <c r="NBN102" s="6"/>
+      <c r="NBP102" s="6"/>
+      <c r="NBR102" s="6"/>
+      <c r="NBT102" s="6"/>
+      <c r="NBV102" s="6"/>
+      <c r="NBX102" s="6"/>
+      <c r="NBZ102" s="6"/>
+      <c r="NCB102" s="6"/>
+      <c r="NCD102" s="6"/>
+      <c r="NCF102" s="6"/>
+      <c r="NCH102" s="6"/>
+      <c r="NCJ102" s="6"/>
+      <c r="NCL102" s="6"/>
+      <c r="NCN102" s="6"/>
+      <c r="NCP102" s="6"/>
+      <c r="NCR102" s="6"/>
+      <c r="NCT102" s="6"/>
+      <c r="NCV102" s="6"/>
+      <c r="NCX102" s="6"/>
+      <c r="NCZ102" s="6"/>
+      <c r="NDB102" s="6"/>
+      <c r="NDD102" s="6"/>
+      <c r="NDF102" s="6"/>
+      <c r="NDH102" s="6"/>
+      <c r="NDJ102" s="6"/>
+      <c r="NDL102" s="6"/>
+      <c r="NDN102" s="6"/>
+      <c r="NDP102" s="6"/>
+      <c r="NDR102" s="6"/>
+      <c r="NDT102" s="6"/>
+      <c r="NDV102" s="6"/>
+      <c r="NDX102" s="6"/>
+      <c r="NDZ102" s="6"/>
+      <c r="NEB102" s="6"/>
+      <c r="NED102" s="6"/>
+      <c r="NEF102" s="6"/>
+      <c r="NEH102" s="6"/>
+      <c r="NEJ102" s="6"/>
+      <c r="NEL102" s="6"/>
+      <c r="NEN102" s="6"/>
+      <c r="NEP102" s="6"/>
+      <c r="NER102" s="6"/>
+      <c r="NET102" s="6"/>
+      <c r="NEV102" s="6"/>
+      <c r="NEX102" s="6"/>
+      <c r="NEZ102" s="6"/>
+      <c r="NFB102" s="6"/>
+      <c r="NFD102" s="6"/>
+      <c r="NFF102" s="6"/>
+      <c r="NFH102" s="6"/>
+      <c r="NFJ102" s="6"/>
+      <c r="NFL102" s="6"/>
+      <c r="NFN102" s="6"/>
+      <c r="NFP102" s="6"/>
+      <c r="NFR102" s="6"/>
+      <c r="NFT102" s="6"/>
+      <c r="NFV102" s="6"/>
+      <c r="NFX102" s="6"/>
+      <c r="NFZ102" s="6"/>
+      <c r="NGB102" s="6"/>
+      <c r="NGD102" s="6"/>
+      <c r="NGF102" s="6"/>
+      <c r="NGH102" s="6"/>
+      <c r="NGJ102" s="6"/>
+      <c r="NGL102" s="6"/>
+      <c r="NGN102" s="6"/>
+      <c r="NGP102" s="6"/>
+      <c r="NGR102" s="6"/>
+      <c r="NGT102" s="6"/>
+      <c r="NGV102" s="6"/>
+      <c r="NGX102" s="6"/>
+      <c r="NGZ102" s="6"/>
+      <c r="NHB102" s="6"/>
+      <c r="NHD102" s="6"/>
+      <c r="NHF102" s="6"/>
+      <c r="NHH102" s="6"/>
+      <c r="NHJ102" s="6"/>
+      <c r="NHL102" s="6"/>
+      <c r="NHN102" s="6"/>
+      <c r="NHP102" s="6"/>
+      <c r="NHR102" s="6"/>
+      <c r="NHT102" s="6"/>
+      <c r="NHV102" s="6"/>
+      <c r="NHX102" s="6"/>
+      <c r="NHZ102" s="6"/>
+      <c r="NIB102" s="6"/>
+      <c r="NID102" s="6"/>
+      <c r="NIF102" s="6"/>
+      <c r="NIH102" s="6"/>
+      <c r="NIJ102" s="6"/>
+      <c r="NIL102" s="6"/>
+      <c r="NIN102" s="6"/>
+      <c r="NIP102" s="6"/>
+      <c r="NIR102" s="6"/>
+      <c r="NIT102" s="6"/>
+      <c r="NIV102" s="6"/>
+      <c r="NIX102" s="6"/>
+      <c r="NIZ102" s="6"/>
+      <c r="NJB102" s="6"/>
+      <c r="NJD102" s="6"/>
+      <c r="NJF102" s="6"/>
+      <c r="NJH102" s="6"/>
+      <c r="NJJ102" s="6"/>
+      <c r="NJL102" s="6"/>
+      <c r="NJN102" s="6"/>
+      <c r="NJP102" s="6"/>
+      <c r="NJR102" s="6"/>
+      <c r="NJT102" s="6"/>
+      <c r="NJV102" s="6"/>
+      <c r="NJX102" s="6"/>
+      <c r="NJZ102" s="6"/>
+      <c r="NKB102" s="6"/>
+      <c r="NKD102" s="6"/>
+      <c r="NKF102" s="6"/>
+      <c r="NKH102" s="6"/>
+      <c r="NKJ102" s="6"/>
+      <c r="NKL102" s="6"/>
+      <c r="NKN102" s="6"/>
+      <c r="NKP102" s="6"/>
+      <c r="NKR102" s="6"/>
+      <c r="NKT102" s="6"/>
+      <c r="NKV102" s="6"/>
+      <c r="NKX102" s="6"/>
+      <c r="NKZ102" s="6"/>
+      <c r="NLB102" s="6"/>
+      <c r="NLD102" s="6"/>
+      <c r="NLF102" s="6"/>
+      <c r="NLH102" s="6"/>
+      <c r="NLJ102" s="6"/>
+      <c r="NLL102" s="6"/>
+      <c r="NLN102" s="6"/>
+      <c r="NLP102" s="6"/>
+      <c r="NLR102" s="6"/>
+      <c r="NLT102" s="6"/>
+      <c r="NLV102" s="6"/>
+      <c r="NLX102" s="6"/>
+      <c r="NLZ102" s="6"/>
+      <c r="NMB102" s="6"/>
+      <c r="NMD102" s="6"/>
+      <c r="NMF102" s="6"/>
+      <c r="NMH102" s="6"/>
+      <c r="NMJ102" s="6"/>
+      <c r="NML102" s="6"/>
+      <c r="NMN102" s="6"/>
+      <c r="NMP102" s="6"/>
+      <c r="NMR102" s="6"/>
+      <c r="NMT102" s="6"/>
+      <c r="NMV102" s="6"/>
+      <c r="NMX102" s="6"/>
+      <c r="NMZ102" s="6"/>
+      <c r="NNB102" s="6"/>
+      <c r="NND102" s="6"/>
+      <c r="NNF102" s="6"/>
+      <c r="NNH102" s="6"/>
+      <c r="NNJ102" s="6"/>
+      <c r="NNL102" s="6"/>
+      <c r="NNN102" s="6"/>
+      <c r="NNP102" s="6"/>
+      <c r="NNR102" s="6"/>
+      <c r="NNT102" s="6"/>
+      <c r="NNV102" s="6"/>
+      <c r="NNX102" s="6"/>
+      <c r="NNZ102" s="6"/>
+      <c r="NOB102" s="6"/>
+      <c r="NOD102" s="6"/>
+      <c r="NOF102" s="6"/>
+      <c r="NOH102" s="6"/>
+      <c r="NOJ102" s="6"/>
+      <c r="NOL102" s="6"/>
+      <c r="NON102" s="6"/>
+      <c r="NOP102" s="6"/>
+      <c r="NOR102" s="6"/>
+      <c r="NOT102" s="6"/>
+      <c r="NOV102" s="6"/>
+      <c r="NOX102" s="6"/>
+      <c r="NOZ102" s="6"/>
+      <c r="NPB102" s="6"/>
+      <c r="NPD102" s="6"/>
+      <c r="NPF102" s="6"/>
+      <c r="NPH102" s="6"/>
+      <c r="NPJ102" s="6"/>
+      <c r="NPL102" s="6"/>
+      <c r="NPN102" s="6"/>
+      <c r="NPP102" s="6"/>
+      <c r="NPR102" s="6"/>
+      <c r="NPT102" s="6"/>
+      <c r="NPV102" s="6"/>
+      <c r="NPX102" s="6"/>
+      <c r="NPZ102" s="6"/>
+      <c r="NQB102" s="6"/>
+      <c r="NQD102" s="6"/>
+      <c r="NQF102" s="6"/>
+      <c r="NQH102" s="6"/>
+      <c r="NQJ102" s="6"/>
+      <c r="NQL102" s="6"/>
+      <c r="NQN102" s="6"/>
+      <c r="NQP102" s="6"/>
+      <c r="NQR102" s="6"/>
+      <c r="NQT102" s="6"/>
+      <c r="NQV102" s="6"/>
+      <c r="NQX102" s="6"/>
+      <c r="NQZ102" s="6"/>
+      <c r="NRB102" s="6"/>
+      <c r="NRD102" s="6"/>
+      <c r="NRF102" s="6"/>
+      <c r="NRH102" s="6"/>
+      <c r="NRJ102" s="6"/>
+      <c r="NRL102" s="6"/>
+      <c r="NRN102" s="6"/>
+      <c r="NRP102" s="6"/>
+      <c r="NRR102" s="6"/>
+      <c r="NRT102" s="6"/>
+      <c r="NRV102" s="6"/>
+      <c r="NRX102" s="6"/>
+      <c r="NRZ102" s="6"/>
+      <c r="NSB102" s="6"/>
+      <c r="NSD102" s="6"/>
+      <c r="NSF102" s="6"/>
+      <c r="NSH102" s="6"/>
+      <c r="NSJ102" s="6"/>
+      <c r="NSL102" s="6"/>
+      <c r="NSN102" s="6"/>
+      <c r="NSP102" s="6"/>
+      <c r="NSR102" s="6"/>
+      <c r="NST102" s="6"/>
+      <c r="NSV102" s="6"/>
+      <c r="NSX102" s="6"/>
+      <c r="NSZ102" s="6"/>
+      <c r="NTB102" s="6"/>
+      <c r="NTD102" s="6"/>
+      <c r="NTF102" s="6"/>
+      <c r="NTH102" s="6"/>
+      <c r="NTJ102" s="6"/>
+      <c r="NTL102" s="6"/>
+      <c r="NTN102" s="6"/>
+      <c r="NTP102" s="6"/>
+      <c r="NTR102" s="6"/>
+      <c r="NTT102" s="6"/>
+      <c r="NTV102" s="6"/>
+      <c r="NTX102" s="6"/>
+      <c r="NTZ102" s="6"/>
+      <c r="NUB102" s="6"/>
+      <c r="NUD102" s="6"/>
+      <c r="NUF102" s="6"/>
+      <c r="NUH102" s="6"/>
+      <c r="NUJ102" s="6"/>
+      <c r="NUL102" s="6"/>
+      <c r="NUN102" s="6"/>
+      <c r="NUP102" s="6"/>
+      <c r="NUR102" s="6"/>
+      <c r="NUT102" s="6"/>
+      <c r="NUV102" s="6"/>
+      <c r="NUX102" s="6"/>
+      <c r="NUZ102" s="6"/>
+      <c r="NVB102" s="6"/>
+      <c r="NVD102" s="6"/>
+      <c r="NVF102" s="6"/>
+      <c r="NVH102" s="6"/>
+      <c r="NVJ102" s="6"/>
+      <c r="NVL102" s="6"/>
+      <c r="NVN102" s="6"/>
+      <c r="NVP102" s="6"/>
+      <c r="NVR102" s="6"/>
+      <c r="NVT102" s="6"/>
+      <c r="NVV102" s="6"/>
+      <c r="NVX102" s="6"/>
+      <c r="NVZ102" s="6"/>
+      <c r="NWB102" s="6"/>
+      <c r="NWD102" s="6"/>
+      <c r="NWF102" s="6"/>
+      <c r="NWH102" s="6"/>
+      <c r="NWJ102" s="6"/>
+      <c r="NWL102" s="6"/>
+      <c r="NWN102" s="6"/>
+      <c r="NWP102" s="6"/>
+      <c r="NWR102" s="6"/>
+      <c r="NWT102" s="6"/>
+      <c r="NWV102" s="6"/>
+      <c r="NWX102" s="6"/>
+      <c r="NWZ102" s="6"/>
+      <c r="NXB102" s="6"/>
+      <c r="NXD102" s="6"/>
+      <c r="NXF102" s="6"/>
+      <c r="NXH102" s="6"/>
+      <c r="NXJ102" s="6"/>
+      <c r="NXL102" s="6"/>
+      <c r="NXN102" s="6"/>
+      <c r="NXP102" s="6"/>
+      <c r="NXR102" s="6"/>
+      <c r="NXT102" s="6"/>
+      <c r="NXV102" s="6"/>
+      <c r="NXX102" s="6"/>
+      <c r="NXZ102" s="6"/>
+      <c r="NYB102" s="6"/>
+      <c r="NYD102" s="6"/>
+      <c r="NYF102" s="6"/>
+      <c r="NYH102" s="6"/>
+      <c r="NYJ102" s="6"/>
+      <c r="NYL102" s="6"/>
+      <c r="NYN102" s="6"/>
+      <c r="NYP102" s="6"/>
+      <c r="NYR102" s="6"/>
+      <c r="NYT102" s="6"/>
+      <c r="NYV102" s="6"/>
+      <c r="NYX102" s="6"/>
+      <c r="NYZ102" s="6"/>
+      <c r="NZB102" s="6"/>
+      <c r="NZD102" s="6"/>
+      <c r="NZF102" s="6"/>
+      <c r="NZH102" s="6"/>
+      <c r="NZJ102" s="6"/>
+      <c r="NZL102" s="6"/>
+      <c r="NZN102" s="6"/>
+      <c r="NZP102" s="6"/>
+      <c r="NZR102" s="6"/>
+      <c r="NZT102" s="6"/>
+      <c r="NZV102" s="6"/>
+      <c r="NZX102" s="6"/>
+      <c r="NZZ102" s="6"/>
+      <c r="OAB102" s="6"/>
+      <c r="OAD102" s="6"/>
+      <c r="OAF102" s="6"/>
+      <c r="OAH102" s="6"/>
+      <c r="OAJ102" s="6"/>
+      <c r="OAL102" s="6"/>
+      <c r="OAN102" s="6"/>
+      <c r="OAP102" s="6"/>
+      <c r="OAR102" s="6"/>
+      <c r="OAT102" s="6"/>
+      <c r="OAV102" s="6"/>
+      <c r="OAX102" s="6"/>
+      <c r="OAZ102" s="6"/>
+      <c r="OBB102" s="6"/>
+      <c r="OBD102" s="6"/>
+      <c r="OBF102" s="6"/>
+      <c r="OBH102" s="6"/>
+      <c r="OBJ102" s="6"/>
+      <c r="OBL102" s="6"/>
+      <c r="OBN102" s="6"/>
+      <c r="OBP102" s="6"/>
+      <c r="OBR102" s="6"/>
+      <c r="OBT102" s="6"/>
+      <c r="OBV102" s="6"/>
+      <c r="OBX102" s="6"/>
+      <c r="OBZ102" s="6"/>
+      <c r="OCB102" s="6"/>
+      <c r="OCD102" s="6"/>
+      <c r="OCF102" s="6"/>
+      <c r="OCH102" s="6"/>
+      <c r="OCJ102" s="6"/>
+      <c r="OCL102" s="6"/>
+      <c r="OCN102" s="6"/>
+      <c r="OCP102" s="6"/>
+      <c r="OCR102" s="6"/>
+      <c r="OCT102" s="6"/>
+      <c r="OCV102" s="6"/>
+      <c r="OCX102" s="6"/>
+      <c r="OCZ102" s="6"/>
+      <c r="ODB102" s="6"/>
+      <c r="ODD102" s="6"/>
+      <c r="ODF102" s="6"/>
+      <c r="ODH102" s="6"/>
+      <c r="ODJ102" s="6"/>
+      <c r="ODL102" s="6"/>
+      <c r="ODN102" s="6"/>
+      <c r="ODP102" s="6"/>
+      <c r="ODR102" s="6"/>
+      <c r="ODT102" s="6"/>
+      <c r="ODV102" s="6"/>
+      <c r="ODX102" s="6"/>
+      <c r="ODZ102" s="6"/>
+      <c r="OEB102" s="6"/>
+      <c r="OED102" s="6"/>
+      <c r="OEF102" s="6"/>
+      <c r="OEH102" s="6"/>
+      <c r="OEJ102" s="6"/>
+      <c r="OEL102" s="6"/>
+      <c r="OEN102" s="6"/>
+      <c r="OEP102" s="6"/>
+      <c r="OER102" s="6"/>
+      <c r="OET102" s="6"/>
+      <c r="OEV102" s="6"/>
+      <c r="OEX102" s="6"/>
+      <c r="OEZ102" s="6"/>
+      <c r="OFB102" s="6"/>
+      <c r="OFD102" s="6"/>
+      <c r="OFF102" s="6"/>
+      <c r="OFH102" s="6"/>
+      <c r="OFJ102" s="6"/>
+      <c r="OFL102" s="6"/>
+      <c r="OFN102" s="6"/>
+      <c r="OFP102" s="6"/>
+      <c r="OFR102" s="6"/>
+      <c r="OFT102" s="6"/>
+      <c r="OFV102" s="6"/>
+      <c r="OFX102" s="6"/>
+      <c r="OFZ102" s="6"/>
+      <c r="OGB102" s="6"/>
+      <c r="OGD102" s="6"/>
+      <c r="OGF102" s="6"/>
+      <c r="OGH102" s="6"/>
+      <c r="OGJ102" s="6"/>
+      <c r="OGL102" s="6"/>
+      <c r="OGN102" s="6"/>
+      <c r="OGP102" s="6"/>
+      <c r="OGR102" s="6"/>
+      <c r="OGT102" s="6"/>
+      <c r="OGV102" s="6"/>
+      <c r="OGX102" s="6"/>
+      <c r="OGZ102" s="6"/>
+      <c r="OHB102" s="6"/>
+      <c r="OHD102" s="6"/>
+      <c r="OHF102" s="6"/>
+      <c r="OHH102" s="6"/>
+      <c r="OHJ102" s="6"/>
+      <c r="OHL102" s="6"/>
+      <c r="OHN102" s="6"/>
+      <c r="OHP102" s="6"/>
+      <c r="OHR102" s="6"/>
+      <c r="OHT102" s="6"/>
+      <c r="OHV102" s="6"/>
+      <c r="OHX102" s="6"/>
+      <c r="OHZ102" s="6"/>
+      <c r="OIB102" s="6"/>
+      <c r="OID102" s="6"/>
+      <c r="OIF102" s="6"/>
+      <c r="OIH102" s="6"/>
+      <c r="OIJ102" s="6"/>
+      <c r="OIL102" s="6"/>
+      <c r="OIN102" s="6"/>
+      <c r="OIP102" s="6"/>
+      <c r="OIR102" s="6"/>
+      <c r="OIT102" s="6"/>
+      <c r="OIV102" s="6"/>
+      <c r="OIX102" s="6"/>
+      <c r="OIZ102" s="6"/>
+      <c r="OJB102" s="6"/>
+      <c r="OJD102" s="6"/>
+      <c r="OJF102" s="6"/>
+      <c r="OJH102" s="6"/>
+      <c r="OJJ102" s="6"/>
+      <c r="OJL102" s="6"/>
+      <c r="OJN102" s="6"/>
+      <c r="OJP102" s="6"/>
+      <c r="OJR102" s="6"/>
+      <c r="OJT102" s="6"/>
+      <c r="OJV102" s="6"/>
+      <c r="OJX102" s="6"/>
+      <c r="OJZ102" s="6"/>
+      <c r="OKB102" s="6"/>
+      <c r="OKD102" s="6"/>
+      <c r="OKF102" s="6"/>
+      <c r="OKH102" s="6"/>
+      <c r="OKJ102" s="6"/>
+      <c r="OKL102" s="6"/>
+      <c r="OKN102" s="6"/>
+      <c r="OKP102" s="6"/>
+      <c r="OKR102" s="6"/>
+      <c r="OKT102" s="6"/>
+      <c r="OKV102" s="6"/>
+      <c r="OKX102" s="6"/>
+      <c r="OKZ102" s="6"/>
+      <c r="OLB102" s="6"/>
+      <c r="OLD102" s="6"/>
+      <c r="OLF102" s="6"/>
+      <c r="OLH102" s="6"/>
+      <c r="OLJ102" s="6"/>
+      <c r="OLL102" s="6"/>
+      <c r="OLN102" s="6"/>
+      <c r="OLP102" s="6"/>
+      <c r="OLR102" s="6"/>
+      <c r="OLT102" s="6"/>
+      <c r="OLV102" s="6"/>
+      <c r="OLX102" s="6"/>
+      <c r="OLZ102" s="6"/>
+      <c r="OMB102" s="6"/>
+      <c r="OMD102" s="6"/>
+      <c r="OMF102" s="6"/>
+      <c r="OMH102" s="6"/>
+      <c r="OMJ102" s="6"/>
+      <c r="OML102" s="6"/>
+      <c r="OMN102" s="6"/>
+      <c r="OMP102" s="6"/>
+      <c r="OMR102" s="6"/>
+      <c r="OMT102" s="6"/>
+      <c r="OMV102" s="6"/>
+      <c r="OMX102" s="6"/>
+      <c r="OMZ102" s="6"/>
+      <c r="ONB102" s="6"/>
+      <c r="OND102" s="6"/>
+      <c r="ONF102" s="6"/>
+      <c r="ONH102" s="6"/>
+      <c r="ONJ102" s="6"/>
+      <c r="ONL102" s="6"/>
+      <c r="ONN102" s="6"/>
+      <c r="ONP102" s="6"/>
+      <c r="ONR102" s="6"/>
+      <c r="ONT102" s="6"/>
+      <c r="ONV102" s="6"/>
+      <c r="ONX102" s="6"/>
+      <c r="ONZ102" s="6"/>
+      <c r="OOB102" s="6"/>
+      <c r="OOD102" s="6"/>
+      <c r="OOF102" s="6"/>
+      <c r="OOH102" s="6"/>
+      <c r="OOJ102" s="6"/>
+      <c r="OOL102" s="6"/>
+      <c r="OON102" s="6"/>
+      <c r="OOP102" s="6"/>
+      <c r="OOR102" s="6"/>
+      <c r="OOT102" s="6"/>
+      <c r="OOV102" s="6"/>
+      <c r="OOX102" s="6"/>
+      <c r="OOZ102" s="6"/>
+      <c r="OPB102" s="6"/>
+      <c r="OPD102" s="6"/>
+      <c r="OPF102" s="6"/>
+      <c r="OPH102" s="6"/>
+      <c r="OPJ102" s="6"/>
+      <c r="OPL102" s="6"/>
+      <c r="OPN102" s="6"/>
+      <c r="OPP102" s="6"/>
+      <c r="OPR102" s="6"/>
+      <c r="OPT102" s="6"/>
+      <c r="OPV102" s="6"/>
+      <c r="OPX102" s="6"/>
+      <c r="OPZ102" s="6"/>
+      <c r="OQB102" s="6"/>
+      <c r="OQD102" s="6"/>
+      <c r="OQF102" s="6"/>
+      <c r="OQH102" s="6"/>
+      <c r="OQJ102" s="6"/>
+      <c r="OQL102" s="6"/>
+      <c r="OQN102" s="6"/>
+      <c r="OQP102" s="6"/>
+      <c r="OQR102" s="6"/>
+      <c r="OQT102" s="6"/>
+      <c r="OQV102" s="6"/>
+      <c r="OQX102" s="6"/>
+      <c r="OQZ102" s="6"/>
+      <c r="ORB102" s="6"/>
+      <c r="ORD102" s="6"/>
+      <c r="ORF102" s="6"/>
+      <c r="ORH102" s="6"/>
+      <c r="ORJ102" s="6"/>
+      <c r="ORL102" s="6"/>
+      <c r="ORN102" s="6"/>
+      <c r="ORP102" s="6"/>
+      <c r="ORR102" s="6"/>
+      <c r="ORT102" s="6"/>
+      <c r="ORV102" s="6"/>
+      <c r="ORX102" s="6"/>
+      <c r="ORZ102" s="6"/>
+      <c r="OSB102" s="6"/>
+      <c r="OSD102" s="6"/>
+      <c r="OSF102" s="6"/>
+      <c r="OSH102" s="6"/>
+      <c r="OSJ102" s="6"/>
+      <c r="OSL102" s="6"/>
+      <c r="OSN102" s="6"/>
+      <c r="OSP102" s="6"/>
+      <c r="OSR102" s="6"/>
+      <c r="OST102" s="6"/>
+      <c r="OSV102" s="6"/>
+      <c r="OSX102" s="6"/>
+      <c r="OSZ102" s="6"/>
+      <c r="OTB102" s="6"/>
+      <c r="OTD102" s="6"/>
+      <c r="OTF102" s="6"/>
+      <c r="OTH102" s="6"/>
+      <c r="OTJ102" s="6"/>
+      <c r="OTL102" s="6"/>
+      <c r="OTN102" s="6"/>
+      <c r="OTP102" s="6"/>
+      <c r="OTR102" s="6"/>
+      <c r="OTT102" s="6"/>
+      <c r="OTV102" s="6"/>
+      <c r="OTX102" s="6"/>
+      <c r="OTZ102" s="6"/>
+      <c r="OUB102" s="6"/>
+      <c r="OUD102" s="6"/>
+      <c r="OUF102" s="6"/>
+      <c r="OUH102" s="6"/>
+      <c r="OUJ102" s="6"/>
+      <c r="OUL102" s="6"/>
+      <c r="OUN102" s="6"/>
+      <c r="OUP102" s="6"/>
+      <c r="OUR102" s="6"/>
+      <c r="OUT102" s="6"/>
+      <c r="OUV102" s="6"/>
+      <c r="OUX102" s="6"/>
+      <c r="OUZ102" s="6"/>
+      <c r="OVB102" s="6"/>
+      <c r="OVD102" s="6"/>
+      <c r="OVF102" s="6"/>
+      <c r="OVH102" s="6"/>
+      <c r="OVJ102" s="6"/>
+      <c r="OVL102" s="6"/>
+      <c r="OVN102" s="6"/>
+      <c r="OVP102" s="6"/>
+      <c r="OVR102" s="6"/>
+      <c r="OVT102" s="6"/>
+      <c r="OVV102" s="6"/>
+      <c r="OVX102" s="6"/>
+      <c r="OVZ102" s="6"/>
+      <c r="OWB102" s="6"/>
+      <c r="OWD102" s="6"/>
+      <c r="OWF102" s="6"/>
+      <c r="OWH102" s="6"/>
+      <c r="OWJ102" s="6"/>
+      <c r="OWL102" s="6"/>
+      <c r="OWN102" s="6"/>
+      <c r="OWP102" s="6"/>
+      <c r="OWR102" s="6"/>
+      <c r="OWT102" s="6"/>
+      <c r="OWV102" s="6"/>
+      <c r="OWX102" s="6"/>
+      <c r="OWZ102" s="6"/>
+      <c r="OXB102" s="6"/>
+      <c r="OXD102" s="6"/>
+      <c r="OXF102" s="6"/>
+      <c r="OXH102" s="6"/>
+      <c r="OXJ102" s="6"/>
+      <c r="OXL102" s="6"/>
+      <c r="OXN102" s="6"/>
+      <c r="OXP102" s="6"/>
+      <c r="OXR102" s="6"/>
+      <c r="OXT102" s="6"/>
+      <c r="OXV102" s="6"/>
+      <c r="OXX102" s="6"/>
+      <c r="OXZ102" s="6"/>
+      <c r="OYB102" s="6"/>
+      <c r="OYD102" s="6"/>
+      <c r="OYF102" s="6"/>
+      <c r="OYH102" s="6"/>
+      <c r="OYJ102" s="6"/>
+      <c r="OYL102" s="6"/>
+      <c r="OYN102" s="6"/>
+      <c r="OYP102" s="6"/>
+      <c r="OYR102" s="6"/>
+      <c r="OYT102" s="6"/>
+      <c r="OYV102" s="6"/>
+      <c r="OYX102" s="6"/>
+      <c r="OYZ102" s="6"/>
+      <c r="OZB102" s="6"/>
+      <c r="OZD102" s="6"/>
+      <c r="OZF102" s="6"/>
+      <c r="OZH102" s="6"/>
+      <c r="OZJ102" s="6"/>
+      <c r="OZL102" s="6"/>
+      <c r="OZN102" s="6"/>
+      <c r="OZP102" s="6"/>
+      <c r="OZR102" s="6"/>
+      <c r="OZT102" s="6"/>
+      <c r="OZV102" s="6"/>
+      <c r="OZX102" s="6"/>
+      <c r="OZZ102" s="6"/>
+      <c r="PAB102" s="6"/>
+      <c r="PAD102" s="6"/>
+      <c r="PAF102" s="6"/>
+      <c r="PAH102" s="6"/>
+      <c r="PAJ102" s="6"/>
+      <c r="PAL102" s="6"/>
+      <c r="PAN102" s="6"/>
+      <c r="PAP102" s="6"/>
+      <c r="PAR102" s="6"/>
+      <c r="PAT102" s="6"/>
+      <c r="PAV102" s="6"/>
+      <c r="PAX102" s="6"/>
+      <c r="PAZ102" s="6"/>
+      <c r="PBB102" s="6"/>
+      <c r="PBD102" s="6"/>
+      <c r="PBF102" s="6"/>
+      <c r="PBH102" s="6"/>
+      <c r="PBJ102" s="6"/>
+      <c r="PBL102" s="6"/>
+      <c r="PBN102" s="6"/>
+      <c r="PBP102" s="6"/>
+      <c r="PBR102" s="6"/>
+      <c r="PBT102" s="6"/>
+      <c r="PBV102" s="6"/>
+      <c r="PBX102" s="6"/>
+      <c r="PBZ102" s="6"/>
+      <c r="PCB102" s="6"/>
+      <c r="PCD102" s="6"/>
+      <c r="PCF102" s="6"/>
+      <c r="PCH102" s="6"/>
+      <c r="PCJ102" s="6"/>
+      <c r="PCL102" s="6"/>
+      <c r="PCN102" s="6"/>
+      <c r="PCP102" s="6"/>
+      <c r="PCR102" s="6"/>
+      <c r="PCT102" s="6"/>
+      <c r="PCV102" s="6"/>
+      <c r="PCX102" s="6"/>
+      <c r="PCZ102" s="6"/>
+      <c r="PDB102" s="6"/>
+      <c r="PDD102" s="6"/>
+      <c r="PDF102" s="6"/>
+      <c r="PDH102" s="6"/>
+      <c r="PDJ102" s="6"/>
+      <c r="PDL102" s="6"/>
+      <c r="PDN102" s="6"/>
+      <c r="PDP102" s="6"/>
+      <c r="PDR102" s="6"/>
+      <c r="PDT102" s="6"/>
+      <c r="PDV102" s="6"/>
+      <c r="PDX102" s="6"/>
+      <c r="PDZ102" s="6"/>
+      <c r="PEB102" s="6"/>
+      <c r="PED102" s="6"/>
+      <c r="PEF102" s="6"/>
+      <c r="PEH102" s="6"/>
+      <c r="PEJ102" s="6"/>
+      <c r="PEL102" s="6"/>
+      <c r="PEN102" s="6"/>
+      <c r="PEP102" s="6"/>
+      <c r="PER102" s="6"/>
+      <c r="PET102" s="6"/>
+      <c r="PEV102" s="6"/>
+      <c r="PEX102" s="6"/>
+      <c r="PEZ102" s="6"/>
+      <c r="PFB102" s="6"/>
+      <c r="PFD102" s="6"/>
+      <c r="PFF102" s="6"/>
+      <c r="PFH102" s="6"/>
+      <c r="PFJ102" s="6"/>
+      <c r="PFL102" s="6"/>
+      <c r="PFN102" s="6"/>
+      <c r="PFP102" s="6"/>
+      <c r="PFR102" s="6"/>
+      <c r="PFT102" s="6"/>
+      <c r="PFV102" s="6"/>
+      <c r="PFX102" s="6"/>
+      <c r="PFZ102" s="6"/>
+      <c r="PGB102" s="6"/>
+      <c r="PGD102" s="6"/>
+      <c r="PGF102" s="6"/>
+      <c r="PGH102" s="6"/>
+      <c r="PGJ102" s="6"/>
+      <c r="PGL102" s="6"/>
+      <c r="PGN102" s="6"/>
+      <c r="PGP102" s="6"/>
+      <c r="PGR102" s="6"/>
+      <c r="PGT102" s="6"/>
+      <c r="PGV102" s="6"/>
+      <c r="PGX102" s="6"/>
+      <c r="PGZ102" s="6"/>
+      <c r="PHB102" s="6"/>
+      <c r="PHD102" s="6"/>
+      <c r="PHF102" s="6"/>
+      <c r="PHH102" s="6"/>
+      <c r="PHJ102" s="6"/>
+      <c r="PHL102" s="6"/>
+      <c r="PHN102" s="6"/>
+      <c r="PHP102" s="6"/>
+      <c r="PHR102" s="6"/>
+      <c r="PHT102" s="6"/>
+      <c r="PHV102" s="6"/>
+      <c r="PHX102" s="6"/>
+      <c r="PHZ102" s="6"/>
+      <c r="PIB102" s="6"/>
+      <c r="PID102" s="6"/>
+      <c r="PIF102" s="6"/>
+      <c r="PIH102" s="6"/>
+      <c r="PIJ102" s="6"/>
+      <c r="PIL102" s="6"/>
+      <c r="PIN102" s="6"/>
+      <c r="PIP102" s="6"/>
+      <c r="PIR102" s="6"/>
+      <c r="PIT102" s="6"/>
+      <c r="PIV102" s="6"/>
+      <c r="PIX102" s="6"/>
+      <c r="PIZ102" s="6"/>
+      <c r="PJB102" s="6"/>
+      <c r="PJD102" s="6"/>
+      <c r="PJF102" s="6"/>
+      <c r="PJH102" s="6"/>
+      <c r="PJJ102" s="6"/>
+      <c r="PJL102" s="6"/>
+      <c r="PJN102" s="6"/>
+      <c r="PJP102" s="6"/>
+      <c r="PJR102" s="6"/>
+      <c r="PJT102" s="6"/>
+      <c r="PJV102" s="6"/>
+      <c r="PJX102" s="6"/>
+      <c r="PJZ102" s="6"/>
+      <c r="PKB102" s="6"/>
+      <c r="PKD102" s="6"/>
+      <c r="PKF102" s="6"/>
+      <c r="PKH102" s="6"/>
+      <c r="PKJ102" s="6"/>
+      <c r="PKL102" s="6"/>
+      <c r="PKN102" s="6"/>
+      <c r="PKP102" s="6"/>
+      <c r="PKR102" s="6"/>
+      <c r="PKT102" s="6"/>
+      <c r="PKV102" s="6"/>
+      <c r="PKX102" s="6"/>
+      <c r="PKZ102" s="6"/>
+      <c r="PLB102" s="6"/>
+      <c r="PLD102" s="6"/>
+      <c r="PLF102" s="6"/>
+      <c r="PLH102" s="6"/>
+      <c r="PLJ102" s="6"/>
+      <c r="PLL102" s="6"/>
+      <c r="PLN102" s="6"/>
+      <c r="PLP102" s="6"/>
+      <c r="PLR102" s="6"/>
+      <c r="PLT102" s="6"/>
+      <c r="PLV102" s="6"/>
+      <c r="PLX102" s="6"/>
+      <c r="PLZ102" s="6"/>
+      <c r="PMB102" s="6"/>
+      <c r="PMD102" s="6"/>
+      <c r="PMF102" s="6"/>
+      <c r="PMH102" s="6"/>
+      <c r="PMJ102" s="6"/>
+      <c r="PML102" s="6"/>
+      <c r="PMN102" s="6"/>
+      <c r="PMP102" s="6"/>
+      <c r="PMR102" s="6"/>
+      <c r="PMT102" s="6"/>
+      <c r="PMV102" s="6"/>
+      <c r="PMX102" s="6"/>
+      <c r="PMZ102" s="6"/>
+      <c r="PNB102" s="6"/>
+      <c r="PND102" s="6"/>
+      <c r="PNF102" s="6"/>
+      <c r="PNH102" s="6"/>
+      <c r="PNJ102" s="6"/>
+      <c r="PNL102" s="6"/>
+      <c r="PNN102" s="6"/>
+      <c r="PNP102" s="6"/>
+      <c r="PNR102" s="6"/>
+      <c r="PNT102" s="6"/>
+      <c r="PNV102" s="6"/>
+      <c r="PNX102" s="6"/>
+      <c r="PNZ102" s="6"/>
+      <c r="POB102" s="6"/>
+      <c r="POD102" s="6"/>
+      <c r="POF102" s="6"/>
+      <c r="POH102" s="6"/>
+      <c r="POJ102" s="6"/>
+      <c r="POL102" s="6"/>
+      <c r="PON102" s="6"/>
+      <c r="POP102" s="6"/>
+      <c r="POR102" s="6"/>
+      <c r="POT102" s="6"/>
+      <c r="POV102" s="6"/>
+      <c r="POX102" s="6"/>
+      <c r="POZ102" s="6"/>
+      <c r="PPB102" s="6"/>
+      <c r="PPD102" s="6"/>
+      <c r="PPF102" s="6"/>
+      <c r="PPH102" s="6"/>
+      <c r="PPJ102" s="6"/>
+      <c r="PPL102" s="6"/>
+      <c r="PPN102" s="6"/>
+      <c r="PPP102" s="6"/>
+      <c r="PPR102" s="6"/>
+      <c r="PPT102" s="6"/>
+      <c r="PPV102" s="6"/>
+      <c r="PPX102" s="6"/>
+      <c r="PPZ102" s="6"/>
+      <c r="PQB102" s="6"/>
+      <c r="PQD102" s="6"/>
+      <c r="PQF102" s="6"/>
+      <c r="PQH102" s="6"/>
+      <c r="PQJ102" s="6"/>
+      <c r="PQL102" s="6"/>
+      <c r="PQN102" s="6"/>
+      <c r="PQP102" s="6"/>
+      <c r="PQR102" s="6"/>
+      <c r="PQT102" s="6"/>
+      <c r="PQV102" s="6"/>
+      <c r="PQX102" s="6"/>
+      <c r="PQZ102" s="6"/>
+      <c r="PRB102" s="6"/>
+      <c r="PRD102" s="6"/>
+      <c r="PRF102" s="6"/>
+      <c r="PRH102" s="6"/>
+      <c r="PRJ102" s="6"/>
+      <c r="PRL102" s="6"/>
+      <c r="PRN102" s="6"/>
+      <c r="PRP102" s="6"/>
+      <c r="PRR102" s="6"/>
+      <c r="PRT102" s="6"/>
+      <c r="PRV102" s="6"/>
+      <c r="PRX102" s="6"/>
+      <c r="PRZ102" s="6"/>
+      <c r="PSB102" s="6"/>
+      <c r="PSD102" s="6"/>
+      <c r="PSF102" s="6"/>
+      <c r="PSH102" s="6"/>
+      <c r="PSJ102" s="6"/>
+      <c r="PSL102" s="6"/>
+      <c r="PSN102" s="6"/>
+      <c r="PSP102" s="6"/>
+      <c r="PSR102" s="6"/>
+      <c r="PST102" s="6"/>
+      <c r="PSV102" s="6"/>
+      <c r="PSX102" s="6"/>
+      <c r="PSZ102" s="6"/>
+      <c r="PTB102" s="6"/>
+      <c r="PTD102" s="6"/>
+      <c r="PTF102" s="6"/>
+      <c r="PTH102" s="6"/>
+      <c r="PTJ102" s="6"/>
+      <c r="PTL102" s="6"/>
+      <c r="PTN102" s="6"/>
+      <c r="PTP102" s="6"/>
+      <c r="PTR102" s="6"/>
+      <c r="PTT102" s="6"/>
+      <c r="PTV102" s="6"/>
+      <c r="PTX102" s="6"/>
+      <c r="PTZ102" s="6"/>
+      <c r="PUB102" s="6"/>
+      <c r="PUD102" s="6"/>
+      <c r="PUF102" s="6"/>
+      <c r="PUH102" s="6"/>
+      <c r="PUJ102" s="6"/>
+      <c r="PUL102" s="6"/>
+      <c r="PUN102" s="6"/>
+      <c r="PUP102" s="6"/>
+      <c r="PUR102" s="6"/>
+      <c r="PUT102" s="6"/>
+      <c r="PUV102" s="6"/>
+      <c r="PUX102" s="6"/>
+      <c r="PUZ102" s="6"/>
+      <c r="PVB102" s="6"/>
+      <c r="PVD102" s="6"/>
+      <c r="PVF102" s="6"/>
+      <c r="PVH102" s="6"/>
+      <c r="PVJ102" s="6"/>
+      <c r="PVL102" s="6"/>
+      <c r="PVN102" s="6"/>
+      <c r="PVP102" s="6"/>
+      <c r="PVR102" s="6"/>
+      <c r="PVT102" s="6"/>
+      <c r="PVV102" s="6"/>
+      <c r="PVX102" s="6"/>
+      <c r="PVZ102" s="6"/>
+      <c r="PWB102" s="6"/>
+      <c r="PWD102" s="6"/>
+      <c r="PWF102" s="6"/>
+      <c r="PWH102" s="6"/>
+      <c r="PWJ102" s="6"/>
+      <c r="PWL102" s="6"/>
+      <c r="PWN102" s="6"/>
+      <c r="PWP102" s="6"/>
+      <c r="PWR102" s="6"/>
+      <c r="PWT102" s="6"/>
+      <c r="PWV102" s="6"/>
+      <c r="PWX102" s="6"/>
+      <c r="PWZ102" s="6"/>
+      <c r="PXB102" s="6"/>
+      <c r="PXD102" s="6"/>
+      <c r="PXF102" s="6"/>
+      <c r="PXH102" s="6"/>
+      <c r="PXJ102" s="6"/>
+      <c r="PXL102" s="6"/>
+      <c r="PXN102" s="6"/>
+      <c r="PXP102" s="6"/>
+      <c r="PXR102" s="6"/>
+      <c r="PXT102" s="6"/>
+      <c r="PXV102" s="6"/>
+      <c r="PXX102" s="6"/>
+      <c r="PXZ102" s="6"/>
+      <c r="PYB102" s="6"/>
+      <c r="PYD102" s="6"/>
+      <c r="PYF102" s="6"/>
+      <c r="PYH102" s="6"/>
+      <c r="PYJ102" s="6"/>
+      <c r="PYL102" s="6"/>
+      <c r="PYN102" s="6"/>
+      <c r="PYP102" s="6"/>
+      <c r="PYR102" s="6"/>
+      <c r="PYT102" s="6"/>
+      <c r="PYV102" s="6"/>
+      <c r="PYX102" s="6"/>
+      <c r="PYZ102" s="6"/>
+      <c r="PZB102" s="6"/>
+      <c r="PZD102" s="6"/>
+      <c r="PZF102" s="6"/>
+      <c r="PZH102" s="6"/>
+      <c r="PZJ102" s="6"/>
+      <c r="PZL102" s="6"/>
+      <c r="PZN102" s="6"/>
+      <c r="PZP102" s="6"/>
+      <c r="PZR102" s="6"/>
+      <c r="PZT102" s="6"/>
+      <c r="PZV102" s="6"/>
+      <c r="PZX102" s="6"/>
+      <c r="PZZ102" s="6"/>
+      <c r="QAB102" s="6"/>
+      <c r="QAD102" s="6"/>
+      <c r="QAF102" s="6"/>
+      <c r="QAH102" s="6"/>
+      <c r="QAJ102" s="6"/>
+      <c r="QAL102" s="6"/>
+      <c r="QAN102" s="6"/>
+      <c r="QAP102" s="6"/>
+      <c r="QAR102" s="6"/>
+      <c r="QAT102" s="6"/>
+      <c r="QAV102" s="6"/>
+      <c r="QAX102" s="6"/>
+      <c r="QAZ102" s="6"/>
+      <c r="QBB102" s="6"/>
+      <c r="QBD102" s="6"/>
+      <c r="QBF102" s="6"/>
+      <c r="QBH102" s="6"/>
+      <c r="QBJ102" s="6"/>
+      <c r="QBL102" s="6"/>
+      <c r="QBN102" s="6"/>
+      <c r="QBP102" s="6"/>
+      <c r="QBR102" s="6"/>
+      <c r="QBT102" s="6"/>
+      <c r="QBV102" s="6"/>
+      <c r="QBX102" s="6"/>
+      <c r="QBZ102" s="6"/>
+      <c r="QCB102" s="6"/>
+      <c r="QCD102" s="6"/>
+      <c r="QCF102" s="6"/>
+      <c r="QCH102" s="6"/>
+      <c r="QCJ102" s="6"/>
+      <c r="QCL102" s="6"/>
+      <c r="QCN102" s="6"/>
+      <c r="QCP102" s="6"/>
+      <c r="QCR102" s="6"/>
+      <c r="QCT102" s="6"/>
+      <c r="QCV102" s="6"/>
+      <c r="QCX102" s="6"/>
+      <c r="QCZ102" s="6"/>
+      <c r="QDB102" s="6"/>
+      <c r="QDD102" s="6"/>
+      <c r="QDF102" s="6"/>
+      <c r="QDH102" s="6"/>
+      <c r="QDJ102" s="6"/>
+      <c r="QDL102" s="6"/>
+      <c r="QDN102" s="6"/>
+      <c r="QDP102" s="6"/>
+      <c r="QDR102" s="6"/>
+      <c r="QDT102" s="6"/>
+      <c r="QDV102" s="6"/>
+      <c r="QDX102" s="6"/>
+      <c r="QDZ102" s="6"/>
+      <c r="QEB102" s="6"/>
+      <c r="QED102" s="6"/>
+      <c r="QEF102" s="6"/>
+      <c r="QEH102" s="6"/>
+      <c r="QEJ102" s="6"/>
+      <c r="QEL102" s="6"/>
+      <c r="QEN102" s="6"/>
+      <c r="QEP102" s="6"/>
+      <c r="QER102" s="6"/>
+      <c r="QET102" s="6"/>
+      <c r="QEV102" s="6"/>
+      <c r="QEX102" s="6"/>
+      <c r="QEZ102" s="6"/>
+      <c r="QFB102" s="6"/>
+      <c r="QFD102" s="6"/>
+      <c r="QFF102" s="6"/>
+      <c r="QFH102" s="6"/>
+      <c r="QFJ102" s="6"/>
+      <c r="QFL102" s="6"/>
+      <c r="QFN102" s="6"/>
+      <c r="QFP102" s="6"/>
+      <c r="QFR102" s="6"/>
+      <c r="QFT102" s="6"/>
+      <c r="QFV102" s="6"/>
+      <c r="QFX102" s="6"/>
+      <c r="QFZ102" s="6"/>
+      <c r="QGB102" s="6"/>
+      <c r="QGD102" s="6"/>
+      <c r="QGF102" s="6"/>
+      <c r="QGH102" s="6"/>
+      <c r="QGJ102" s="6"/>
+      <c r="QGL102" s="6"/>
+      <c r="QGN102" s="6"/>
+      <c r="QGP102" s="6"/>
+      <c r="QGR102" s="6"/>
+      <c r="QGT102" s="6"/>
+      <c r="QGV102" s="6"/>
+      <c r="QGX102" s="6"/>
+      <c r="QGZ102" s="6"/>
+      <c r="QHB102" s="6"/>
+      <c r="QHD102" s="6"/>
+      <c r="QHF102" s="6"/>
+      <c r="QHH102" s="6"/>
+      <c r="QHJ102" s="6"/>
+      <c r="QHL102" s="6"/>
+      <c r="QHN102" s="6"/>
+      <c r="QHP102" s="6"/>
+      <c r="QHR102" s="6"/>
+      <c r="QHT102" s="6"/>
+      <c r="QHV102" s="6"/>
+      <c r="QHX102" s="6"/>
+      <c r="QHZ102" s="6"/>
+      <c r="QIB102" s="6"/>
+      <c r="QID102" s="6"/>
+      <c r="QIF102" s="6"/>
+      <c r="QIH102" s="6"/>
+      <c r="QIJ102" s="6"/>
+      <c r="QIL102" s="6"/>
+      <c r="QIN102" s="6"/>
+      <c r="QIP102" s="6"/>
+      <c r="QIR102" s="6"/>
+      <c r="QIT102" s="6"/>
+      <c r="QIV102" s="6"/>
+      <c r="QIX102" s="6"/>
+      <c r="QIZ102" s="6"/>
+      <c r="QJB102" s="6"/>
+      <c r="QJD102" s="6"/>
+      <c r="QJF102" s="6"/>
+      <c r="QJH102" s="6"/>
+      <c r="QJJ102" s="6"/>
+      <c r="QJL102" s="6"/>
+      <c r="QJN102" s="6"/>
+      <c r="QJP102" s="6"/>
+      <c r="QJR102" s="6"/>
+      <c r="QJT102" s="6"/>
+      <c r="QJV102" s="6"/>
+      <c r="QJX102" s="6"/>
+      <c r="QJZ102" s="6"/>
+      <c r="QKB102" s="6"/>
+      <c r="QKD102" s="6"/>
+      <c r="QKF102" s="6"/>
+      <c r="QKH102" s="6"/>
+      <c r="QKJ102" s="6"/>
+      <c r="QKL102" s="6"/>
+      <c r="QKN102" s="6"/>
+      <c r="QKP102" s="6"/>
+      <c r="QKR102" s="6"/>
+      <c r="QKT102" s="6"/>
+      <c r="QKV102" s="6"/>
+      <c r="QKX102" s="6"/>
+      <c r="QKZ102" s="6"/>
+      <c r="QLB102" s="6"/>
+      <c r="QLD102" s="6"/>
+      <c r="QLF102" s="6"/>
+      <c r="QLH102" s="6"/>
+      <c r="QLJ102" s="6"/>
+      <c r="QLL102" s="6"/>
+      <c r="QLN102" s="6"/>
+      <c r="QLP102" s="6"/>
+      <c r="QLR102" s="6"/>
+      <c r="QLT102" s="6"/>
+      <c r="QLV102" s="6"/>
+      <c r="QLX102" s="6"/>
+      <c r="QLZ102" s="6"/>
+      <c r="QMB102" s="6"/>
+      <c r="QMD102" s="6"/>
+      <c r="QMF102" s="6"/>
+      <c r="QMH102" s="6"/>
+      <c r="QMJ102" s="6"/>
+      <c r="QML102" s="6"/>
+      <c r="QMN102" s="6"/>
+      <c r="QMP102" s="6"/>
+      <c r="QMR102" s="6"/>
+      <c r="QMT102" s="6"/>
+      <c r="QMV102" s="6"/>
+      <c r="QMX102" s="6"/>
+      <c r="QMZ102" s="6"/>
+      <c r="QNB102" s="6"/>
+      <c r="QND102" s="6"/>
+      <c r="QNF102" s="6"/>
+      <c r="QNH102" s="6"/>
+      <c r="QNJ102" s="6"/>
+      <c r="QNL102" s="6"/>
+      <c r="QNN102" s="6"/>
+      <c r="QNP102" s="6"/>
+      <c r="QNR102" s="6"/>
+      <c r="QNT102" s="6"/>
+      <c r="QNV102" s="6"/>
+      <c r="QNX102" s="6"/>
+      <c r="QNZ102" s="6"/>
+      <c r="QOB102" s="6"/>
+      <c r="QOD102" s="6"/>
+      <c r="QOF102" s="6"/>
+      <c r="QOH102" s="6"/>
+      <c r="QOJ102" s="6"/>
+      <c r="QOL102" s="6"/>
+      <c r="QON102" s="6"/>
+      <c r="QOP102" s="6"/>
+      <c r="QOR102" s="6"/>
+      <c r="QOT102" s="6"/>
+      <c r="QOV102" s="6"/>
+      <c r="QOX102" s="6"/>
+      <c r="QOZ102" s="6"/>
+      <c r="QPB102" s="6"/>
+      <c r="QPD102" s="6"/>
+      <c r="QPF102" s="6"/>
+      <c r="QPH102" s="6"/>
+      <c r="QPJ102" s="6"/>
+      <c r="QPL102" s="6"/>
+      <c r="QPN102" s="6"/>
+      <c r="QPP102" s="6"/>
+      <c r="QPR102" s="6"/>
+      <c r="QPT102" s="6"/>
+      <c r="QPV102" s="6"/>
+      <c r="QPX102" s="6"/>
+      <c r="QPZ102" s="6"/>
+      <c r="QQB102" s="6"/>
+      <c r="QQD102" s="6"/>
+      <c r="QQF102" s="6"/>
+      <c r="QQH102" s="6"/>
+      <c r="QQJ102" s="6"/>
+      <c r="QQL102" s="6"/>
+      <c r="QQN102" s="6"/>
+      <c r="QQP102" s="6"/>
+      <c r="QQR102" s="6"/>
+      <c r="QQT102" s="6"/>
+      <c r="QQV102" s="6"/>
+      <c r="QQX102" s="6"/>
+      <c r="QQZ102" s="6"/>
+      <c r="QRB102" s="6"/>
+      <c r="QRD102" s="6"/>
+      <c r="QRF102" s="6"/>
+      <c r="QRH102" s="6"/>
+      <c r="QRJ102" s="6"/>
+      <c r="QRL102" s="6"/>
+      <c r="QRN102" s="6"/>
+      <c r="QRP102" s="6"/>
+      <c r="QRR102" s="6"/>
+      <c r="QRT102" s="6"/>
+      <c r="QRV102" s="6"/>
+      <c r="QRX102" s="6"/>
+      <c r="QRZ102" s="6"/>
+      <c r="QSB102" s="6"/>
+      <c r="QSD102" s="6"/>
+      <c r="QSF102" s="6"/>
+      <c r="QSH102" s="6"/>
+      <c r="QSJ102" s="6"/>
+      <c r="QSL102" s="6"/>
+      <c r="QSN102" s="6"/>
+      <c r="QSP102" s="6"/>
+      <c r="QSR102" s="6"/>
+      <c r="QST102" s="6"/>
+      <c r="QSV102" s="6"/>
+      <c r="QSX102" s="6"/>
+      <c r="QSZ102" s="6"/>
+      <c r="QTB102" s="6"/>
+      <c r="QTD102" s="6"/>
+      <c r="QTF102" s="6"/>
+      <c r="QTH102" s="6"/>
+      <c r="QTJ102" s="6"/>
+      <c r="QTL102" s="6"/>
+      <c r="QTN102" s="6"/>
+      <c r="QTP102" s="6"/>
+      <c r="QTR102" s="6"/>
+      <c r="QTT102" s="6"/>
+      <c r="QTV102" s="6"/>
+      <c r="QTX102" s="6"/>
+      <c r="QTZ102" s="6"/>
+      <c r="QUB102" s="6"/>
+      <c r="QUD102" s="6"/>
+      <c r="QUF102" s="6"/>
+      <c r="QUH102" s="6"/>
+      <c r="QUJ102" s="6"/>
+      <c r="QUL102" s="6"/>
+      <c r="QUN102" s="6"/>
+      <c r="QUP102" s="6"/>
+      <c r="QUR102" s="6"/>
+      <c r="QUT102" s="6"/>
+      <c r="QUV102" s="6"/>
+      <c r="QUX102" s="6"/>
+      <c r="QUZ102" s="6"/>
+      <c r="QVB102" s="6"/>
+      <c r="QVD102" s="6"/>
+      <c r="QVF102" s="6"/>
+      <c r="QVH102" s="6"/>
+      <c r="QVJ102" s="6"/>
+      <c r="QVL102" s="6"/>
+      <c r="QVN102" s="6"/>
+      <c r="QVP102" s="6"/>
+      <c r="QVR102" s="6"/>
+      <c r="QVT102" s="6"/>
+      <c r="QVV102" s="6"/>
+      <c r="QVX102" s="6"/>
+      <c r="QVZ102" s="6"/>
+      <c r="QWB102" s="6"/>
+      <c r="QWD102" s="6"/>
+      <c r="QWF102" s="6"/>
+      <c r="QWH102" s="6"/>
+      <c r="QWJ102" s="6"/>
+      <c r="QWL102" s="6"/>
+      <c r="QWN102" s="6"/>
+      <c r="QWP102" s="6"/>
+      <c r="QWR102" s="6"/>
+      <c r="QWT102" s="6"/>
+      <c r="QWV102" s="6"/>
+      <c r="QWX102" s="6"/>
+      <c r="QWZ102" s="6"/>
+      <c r="QXB102" s="6"/>
+      <c r="QXD102" s="6"/>
+      <c r="QXF102" s="6"/>
+      <c r="QXH102" s="6"/>
+      <c r="QXJ102" s="6"/>
+      <c r="QXL102" s="6"/>
+      <c r="QXN102" s="6"/>
+      <c r="QXP102" s="6"/>
+      <c r="QXR102" s="6"/>
+      <c r="QXT102" s="6"/>
+      <c r="QXV102" s="6"/>
+      <c r="QXX102" s="6"/>
+      <c r="QXZ102" s="6"/>
+      <c r="QYB102" s="6"/>
+      <c r="QYD102" s="6"/>
+      <c r="QYF102" s="6"/>
+      <c r="QYH102" s="6"/>
+      <c r="QYJ102" s="6"/>
+      <c r="QYL102" s="6"/>
+      <c r="QYN102" s="6"/>
+      <c r="QYP102" s="6"/>
+      <c r="QYR102" s="6"/>
+      <c r="QYT102" s="6"/>
+      <c r="QYV102" s="6"/>
+      <c r="QYX102" s="6"/>
+      <c r="QYZ102" s="6"/>
+      <c r="QZB102" s="6"/>
+      <c r="QZD102" s="6"/>
+      <c r="QZF102" s="6"/>
+      <c r="QZH102" s="6"/>
+      <c r="QZJ102" s="6"/>
+      <c r="QZL102" s="6"/>
+      <c r="QZN102" s="6"/>
+      <c r="QZP102" s="6"/>
+      <c r="QZR102" s="6"/>
+      <c r="QZT102" s="6"/>
+      <c r="QZV102" s="6"/>
+      <c r="QZX102" s="6"/>
+      <c r="QZZ102" s="6"/>
+      <c r="RAB102" s="6"/>
+      <c r="RAD102" s="6"/>
+      <c r="RAF102" s="6"/>
+      <c r="RAH102" s="6"/>
+      <c r="RAJ102" s="6"/>
+      <c r="RAL102" s="6"/>
+      <c r="RAN102" s="6"/>
+      <c r="RAP102" s="6"/>
+      <c r="RAR102" s="6"/>
+      <c r="RAT102" s="6"/>
+      <c r="RAV102" s="6"/>
+      <c r="RAX102" s="6"/>
+      <c r="RAZ102" s="6"/>
+      <c r="RBB102" s="6"/>
+      <c r="RBD102" s="6"/>
+      <c r="RBF102" s="6"/>
+      <c r="RBH102" s="6"/>
+      <c r="RBJ102" s="6"/>
+      <c r="RBL102" s="6"/>
+      <c r="RBN102" s="6"/>
+      <c r="RBP102" s="6"/>
+      <c r="RBR102" s="6"/>
+      <c r="RBT102" s="6"/>
+      <c r="RBV102" s="6"/>
+      <c r="RBX102" s="6"/>
+      <c r="RBZ102" s="6"/>
+      <c r="RCB102" s="6"/>
+      <c r="RCD102" s="6"/>
+      <c r="RCF102" s="6"/>
+      <c r="RCH102" s="6"/>
+      <c r="RCJ102" s="6"/>
+      <c r="RCL102" s="6"/>
+      <c r="RCN102" s="6"/>
+      <c r="RCP102" s="6"/>
+      <c r="RCR102" s="6"/>
+      <c r="RCT102" s="6"/>
+      <c r="RCV102" s="6"/>
+      <c r="RCX102" s="6"/>
+      <c r="RCZ102" s="6"/>
+      <c r="RDB102" s="6"/>
+      <c r="RDD102" s="6"/>
+      <c r="RDF102" s="6"/>
+      <c r="RDH102" s="6"/>
+      <c r="RDJ102" s="6"/>
+      <c r="RDL102" s="6"/>
+      <c r="RDN102" s="6"/>
+      <c r="RDP102" s="6"/>
+      <c r="RDR102" s="6"/>
+      <c r="RDT102" s="6"/>
+      <c r="RDV102" s="6"/>
+      <c r="RDX102" s="6"/>
+      <c r="RDZ102" s="6"/>
+      <c r="REB102" s="6"/>
+      <c r="RED102" s="6"/>
+      <c r="REF102" s="6"/>
+      <c r="REH102" s="6"/>
+      <c r="REJ102" s="6"/>
+      <c r="REL102" s="6"/>
+      <c r="REN102" s="6"/>
+      <c r="REP102" s="6"/>
+      <c r="RER102" s="6"/>
+      <c r="RET102" s="6"/>
+      <c r="REV102" s="6"/>
+      <c r="REX102" s="6"/>
+      <c r="REZ102" s="6"/>
+      <c r="RFB102" s="6"/>
+      <c r="RFD102" s="6"/>
+      <c r="RFF102" s="6"/>
+      <c r="RFH102" s="6"/>
+      <c r="RFJ102" s="6"/>
+      <c r="RFL102" s="6"/>
+      <c r="RFN102" s="6"/>
+      <c r="RFP102" s="6"/>
+      <c r="RFR102" s="6"/>
+      <c r="RFT102" s="6"/>
+      <c r="RFV102" s="6"/>
+      <c r="RFX102" s="6"/>
+      <c r="RFZ102" s="6"/>
+      <c r="RGB102" s="6"/>
+      <c r="RGD102" s="6"/>
+      <c r="RGF102" s="6"/>
+      <c r="RGH102" s="6"/>
+      <c r="RGJ102" s="6"/>
+      <c r="RGL102" s="6"/>
+      <c r="RGN102" s="6"/>
+      <c r="RGP102" s="6"/>
+      <c r="RGR102" s="6"/>
+      <c r="RGT102" s="6"/>
+      <c r="RGV102" s="6"/>
+      <c r="RGX102" s="6"/>
+      <c r="RGZ102" s="6"/>
+      <c r="RHB102" s="6"/>
+      <c r="RHD102" s="6"/>
+      <c r="RHF102" s="6"/>
+      <c r="RHH102" s="6"/>
+      <c r="RHJ102" s="6"/>
+      <c r="RHL102" s="6"/>
+      <c r="RHN102" s="6"/>
+      <c r="RHP102" s="6"/>
+      <c r="RHR102" s="6"/>
+      <c r="RHT102" s="6"/>
+      <c r="RHV102" s="6"/>
+      <c r="RHX102" s="6"/>
+      <c r="RHZ102" s="6"/>
+      <c r="RIB102" s="6"/>
+      <c r="RID102" s="6"/>
+      <c r="RIF102" s="6"/>
+      <c r="RIH102" s="6"/>
+      <c r="RIJ102" s="6"/>
+      <c r="RIL102" s="6"/>
+      <c r="RIN102" s="6"/>
+      <c r="RIP102" s="6"/>
+      <c r="RIR102" s="6"/>
+      <c r="RIT102" s="6"/>
+      <c r="RIV102" s="6"/>
+      <c r="RIX102" s="6"/>
+      <c r="RIZ102" s="6"/>
+      <c r="RJB102" s="6"/>
+      <c r="RJD102" s="6"/>
+      <c r="RJF102" s="6"/>
+      <c r="RJH102" s="6"/>
+      <c r="RJJ102" s="6"/>
+      <c r="RJL102" s="6"/>
+      <c r="RJN102" s="6"/>
+      <c r="RJP102" s="6"/>
+      <c r="RJR102" s="6"/>
+      <c r="RJT102" s="6"/>
+      <c r="RJV102" s="6"/>
+      <c r="RJX102" s="6"/>
+      <c r="RJZ102" s="6"/>
+      <c r="RKB102" s="6"/>
+      <c r="RKD102" s="6"/>
+      <c r="RKF102" s="6"/>
+      <c r="RKH102" s="6"/>
+      <c r="RKJ102" s="6"/>
+      <c r="RKL102" s="6"/>
+      <c r="RKN102" s="6"/>
+      <c r="RKP102" s="6"/>
+      <c r="RKR102" s="6"/>
+      <c r="RKT102" s="6"/>
+      <c r="RKV102" s="6"/>
+      <c r="RKX102" s="6"/>
+      <c r="RKZ102" s="6"/>
+      <c r="RLB102" s="6"/>
+      <c r="RLD102" s="6"/>
+      <c r="RLF102" s="6"/>
+      <c r="RLH102" s="6"/>
+      <c r="RLJ102" s="6"/>
+      <c r="RLL102" s="6"/>
+      <c r="RLN102" s="6"/>
+      <c r="RLP102" s="6"/>
+      <c r="RLR102" s="6"/>
+      <c r="RLT102" s="6"/>
+      <c r="RLV102" s="6"/>
+      <c r="RLX102" s="6"/>
+      <c r="RLZ102" s="6"/>
+      <c r="RMB102" s="6"/>
+      <c r="RMD102" s="6"/>
+      <c r="RMF102" s="6"/>
+      <c r="RMH102" s="6"/>
+      <c r="RMJ102" s="6"/>
+      <c r="RML102" s="6"/>
+      <c r="RMN102" s="6"/>
+      <c r="RMP102" s="6"/>
+      <c r="RMR102" s="6"/>
+      <c r="RMT102" s="6"/>
+      <c r="RMV102" s="6"/>
+      <c r="RMX102" s="6"/>
+      <c r="RMZ102" s="6"/>
+      <c r="RNB102" s="6"/>
+      <c r="RND102" s="6"/>
+      <c r="RNF102" s="6"/>
+      <c r="RNH102" s="6"/>
+      <c r="RNJ102" s="6"/>
+      <c r="RNL102" s="6"/>
+      <c r="RNN102" s="6"/>
+      <c r="RNP102" s="6"/>
+      <c r="RNR102" s="6"/>
+      <c r="RNT102" s="6"/>
+      <c r="RNV102" s="6"/>
+      <c r="RNX102" s="6"/>
+      <c r="RNZ102" s="6"/>
+      <c r="ROB102" s="6"/>
+      <c r="ROD102" s="6"/>
+      <c r="ROF102" s="6"/>
+      <c r="ROH102" s="6"/>
+      <c r="ROJ102" s="6"/>
+      <c r="ROL102" s="6"/>
+      <c r="RON102" s="6"/>
+      <c r="ROP102" s="6"/>
+      <c r="ROR102" s="6"/>
+      <c r="ROT102" s="6"/>
+      <c r="ROV102" s="6"/>
+      <c r="ROX102" s="6"/>
+      <c r="ROZ102" s="6"/>
+      <c r="RPB102" s="6"/>
+      <c r="RPD102" s="6"/>
+      <c r="RPF102" s="6"/>
+      <c r="RPH102" s="6"/>
+      <c r="RPJ102" s="6"/>
+      <c r="RPL102" s="6"/>
+      <c r="RPN102" s="6"/>
+      <c r="RPP102" s="6"/>
+      <c r="RPR102" s="6"/>
+      <c r="RPT102" s="6"/>
+      <c r="RPV102" s="6"/>
+      <c r="RPX102" s="6"/>
+      <c r="RPZ102" s="6"/>
+      <c r="RQB102" s="6"/>
+      <c r="RQD102" s="6"/>
+      <c r="RQF102" s="6"/>
+      <c r="RQH102" s="6"/>
+      <c r="RQJ102" s="6"/>
+      <c r="RQL102" s="6"/>
+      <c r="RQN102" s="6"/>
+      <c r="RQP102" s="6"/>
+      <c r="RQR102" s="6"/>
+      <c r="RQT102" s="6"/>
+      <c r="RQV102" s="6"/>
+      <c r="RQX102" s="6"/>
+      <c r="RQZ102" s="6"/>
+      <c r="RRB102" s="6"/>
+      <c r="RRD102" s="6"/>
+      <c r="RRF102" s="6"/>
+      <c r="RRH102" s="6"/>
+      <c r="RRJ102" s="6"/>
+      <c r="RRL102" s="6"/>
+      <c r="RRN102" s="6"/>
+      <c r="RRP102" s="6"/>
+      <c r="RRR102" s="6"/>
+      <c r="RRT102" s="6"/>
+      <c r="RRV102" s="6"/>
+      <c r="RRX102" s="6"/>
+      <c r="RRZ102" s="6"/>
+      <c r="RSB102" s="6"/>
+      <c r="RSD102" s="6"/>
+      <c r="RSF102" s="6"/>
+      <c r="RSH102" s="6"/>
+      <c r="RSJ102" s="6"/>
+      <c r="RSL102" s="6"/>
+      <c r="RSN102" s="6"/>
+      <c r="RSP102" s="6"/>
+      <c r="RSR102" s="6"/>
+      <c r="RST102" s="6"/>
+      <c r="RSV102" s="6"/>
+      <c r="RSX102" s="6"/>
+      <c r="RSZ102" s="6"/>
+      <c r="RTB102" s="6"/>
+      <c r="RTD102" s="6"/>
+      <c r="RTF102" s="6"/>
+      <c r="RTH102" s="6"/>
+      <c r="RTJ102" s="6"/>
+      <c r="RTL102" s="6"/>
+      <c r="RTN102" s="6"/>
+      <c r="RTP102" s="6"/>
+      <c r="RTR102" s="6"/>
+      <c r="RTT102" s="6"/>
+      <c r="RTV102" s="6"/>
+      <c r="RTX102" s="6"/>
+      <c r="RTZ102" s="6"/>
+      <c r="RUB102" s="6"/>
+      <c r="RUD102" s="6"/>
+      <c r="RUF102" s="6"/>
+      <c r="RUH102" s="6"/>
+      <c r="RUJ102" s="6"/>
+      <c r="RUL102" s="6"/>
+      <c r="RUN102" s="6"/>
+      <c r="RUP102" s="6"/>
+      <c r="RUR102" s="6"/>
+      <c r="RUT102" s="6"/>
+      <c r="RUV102" s="6"/>
+      <c r="RUX102" s="6"/>
+      <c r="RUZ102" s="6"/>
+      <c r="RVB102" s="6"/>
+      <c r="RVD102" s="6"/>
+      <c r="RVF102" s="6"/>
+      <c r="RVH102" s="6"/>
+      <c r="RVJ102" s="6"/>
+      <c r="RVL102" s="6"/>
+      <c r="RVN102" s="6"/>
+      <c r="RVP102" s="6"/>
+      <c r="RVR102" s="6"/>
+      <c r="RVT102" s="6"/>
+      <c r="RVV102" s="6"/>
+      <c r="RVX102" s="6"/>
+      <c r="RVZ102" s="6"/>
+      <c r="RWB102" s="6"/>
+      <c r="RWD102" s="6"/>
+      <c r="RWF102" s="6"/>
+      <c r="RWH102" s="6"/>
+      <c r="RWJ102" s="6"/>
+      <c r="RWL102" s="6"/>
+      <c r="RWN102" s="6"/>
+      <c r="RWP102" s="6"/>
+      <c r="RWR102" s="6"/>
+      <c r="RWT102" s="6"/>
+      <c r="RWV102" s="6"/>
+      <c r="RWX102" s="6"/>
+      <c r="RWZ102" s="6"/>
+      <c r="RXB102" s="6"/>
+      <c r="RXD102" s="6"/>
+      <c r="RXF102" s="6"/>
+      <c r="RXH102" s="6"/>
+      <c r="RXJ102" s="6"/>
+      <c r="RXL102" s="6"/>
+      <c r="RXN102" s="6"/>
+      <c r="RXP102" s="6"/>
+      <c r="RXR102" s="6"/>
+      <c r="RXT102" s="6"/>
+      <c r="RXV102" s="6"/>
+      <c r="RXX102" s="6"/>
+      <c r="RXZ102" s="6"/>
+      <c r="RYB102" s="6"/>
+      <c r="RYD102" s="6"/>
+      <c r="RYF102" s="6"/>
+      <c r="RYH102" s="6"/>
+      <c r="RYJ102" s="6"/>
+      <c r="RYL102" s="6"/>
+      <c r="RYN102" s="6"/>
+      <c r="RYP102" s="6"/>
+      <c r="RYR102" s="6"/>
+      <c r="RYT102" s="6"/>
+      <c r="RYV102" s="6"/>
+      <c r="RYX102" s="6"/>
+      <c r="RYZ102" s="6"/>
+      <c r="RZB102" s="6"/>
+      <c r="RZD102" s="6"/>
+      <c r="RZF102" s="6"/>
+      <c r="RZH102" s="6"/>
+      <c r="RZJ102" s="6"/>
+      <c r="RZL102" s="6"/>
+      <c r="RZN102" s="6"/>
+      <c r="RZP102" s="6"/>
+      <c r="RZR102" s="6"/>
+      <c r="RZT102" s="6"/>
+      <c r="RZV102" s="6"/>
+      <c r="RZX102" s="6"/>
+      <c r="RZZ102" s="6"/>
+      <c r="SAB102" s="6"/>
+      <c r="SAD102" s="6"/>
+      <c r="SAF102" s="6"/>
+      <c r="SAH102" s="6"/>
+      <c r="SAJ102" s="6"/>
+      <c r="SAL102" s="6"/>
+      <c r="SAN102" s="6"/>
+      <c r="SAP102" s="6"/>
+      <c r="SAR102" s="6"/>
+      <c r="SAT102" s="6"/>
+      <c r="SAV102" s="6"/>
+      <c r="SAX102" s="6"/>
+      <c r="SAZ102" s="6"/>
+      <c r="SBB102" s="6"/>
+      <c r="SBD102" s="6"/>
+      <c r="SBF102" s="6"/>
+      <c r="SBH102" s="6"/>
+      <c r="SBJ102" s="6"/>
+      <c r="SBL102" s="6"/>
+      <c r="SBN102" s="6"/>
+      <c r="SBP102" s="6"/>
+      <c r="SBR102" s="6"/>
+      <c r="SBT102" s="6"/>
+      <c r="SBV102" s="6"/>
+      <c r="SBX102" s="6"/>
+      <c r="SBZ102" s="6"/>
+      <c r="SCB102" s="6"/>
+      <c r="SCD102" s="6"/>
+      <c r="SCF102" s="6"/>
+      <c r="SCH102" s="6"/>
+      <c r="SCJ102" s="6"/>
+      <c r="SCL102" s="6"/>
+      <c r="SCN102" s="6"/>
+      <c r="SCP102" s="6"/>
+      <c r="SCR102" s="6"/>
+      <c r="SCT102" s="6"/>
+      <c r="SCV102" s="6"/>
+      <c r="SCX102" s="6"/>
+      <c r="SCZ102" s="6"/>
+      <c r="SDB102" s="6"/>
+      <c r="SDD102" s="6"/>
+      <c r="SDF102" s="6"/>
+      <c r="SDH102" s="6"/>
+      <c r="SDJ102" s="6"/>
+      <c r="SDL102" s="6"/>
+      <c r="SDN102" s="6"/>
+      <c r="SDP102" s="6"/>
+      <c r="SDR102" s="6"/>
+      <c r="SDT102" s="6"/>
+      <c r="SDV102" s="6"/>
+      <c r="SDX102" s="6"/>
+      <c r="SDZ102" s="6"/>
+      <c r="SEB102" s="6"/>
+      <c r="SED102" s="6"/>
+      <c r="SEF102" s="6"/>
+      <c r="SEH102" s="6"/>
+      <c r="SEJ102" s="6"/>
+      <c r="SEL102" s="6"/>
+      <c r="SEN102" s="6"/>
+      <c r="SEP102" s="6"/>
+      <c r="SER102" s="6"/>
+      <c r="SET102" s="6"/>
+      <c r="SEV102" s="6"/>
+      <c r="SEX102" s="6"/>
+      <c r="SEZ102" s="6"/>
+      <c r="SFB102" s="6"/>
+      <c r="SFD102" s="6"/>
+      <c r="SFF102" s="6"/>
+      <c r="SFH102" s="6"/>
+      <c r="SFJ102" s="6"/>
+      <c r="SFL102" s="6"/>
+      <c r="SFN102" s="6"/>
+      <c r="SFP102" s="6"/>
+      <c r="SFR102" s="6"/>
+      <c r="SFT102" s="6"/>
+      <c r="SFV102" s="6"/>
+      <c r="SFX102" s="6"/>
+      <c r="SFZ102" s="6"/>
+      <c r="SGB102" s="6"/>
+      <c r="SGD102" s="6"/>
+      <c r="SGF102" s="6"/>
+      <c r="SGH102" s="6"/>
+      <c r="SGJ102" s="6"/>
+      <c r="SGL102" s="6"/>
+      <c r="SGN102" s="6"/>
+      <c r="SGP102" s="6"/>
+      <c r="SGR102" s="6"/>
+      <c r="SGT102" s="6"/>
+      <c r="SGV102" s="6"/>
+      <c r="SGX102" s="6"/>
+      <c r="SGZ102" s="6"/>
+      <c r="SHB102" s="6"/>
+      <c r="SHD102" s="6"/>
+      <c r="SHF102" s="6"/>
+      <c r="SHH102" s="6"/>
+      <c r="SHJ102" s="6"/>
+      <c r="SHL102" s="6"/>
+      <c r="SHN102" s="6"/>
+      <c r="SHP102" s="6"/>
+      <c r="SHR102" s="6"/>
+      <c r="SHT102" s="6"/>
+      <c r="SHV102" s="6"/>
+      <c r="SHX102" s="6"/>
+      <c r="SHZ102" s="6"/>
+      <c r="SIB102" s="6"/>
+      <c r="SID102" s="6"/>
+      <c r="SIF102" s="6"/>
+      <c r="SIH102" s="6"/>
+      <c r="SIJ102" s="6"/>
+      <c r="SIL102" s="6"/>
+      <c r="SIN102" s="6"/>
+      <c r="SIP102" s="6"/>
+      <c r="SIR102" s="6"/>
+      <c r="SIT102" s="6"/>
+      <c r="SIV102" s="6"/>
+      <c r="SIX102" s="6"/>
+      <c r="SIZ102" s="6"/>
+      <c r="SJB102" s="6"/>
+      <c r="SJD102" s="6"/>
+      <c r="SJF102" s="6"/>
+      <c r="SJH102" s="6"/>
+      <c r="SJJ102" s="6"/>
+      <c r="SJL102" s="6"/>
+      <c r="SJN102" s="6"/>
+      <c r="SJP102" s="6"/>
+      <c r="SJR102" s="6"/>
+      <c r="SJT102" s="6"/>
+      <c r="SJV102" s="6"/>
+      <c r="SJX102" s="6"/>
+      <c r="SJZ102" s="6"/>
+      <c r="SKB102" s="6"/>
+      <c r="SKD102" s="6"/>
+      <c r="SKF102" s="6"/>
+      <c r="SKH102" s="6"/>
+      <c r="SKJ102" s="6"/>
+      <c r="SKL102" s="6"/>
+      <c r="SKN102" s="6"/>
+      <c r="SKP102" s="6"/>
+      <c r="SKR102" s="6"/>
+      <c r="SKT102" s="6"/>
+      <c r="SKV102" s="6"/>
+      <c r="SKX102" s="6"/>
+      <c r="SKZ102" s="6"/>
+      <c r="SLB102" s="6"/>
+      <c r="SLD102" s="6"/>
+      <c r="SLF102" s="6"/>
+      <c r="SLH102" s="6"/>
+      <c r="SLJ102" s="6"/>
+      <c r="SLL102" s="6"/>
+      <c r="SLN102" s="6"/>
+      <c r="SLP102" s="6"/>
+      <c r="SLR102" s="6"/>
+      <c r="SLT102" s="6"/>
+      <c r="SLV102" s="6"/>
+      <c r="SLX102" s="6"/>
+      <c r="SLZ102" s="6"/>
+      <c r="SMB102" s="6"/>
+      <c r="SMD102" s="6"/>
+      <c r="SMF102" s="6"/>
+      <c r="SMH102" s="6"/>
+      <c r="SMJ102" s="6"/>
+      <c r="SML102" s="6"/>
+      <c r="SMN102" s="6"/>
+      <c r="SMP102" s="6"/>
+      <c r="SMR102" s="6"/>
+      <c r="SMT102" s="6"/>
+      <c r="SMV102" s="6"/>
+      <c r="SMX102" s="6"/>
+      <c r="SMZ102" s="6"/>
+      <c r="SNB102" s="6"/>
+      <c r="SND102" s="6"/>
+      <c r="SNF102" s="6"/>
+      <c r="SNH102" s="6"/>
+      <c r="SNJ102" s="6"/>
+      <c r="SNL102" s="6"/>
+      <c r="SNN102" s="6"/>
+      <c r="SNP102" s="6"/>
+      <c r="SNR102" s="6"/>
+      <c r="SNT102" s="6"/>
+      <c r="SNV102" s="6"/>
+      <c r="SNX102" s="6"/>
+      <c r="SNZ102" s="6"/>
+      <c r="SOB102" s="6"/>
+      <c r="SOD102" s="6"/>
+      <c r="SOF102" s="6"/>
+      <c r="SOH102" s="6"/>
+      <c r="SOJ102" s="6"/>
+      <c r="SOL102" s="6"/>
+      <c r="SON102" s="6"/>
+      <c r="SOP102" s="6"/>
+      <c r="SOR102" s="6"/>
+      <c r="SOT102" s="6"/>
+      <c r="SOV102" s="6"/>
+      <c r="SOX102" s="6"/>
+      <c r="SOZ102" s="6"/>
+      <c r="SPB102" s="6"/>
+      <c r="SPD102" s="6"/>
+      <c r="SPF102" s="6"/>
+      <c r="SPH102" s="6"/>
+      <c r="SPJ102" s="6"/>
+      <c r="SPL102" s="6"/>
+      <c r="SPN102" s="6"/>
+      <c r="SPP102" s="6"/>
+      <c r="SPR102" s="6"/>
+      <c r="SPT102" s="6"/>
+      <c r="SPV102" s="6"/>
+      <c r="SPX102" s="6"/>
+      <c r="SPZ102" s="6"/>
+      <c r="SQB102" s="6"/>
+      <c r="SQD102" s="6"/>
+      <c r="SQF102" s="6"/>
+      <c r="SQH102" s="6"/>
+      <c r="SQJ102" s="6"/>
+      <c r="SQL102" s="6"/>
+      <c r="SQN102" s="6"/>
+      <c r="SQP102" s="6"/>
+      <c r="SQR102" s="6"/>
+      <c r="SQT102" s="6"/>
+      <c r="SQV102" s="6"/>
+      <c r="SQX102" s="6"/>
+      <c r="SQZ102" s="6"/>
+      <c r="SRB102" s="6"/>
+      <c r="SRD102" s="6"/>
+      <c r="SRF102" s="6"/>
+      <c r="SRH102" s="6"/>
+      <c r="SRJ102" s="6"/>
+      <c r="SRL102" s="6"/>
+      <c r="SRN102" s="6"/>
+      <c r="SRP102" s="6"/>
+      <c r="SRR102" s="6"/>
+      <c r="SRT102" s="6"/>
+      <c r="SRV102" s="6"/>
+      <c r="SRX102" s="6"/>
+      <c r="SRZ102" s="6"/>
+      <c r="SSB102" s="6"/>
+      <c r="SSD102" s="6"/>
+      <c r="SSF102" s="6"/>
+      <c r="SSH102" s="6"/>
+      <c r="SSJ102" s="6"/>
+      <c r="SSL102" s="6"/>
+      <c r="SSN102" s="6"/>
+      <c r="SSP102" s="6"/>
+      <c r="SSR102" s="6"/>
+      <c r="SST102" s="6"/>
+      <c r="SSV102" s="6"/>
+      <c r="SSX102" s="6"/>
+      <c r="SSZ102" s="6"/>
+      <c r="STB102" s="6"/>
+      <c r="STD102" s="6"/>
+      <c r="STF102" s="6"/>
+      <c r="STH102" s="6"/>
+      <c r="STJ102" s="6"/>
+      <c r="STL102" s="6"/>
+      <c r="STN102" s="6"/>
+      <c r="STP102" s="6"/>
+      <c r="STR102" s="6"/>
+      <c r="STT102" s="6"/>
+      <c r="STV102" s="6"/>
+      <c r="STX102" s="6"/>
+      <c r="STZ102" s="6"/>
+      <c r="SUB102" s="6"/>
+      <c r="SUD102" s="6"/>
+      <c r="SUF102" s="6"/>
+      <c r="SUH102" s="6"/>
+      <c r="SUJ102" s="6"/>
+      <c r="SUL102" s="6"/>
+      <c r="SUN102" s="6"/>
+      <c r="SUP102" s="6"/>
+      <c r="SUR102" s="6"/>
+      <c r="SUT102" s="6"/>
+      <c r="SUV102" s="6"/>
+      <c r="SUX102" s="6"/>
+      <c r="SUZ102" s="6"/>
+      <c r="SVB102" s="6"/>
+      <c r="SVD102" s="6"/>
+      <c r="SVF102" s="6"/>
+      <c r="SVH102" s="6"/>
+      <c r="SVJ102" s="6"/>
+      <c r="SVL102" s="6"/>
+      <c r="SVN102" s="6"/>
+      <c r="SVP102" s="6"/>
+      <c r="SVR102" s="6"/>
+      <c r="SVT102" s="6"/>
+      <c r="SVV102" s="6"/>
+      <c r="SVX102" s="6"/>
+      <c r="SVZ102" s="6"/>
+      <c r="SWB102" s="6"/>
+      <c r="SWD102" s="6"/>
+      <c r="SWF102" s="6"/>
+      <c r="SWH102" s="6"/>
+      <c r="SWJ102" s="6"/>
+      <c r="SWL102" s="6"/>
+      <c r="SWN102" s="6"/>
+      <c r="SWP102" s="6"/>
+      <c r="SWR102" s="6"/>
+      <c r="SWT102" s="6"/>
+      <c r="SWV102" s="6"/>
+      <c r="SWX102" s="6"/>
+      <c r="SWZ102" s="6"/>
+      <c r="SXB102" s="6"/>
+      <c r="SXD102" s="6"/>
+      <c r="SXF102" s="6"/>
+      <c r="SXH102" s="6"/>
+      <c r="SXJ102" s="6"/>
+      <c r="SXL102" s="6"/>
+      <c r="SXN102" s="6"/>
+      <c r="SXP102" s="6"/>
+      <c r="SXR102" s="6"/>
+      <c r="SXT102" s="6"/>
+      <c r="SXV102" s="6"/>
+      <c r="SXX102" s="6"/>
+      <c r="SXZ102" s="6"/>
+      <c r="SYB102" s="6"/>
+      <c r="SYD102" s="6"/>
+      <c r="SYF102" s="6"/>
+      <c r="SYH102" s="6"/>
+      <c r="SYJ102" s="6"/>
+      <c r="SYL102" s="6"/>
+      <c r="SYN102" s="6"/>
+      <c r="SYP102" s="6"/>
+      <c r="SYR102" s="6"/>
+      <c r="SYT102" s="6"/>
+      <c r="SYV102" s="6"/>
+      <c r="SYX102" s="6"/>
+      <c r="SYZ102" s="6"/>
+      <c r="SZB102" s="6"/>
+      <c r="SZD102" s="6"/>
+      <c r="SZF102" s="6"/>
+      <c r="SZH102" s="6"/>
+      <c r="SZJ102" s="6"/>
+      <c r="SZL102" s="6"/>
+      <c r="SZN102" s="6"/>
+      <c r="SZP102" s="6"/>
+      <c r="SZR102" s="6"/>
+      <c r="SZT102" s="6"/>
+      <c r="SZV102" s="6"/>
+      <c r="SZX102" s="6"/>
+      <c r="SZZ102" s="6"/>
+      <c r="TAB102" s="6"/>
+      <c r="TAD102" s="6"/>
+      <c r="TAF102" s="6"/>
+      <c r="TAH102" s="6"/>
+      <c r="TAJ102" s="6"/>
+      <c r="TAL102" s="6"/>
+      <c r="TAN102" s="6"/>
+      <c r="TAP102" s="6"/>
+      <c r="TAR102" s="6"/>
+      <c r="TAT102" s="6"/>
+      <c r="TAV102" s="6"/>
+      <c r="TAX102" s="6"/>
+      <c r="TAZ102" s="6"/>
+      <c r="TBB102" s="6"/>
+      <c r="TBD102" s="6"/>
+      <c r="TBF102" s="6"/>
+      <c r="TBH102" s="6"/>
+      <c r="TBJ102" s="6"/>
+      <c r="TBL102" s="6"/>
+      <c r="TBN102" s="6"/>
+      <c r="TBP102" s="6"/>
+      <c r="TBR102" s="6"/>
+      <c r="TBT102" s="6"/>
+      <c r="TBV102" s="6"/>
+      <c r="TBX102" s="6"/>
+      <c r="TBZ102" s="6"/>
+      <c r="TCB102" s="6"/>
+      <c r="TCD102" s="6"/>
+      <c r="TCF102" s="6"/>
+      <c r="TCH102" s="6"/>
+      <c r="TCJ102" s="6"/>
+      <c r="TCL102" s="6"/>
+      <c r="TCN102" s="6"/>
+      <c r="TCP102" s="6"/>
+      <c r="TCR102" s="6"/>
+      <c r="TCT102" s="6"/>
+      <c r="TCV102" s="6"/>
+      <c r="TCX102" s="6"/>
+      <c r="TCZ102" s="6"/>
+      <c r="TDB102" s="6"/>
+      <c r="TDD102" s="6"/>
+      <c r="TDF102" s="6"/>
+      <c r="TDH102" s="6"/>
+      <c r="TDJ102" s="6"/>
+      <c r="TDL102" s="6"/>
+      <c r="TDN102" s="6"/>
+      <c r="TDP102" s="6"/>
+      <c r="TDR102" s="6"/>
+      <c r="TDT102" s="6"/>
+      <c r="TDV102" s="6"/>
+      <c r="TDX102" s="6"/>
+      <c r="TDZ102" s="6"/>
+      <c r="TEB102" s="6"/>
+      <c r="TED102" s="6"/>
+      <c r="TEF102" s="6"/>
+      <c r="TEH102" s="6"/>
+      <c r="TEJ102" s="6"/>
+      <c r="TEL102" s="6"/>
+      <c r="TEN102" s="6"/>
+      <c r="TEP102" s="6"/>
+      <c r="TER102" s="6"/>
+      <c r="TET102" s="6"/>
+      <c r="TEV102" s="6"/>
+      <c r="TEX102" s="6"/>
+      <c r="TEZ102" s="6"/>
+      <c r="TFB102" s="6"/>
+      <c r="TFD102" s="6"/>
+      <c r="TFF102" s="6"/>
+      <c r="TFH102" s="6"/>
+      <c r="TFJ102" s="6"/>
+      <c r="TFL102" s="6"/>
+      <c r="TFN102" s="6"/>
+      <c r="TFP102" s="6"/>
+      <c r="TFR102" s="6"/>
+      <c r="TFT102" s="6"/>
+      <c r="TFV102" s="6"/>
+      <c r="TFX102" s="6"/>
+      <c r="TFZ102" s="6"/>
+      <c r="TGB102" s="6"/>
+      <c r="TGD102" s="6"/>
+      <c r="TGF102" s="6"/>
+      <c r="TGH102" s="6"/>
+      <c r="TGJ102" s="6"/>
+      <c r="TGL102" s="6"/>
+      <c r="TGN102" s="6"/>
+      <c r="TGP102" s="6"/>
+      <c r="TGR102" s="6"/>
+      <c r="TGT102" s="6"/>
+      <c r="TGV102" s="6"/>
+      <c r="TGX102" s="6"/>
+      <c r="TGZ102" s="6"/>
+      <c r="THB102" s="6"/>
+      <c r="THD102" s="6"/>
+      <c r="THF102" s="6"/>
+      <c r="THH102" s="6"/>
+      <c r="THJ102" s="6"/>
+      <c r="THL102" s="6"/>
+      <c r="THN102" s="6"/>
+      <c r="THP102" s="6"/>
+      <c r="THR102" s="6"/>
+      <c r="THT102" s="6"/>
+      <c r="THV102" s="6"/>
+      <c r="THX102" s="6"/>
+      <c r="THZ102" s="6"/>
+      <c r="TIB102" s="6"/>
+      <c r="TID102" s="6"/>
+      <c r="TIF102" s="6"/>
+      <c r="TIH102" s="6"/>
+      <c r="TIJ102" s="6"/>
+      <c r="TIL102" s="6"/>
+      <c r="TIN102" s="6"/>
+      <c r="TIP102" s="6"/>
+      <c r="TIR102" s="6"/>
+      <c r="TIT102" s="6"/>
+      <c r="TIV102" s="6"/>
+      <c r="TIX102" s="6"/>
+      <c r="TIZ102" s="6"/>
+      <c r="TJB102" s="6"/>
+      <c r="TJD102" s="6"/>
+      <c r="TJF102" s="6"/>
+      <c r="TJH102" s="6"/>
+      <c r="TJJ102" s="6"/>
+      <c r="TJL102" s="6"/>
+      <c r="TJN102" s="6"/>
+      <c r="TJP102" s="6"/>
+      <c r="TJR102" s="6"/>
+      <c r="TJT102" s="6"/>
+      <c r="TJV102" s="6"/>
+      <c r="TJX102" s="6"/>
+      <c r="TJZ102" s="6"/>
+      <c r="TKB102" s="6"/>
+      <c r="TKD102" s="6"/>
+      <c r="TKF102" s="6"/>
+      <c r="TKH102" s="6"/>
+      <c r="TKJ102" s="6"/>
+      <c r="TKL102" s="6"/>
+      <c r="TKN102" s="6"/>
+      <c r="TKP102" s="6"/>
+      <c r="TKR102" s="6"/>
+      <c r="TKT102" s="6"/>
+      <c r="TKV102" s="6"/>
+      <c r="TKX102" s="6"/>
+      <c r="TKZ102" s="6"/>
+      <c r="TLB102" s="6"/>
+      <c r="TLD102" s="6"/>
+      <c r="TLF102" s="6"/>
+      <c r="TLH102" s="6"/>
+      <c r="TLJ102" s="6"/>
+      <c r="TLL102" s="6"/>
+      <c r="TLN102" s="6"/>
+      <c r="TLP102" s="6"/>
+      <c r="TLR102" s="6"/>
+      <c r="TLT102" s="6"/>
+      <c r="TLV102" s="6"/>
+      <c r="TLX102" s="6"/>
+      <c r="TLZ102" s="6"/>
+      <c r="TMB102" s="6"/>
+      <c r="TMD102" s="6"/>
+      <c r="TMF102" s="6"/>
+      <c r="TMH102" s="6"/>
+      <c r="TMJ102" s="6"/>
+      <c r="TML102" s="6"/>
+      <c r="TMN102" s="6"/>
+      <c r="TMP102" s="6"/>
+      <c r="TMR102" s="6"/>
+      <c r="TMT102" s="6"/>
+      <c r="TMV102" s="6"/>
+      <c r="TMX102" s="6"/>
+      <c r="TMZ102" s="6"/>
+      <c r="TNB102" s="6"/>
+      <c r="TND102" s="6"/>
+      <c r="TNF102" s="6"/>
+      <c r="TNH102" s="6"/>
+      <c r="TNJ102" s="6"/>
+      <c r="TNL102" s="6"/>
+      <c r="TNN102" s="6"/>
+      <c r="TNP102" s="6"/>
+      <c r="TNR102" s="6"/>
+      <c r="TNT102" s="6"/>
+      <c r="TNV102" s="6"/>
+      <c r="TNX102" s="6"/>
+      <c r="TNZ102" s="6"/>
+      <c r="TOB102" s="6"/>
+      <c r="TOD102" s="6"/>
+      <c r="TOF102" s="6"/>
+      <c r="TOH102" s="6"/>
+      <c r="TOJ102" s="6"/>
+      <c r="TOL102" s="6"/>
+      <c r="TON102" s="6"/>
+      <c r="TOP102" s="6"/>
+      <c r="TOR102" s="6"/>
+      <c r="TOT102" s="6"/>
+      <c r="TOV102" s="6"/>
+      <c r="TOX102" s="6"/>
+      <c r="TOZ102" s="6"/>
+      <c r="TPB102" s="6"/>
+      <c r="TPD102" s="6"/>
+      <c r="TPF102" s="6"/>
+      <c r="TPH102" s="6"/>
+      <c r="TPJ102" s="6"/>
+      <c r="TPL102" s="6"/>
+      <c r="TPN102" s="6"/>
+      <c r="TPP102" s="6"/>
+      <c r="TPR102" s="6"/>
+      <c r="TPT102" s="6"/>
+      <c r="TPV102" s="6"/>
+      <c r="TPX102" s="6"/>
+      <c r="TPZ102" s="6"/>
+      <c r="TQB102" s="6"/>
+      <c r="TQD102" s="6"/>
+      <c r="TQF102" s="6"/>
+      <c r="TQH102" s="6"/>
+      <c r="TQJ102" s="6"/>
+      <c r="TQL102" s="6"/>
+      <c r="TQN102" s="6"/>
+      <c r="TQP102" s="6"/>
+      <c r="TQR102" s="6"/>
+      <c r="TQT102" s="6"/>
+      <c r="TQV102" s="6"/>
+      <c r="TQX102" s="6"/>
+      <c r="TQZ102" s="6"/>
+      <c r="TRB102" s="6"/>
+      <c r="TRD102" s="6"/>
+      <c r="TRF102" s="6"/>
+      <c r="TRH102" s="6"/>
+      <c r="TRJ102" s="6"/>
+      <c r="TRL102" s="6"/>
+      <c r="TRN102" s="6"/>
+      <c r="TRP102" s="6"/>
+      <c r="TRR102" s="6"/>
+      <c r="TRT102" s="6"/>
+      <c r="TRV102" s="6"/>
+      <c r="TRX102" s="6"/>
+      <c r="TRZ102" s="6"/>
+      <c r="TSB102" s="6"/>
+      <c r="TSD102" s="6"/>
+      <c r="TSF102" s="6"/>
+      <c r="TSH102" s="6"/>
+      <c r="TSJ102" s="6"/>
+      <c r="TSL102" s="6"/>
+      <c r="TSN102" s="6"/>
+      <c r="TSP102" s="6"/>
+      <c r="TSR102" s="6"/>
+      <c r="TST102" s="6"/>
+      <c r="TSV102" s="6"/>
+      <c r="TSX102" s="6"/>
+      <c r="TSZ102" s="6"/>
+      <c r="TTB102" s="6"/>
+      <c r="TTD102" s="6"/>
+      <c r="TTF102" s="6"/>
+      <c r="TTH102" s="6"/>
+      <c r="TTJ102" s="6"/>
+      <c r="TTL102" s="6"/>
+      <c r="TTN102" s="6"/>
+      <c r="TTP102" s="6"/>
+      <c r="TTR102" s="6"/>
+      <c r="TTT102" s="6"/>
+      <c r="TTV102" s="6"/>
+      <c r="TTX102" s="6"/>
+      <c r="TTZ102" s="6"/>
+      <c r="TUB102" s="6"/>
+      <c r="TUD102" s="6"/>
+      <c r="TUF102" s="6"/>
+      <c r="TUH102" s="6"/>
+      <c r="TUJ102" s="6"/>
+      <c r="TUL102" s="6"/>
+      <c r="TUN102" s="6"/>
+      <c r="TUP102" s="6"/>
+      <c r="TUR102" s="6"/>
+      <c r="TUT102" s="6"/>
+      <c r="TUV102" s="6"/>
+      <c r="TUX102" s="6"/>
+      <c r="TUZ102" s="6"/>
+      <c r="TVB102" s="6"/>
+      <c r="TVD102" s="6"/>
+      <c r="TVF102" s="6"/>
+      <c r="TVH102" s="6"/>
+      <c r="TVJ102" s="6"/>
+      <c r="TVL102" s="6"/>
+      <c r="TVN102" s="6"/>
+      <c r="TVP102" s="6"/>
+      <c r="TVR102" s="6"/>
+      <c r="TVT102" s="6"/>
+      <c r="TVV102" s="6"/>
+      <c r="TVX102" s="6"/>
+      <c r="TVZ102" s="6"/>
+      <c r="TWB102" s="6"/>
+      <c r="TWD102" s="6"/>
+      <c r="TWF102" s="6"/>
+      <c r="TWH102" s="6"/>
+      <c r="TWJ102" s="6"/>
+      <c r="TWL102" s="6"/>
+      <c r="TWN102" s="6"/>
+      <c r="TWP102" s="6"/>
+      <c r="TWR102" s="6"/>
+      <c r="TWT102" s="6"/>
+      <c r="TWV102" s="6"/>
+      <c r="TWX102" s="6"/>
+      <c r="TWZ102" s="6"/>
+      <c r="TXB102" s="6"/>
+      <c r="TXD102" s="6"/>
+      <c r="TXF102" s="6"/>
+      <c r="TXH102" s="6"/>
+      <c r="TXJ102" s="6"/>
+      <c r="TXL102" s="6"/>
+      <c r="TXN102" s="6"/>
+      <c r="TXP102" s="6"/>
+      <c r="TXR102" s="6"/>
+      <c r="TXT102" s="6"/>
+      <c r="TXV102" s="6"/>
+      <c r="TXX102" s="6"/>
+      <c r="TXZ102" s="6"/>
+      <c r="TYB102" s="6"/>
+      <c r="TYD102" s="6"/>
+      <c r="TYF102" s="6"/>
+      <c r="TYH102" s="6"/>
+      <c r="TYJ102" s="6"/>
+      <c r="TYL102" s="6"/>
+      <c r="TYN102" s="6"/>
+      <c r="TYP102" s="6"/>
+      <c r="TYR102" s="6"/>
+      <c r="TYT102" s="6"/>
+      <c r="TYV102" s="6"/>
+      <c r="TYX102" s="6"/>
+      <c r="TYZ102" s="6"/>
+      <c r="TZB102" s="6"/>
+      <c r="TZD102" s="6"/>
+      <c r="TZF102" s="6"/>
+      <c r="TZH102" s="6"/>
+      <c r="TZJ102" s="6"/>
+      <c r="TZL102" s="6"/>
+      <c r="TZN102" s="6"/>
+      <c r="TZP102" s="6"/>
+      <c r="TZR102" s="6"/>
+      <c r="TZT102" s="6"/>
+      <c r="TZV102" s="6"/>
+      <c r="TZX102" s="6"/>
+      <c r="TZZ102" s="6"/>
+      <c r="UAB102" s="6"/>
+      <c r="UAD102" s="6"/>
+      <c r="UAF102" s="6"/>
+      <c r="UAH102" s="6"/>
+      <c r="UAJ102" s="6"/>
+      <c r="UAL102" s="6"/>
+      <c r="UAN102" s="6"/>
+      <c r="UAP102" s="6"/>
+      <c r="UAR102" s="6"/>
+      <c r="UAT102" s="6"/>
+      <c r="UAV102" s="6"/>
+      <c r="UAX102" s="6"/>
+      <c r="UAZ102" s="6"/>
+      <c r="UBB102" s="6"/>
+      <c r="UBD102" s="6"/>
+      <c r="UBF102" s="6"/>
+      <c r="UBH102" s="6"/>
+      <c r="UBJ102" s="6"/>
+      <c r="UBL102" s="6"/>
+      <c r="UBN102" s="6"/>
+      <c r="UBP102" s="6"/>
+      <c r="UBR102" s="6"/>
+      <c r="UBT102" s="6"/>
+      <c r="UBV102" s="6"/>
+      <c r="UBX102" s="6"/>
+      <c r="UBZ102" s="6"/>
+      <c r="UCB102" s="6"/>
+      <c r="UCD102" s="6"/>
+      <c r="UCF102" s="6"/>
+      <c r="UCH102" s="6"/>
+      <c r="UCJ102" s="6"/>
+      <c r="UCL102" s="6"/>
+      <c r="UCN102" s="6"/>
+      <c r="UCP102" s="6"/>
+      <c r="UCR102" s="6"/>
+      <c r="UCT102" s="6"/>
+      <c r="UCV102" s="6"/>
+      <c r="UCX102" s="6"/>
+      <c r="UCZ102" s="6"/>
+      <c r="UDB102" s="6"/>
+      <c r="UDD102" s="6"/>
+      <c r="UDF102" s="6"/>
+      <c r="UDH102" s="6"/>
+      <c r="UDJ102" s="6"/>
+      <c r="UDL102" s="6"/>
+      <c r="UDN102" s="6"/>
+      <c r="UDP102" s="6"/>
+      <c r="UDR102" s="6"/>
+      <c r="UDT102" s="6"/>
+      <c r="UDV102" s="6"/>
+      <c r="UDX102" s="6"/>
+      <c r="UDZ102" s="6"/>
+      <c r="UEB102" s="6"/>
+      <c r="UED102" s="6"/>
+      <c r="UEF102" s="6"/>
+      <c r="UEH102" s="6"/>
+      <c r="UEJ102" s="6"/>
+      <c r="UEL102" s="6"/>
+      <c r="UEN102" s="6"/>
+      <c r="UEP102" s="6"/>
+      <c r="UER102" s="6"/>
+      <c r="UET102" s="6"/>
+      <c r="UEV102" s="6"/>
+      <c r="UEX102" s="6"/>
+      <c r="UEZ102" s="6"/>
+      <c r="UFB102" s="6"/>
+      <c r="UFD102" s="6"/>
+      <c r="UFF102" s="6"/>
+      <c r="UFH102" s="6"/>
+      <c r="UFJ102" s="6"/>
+      <c r="UFL102" s="6"/>
+      <c r="UFN102" s="6"/>
+      <c r="UFP102" s="6"/>
+      <c r="UFR102" s="6"/>
+      <c r="UFT102" s="6"/>
+      <c r="UFV102" s="6"/>
+      <c r="UFX102" s="6"/>
+      <c r="UFZ102" s="6"/>
+      <c r="UGB102" s="6"/>
+      <c r="UGD102" s="6"/>
+      <c r="UGF102" s="6"/>
+      <c r="UGH102" s="6"/>
+      <c r="UGJ102" s="6"/>
+      <c r="UGL102" s="6"/>
+      <c r="UGN102" s="6"/>
+      <c r="UGP102" s="6"/>
+      <c r="UGR102" s="6"/>
+      <c r="UGT102" s="6"/>
+      <c r="UGV102" s="6"/>
+      <c r="UGX102" s="6"/>
+      <c r="UGZ102" s="6"/>
+      <c r="UHB102" s="6"/>
+      <c r="UHD102" s="6"/>
+      <c r="UHF102" s="6"/>
+      <c r="UHH102" s="6"/>
+      <c r="UHJ102" s="6"/>
+      <c r="UHL102" s="6"/>
+      <c r="UHN102" s="6"/>
+      <c r="UHP102" s="6"/>
+      <c r="UHR102" s="6"/>
+      <c r="UHT102" s="6"/>
+      <c r="UHV102" s="6"/>
+      <c r="UHX102" s="6"/>
+      <c r="UHZ102" s="6"/>
+      <c r="UIB102" s="6"/>
+      <c r="UID102" s="6"/>
+      <c r="UIF102" s="6"/>
+      <c r="UIH102" s="6"/>
+      <c r="UIJ102" s="6"/>
+      <c r="UIL102" s="6"/>
+      <c r="UIN102" s="6"/>
+      <c r="UIP102" s="6"/>
+      <c r="UIR102" s="6"/>
+      <c r="UIT102" s="6"/>
+      <c r="UIV102" s="6"/>
+      <c r="UIX102" s="6"/>
+      <c r="UIZ102" s="6"/>
+      <c r="UJB102" s="6"/>
+      <c r="UJD102" s="6"/>
+      <c r="UJF102" s="6"/>
+      <c r="UJH102" s="6"/>
+      <c r="UJJ102" s="6"/>
+      <c r="UJL102" s="6"/>
+      <c r="UJN102" s="6"/>
+      <c r="UJP102" s="6"/>
+      <c r="UJR102" s="6"/>
+      <c r="UJT102" s="6"/>
+      <c r="UJV102" s="6"/>
+      <c r="UJX102" s="6"/>
+      <c r="UJZ102" s="6"/>
+      <c r="UKB102" s="6"/>
+      <c r="UKD102" s="6"/>
+      <c r="UKF102" s="6"/>
+      <c r="UKH102" s="6"/>
+      <c r="UKJ102" s="6"/>
+      <c r="UKL102" s="6"/>
+      <c r="UKN102" s="6"/>
+      <c r="UKP102" s="6"/>
+      <c r="UKR102" s="6"/>
+      <c r="UKT102" s="6"/>
+      <c r="UKV102" s="6"/>
+      <c r="UKX102" s="6"/>
+      <c r="UKZ102" s="6"/>
+      <c r="ULB102" s="6"/>
+      <c r="ULD102" s="6"/>
+      <c r="ULF102" s="6"/>
+      <c r="ULH102" s="6"/>
+      <c r="ULJ102" s="6"/>
+      <c r="ULL102" s="6"/>
+      <c r="ULN102" s="6"/>
+      <c r="ULP102" s="6"/>
+      <c r="ULR102" s="6"/>
+      <c r="ULT102" s="6"/>
+      <c r="ULV102" s="6"/>
+      <c r="ULX102" s="6"/>
+      <c r="ULZ102" s="6"/>
+      <c r="UMB102" s="6"/>
+      <c r="UMD102" s="6"/>
+      <c r="UMF102" s="6"/>
+      <c r="UMH102" s="6"/>
+      <c r="UMJ102" s="6"/>
+      <c r="UML102" s="6"/>
+      <c r="UMN102" s="6"/>
+      <c r="UMP102" s="6"/>
+      <c r="UMR102" s="6"/>
+      <c r="UMT102" s="6"/>
+      <c r="UMV102" s="6"/>
+      <c r="UMX102" s="6"/>
+      <c r="UMZ102" s="6"/>
+      <c r="UNB102" s="6"/>
+      <c r="UND102" s="6"/>
+      <c r="UNF102" s="6"/>
+      <c r="UNH102" s="6"/>
+      <c r="UNJ102" s="6"/>
+      <c r="UNL102" s="6"/>
+      <c r="UNN102" s="6"/>
+      <c r="UNP102" s="6"/>
+      <c r="UNR102" s="6"/>
+      <c r="UNT102" s="6"/>
+      <c r="UNV102" s="6"/>
+      <c r="UNX102" s="6"/>
+      <c r="UNZ102" s="6"/>
+      <c r="UOB102" s="6"/>
+      <c r="UOD102" s="6"/>
+      <c r="UOF102" s="6"/>
+      <c r="UOH102" s="6"/>
+      <c r="UOJ102" s="6"/>
+      <c r="UOL102" s="6"/>
+      <c r="UON102" s="6"/>
+      <c r="UOP102" s="6"/>
+      <c r="UOR102" s="6"/>
+      <c r="UOT102" s="6"/>
+      <c r="UOV102" s="6"/>
+      <c r="UOX102" s="6"/>
+      <c r="UOZ102" s="6"/>
+      <c r="UPB102" s="6"/>
+      <c r="UPD102" s="6"/>
+      <c r="UPF102" s="6"/>
+      <c r="UPH102" s="6"/>
+      <c r="UPJ102" s="6"/>
+      <c r="UPL102" s="6"/>
+      <c r="UPN102" s="6"/>
+      <c r="UPP102" s="6"/>
+      <c r="UPR102" s="6"/>
+      <c r="UPT102" s="6"/>
+      <c r="UPV102" s="6"/>
+      <c r="UPX102" s="6"/>
+      <c r="UPZ102" s="6"/>
+      <c r="UQB102" s="6"/>
+      <c r="UQD102" s="6"/>
+      <c r="UQF102" s="6"/>
+      <c r="UQH102" s="6"/>
+      <c r="UQJ102" s="6"/>
+      <c r="UQL102" s="6"/>
+      <c r="UQN102" s="6"/>
+      <c r="UQP102" s="6"/>
+      <c r="UQR102" s="6"/>
+      <c r="UQT102" s="6"/>
+      <c r="UQV102" s="6"/>
+      <c r="UQX102" s="6"/>
+      <c r="UQZ102" s="6"/>
+      <c r="URB102" s="6"/>
+      <c r="URD102" s="6"/>
+      <c r="URF102" s="6"/>
+      <c r="URH102" s="6"/>
+      <c r="URJ102" s="6"/>
+      <c r="URL102" s="6"/>
+      <c r="URN102" s="6"/>
+      <c r="URP102" s="6"/>
+      <c r="URR102" s="6"/>
+      <c r="URT102" s="6"/>
+      <c r="URV102" s="6"/>
+      <c r="URX102" s="6"/>
+      <c r="URZ102" s="6"/>
+      <c r="USB102" s="6"/>
+      <c r="USD102" s="6"/>
+      <c r="USF102" s="6"/>
+      <c r="USH102" s="6"/>
+      <c r="USJ102" s="6"/>
+      <c r="USL102" s="6"/>
+      <c r="USN102" s="6"/>
+      <c r="USP102" s="6"/>
+      <c r="USR102" s="6"/>
+      <c r="UST102" s="6"/>
+      <c r="USV102" s="6"/>
+      <c r="USX102" s="6"/>
+      <c r="USZ102" s="6"/>
+      <c r="UTB102" s="6"/>
+      <c r="UTD102" s="6"/>
+      <c r="UTF102" s="6"/>
+      <c r="UTH102" s="6"/>
+      <c r="UTJ102" s="6"/>
+      <c r="UTL102" s="6"/>
+      <c r="UTN102" s="6"/>
+      <c r="UTP102" s="6"/>
+      <c r="UTR102" s="6"/>
+      <c r="UTT102" s="6"/>
+      <c r="UTV102" s="6"/>
+      <c r="UTX102" s="6"/>
+      <c r="UTZ102" s="6"/>
+      <c r="UUB102" s="6"/>
+      <c r="UUD102" s="6"/>
+      <c r="UUF102" s="6"/>
+      <c r="UUH102" s="6"/>
+      <c r="UUJ102" s="6"/>
+      <c r="UUL102" s="6"/>
+      <c r="UUN102" s="6"/>
+      <c r="UUP102" s="6"/>
+      <c r="UUR102" s="6"/>
+      <c r="UUT102" s="6"/>
+      <c r="UUV102" s="6"/>
+      <c r="UUX102" s="6"/>
+      <c r="UUZ102" s="6"/>
+      <c r="UVB102" s="6"/>
+      <c r="UVD102" s="6"/>
+      <c r="UVF102" s="6"/>
+      <c r="UVH102" s="6"/>
+      <c r="UVJ102" s="6"/>
+      <c r="UVL102" s="6"/>
+      <c r="UVN102" s="6"/>
+      <c r="UVP102" s="6"/>
+      <c r="UVR102" s="6"/>
+      <c r="UVT102" s="6"/>
+      <c r="UVV102" s="6"/>
+      <c r="UVX102" s="6"/>
+      <c r="UVZ102" s="6"/>
+      <c r="UWB102" s="6"/>
+      <c r="UWD102" s="6"/>
+      <c r="UWF102" s="6"/>
+      <c r="UWH102" s="6"/>
+      <c r="UWJ102" s="6"/>
+      <c r="UWL102" s="6"/>
+      <c r="UWN102" s="6"/>
+      <c r="UWP102" s="6"/>
+      <c r="UWR102" s="6"/>
+      <c r="UWT102" s="6"/>
+      <c r="UWV102" s="6"/>
+      <c r="UWX102" s="6"/>
+      <c r="UWZ102" s="6"/>
+      <c r="UXB102" s="6"/>
+      <c r="UXD102" s="6"/>
+      <c r="UXF102" s="6"/>
+      <c r="UXH102" s="6"/>
+      <c r="UXJ102" s="6"/>
+      <c r="UXL102" s="6"/>
+      <c r="UXN102" s="6"/>
+      <c r="UXP102" s="6"/>
+      <c r="UXR102" s="6"/>
+      <c r="UXT102" s="6"/>
+      <c r="UXV102" s="6"/>
+      <c r="UXX102" s="6"/>
+      <c r="UXZ102" s="6"/>
+      <c r="UYB102" s="6"/>
+      <c r="UYD102" s="6"/>
+      <c r="UYF102" s="6"/>
+      <c r="UYH102" s="6"/>
+      <c r="UYJ102" s="6"/>
+      <c r="UYL102" s="6"/>
+      <c r="UYN102" s="6"/>
+      <c r="UYP102" s="6"/>
+      <c r="UYR102" s="6"/>
+      <c r="UYT102" s="6"/>
+      <c r="UYV102" s="6"/>
+      <c r="UYX102" s="6"/>
+      <c r="UYZ102" s="6"/>
+      <c r="UZB102" s="6"/>
+      <c r="UZD102" s="6"/>
+      <c r="UZF102" s="6"/>
+      <c r="UZH102" s="6"/>
+      <c r="UZJ102" s="6"/>
+      <c r="UZL102" s="6"/>
+      <c r="UZN102" s="6"/>
+      <c r="UZP102" s="6"/>
+      <c r="UZR102" s="6"/>
+      <c r="UZT102" s="6"/>
+      <c r="UZV102" s="6"/>
+      <c r="UZX102" s="6"/>
+      <c r="UZZ102" s="6"/>
+      <c r="VAB102" s="6"/>
+      <c r="VAD102" s="6"/>
+      <c r="VAF102" s="6"/>
+      <c r="VAH102" s="6"/>
+      <c r="VAJ102" s="6"/>
+      <c r="VAL102" s="6"/>
+      <c r="VAN102" s="6"/>
+      <c r="VAP102" s="6"/>
+      <c r="VAR102" s="6"/>
+      <c r="VAT102" s="6"/>
+      <c r="VAV102" s="6"/>
+      <c r="VAX102" s="6"/>
+      <c r="VAZ102" s="6"/>
+      <c r="VBB102" s="6"/>
+      <c r="VBD102" s="6"/>
+      <c r="VBF102" s="6"/>
+      <c r="VBH102" s="6"/>
+      <c r="VBJ102" s="6"/>
+      <c r="VBL102" s="6"/>
+      <c r="VBN102" s="6"/>
+      <c r="VBP102" s="6"/>
+      <c r="VBR102" s="6"/>
+      <c r="VBT102" s="6"/>
+      <c r="VBV102" s="6"/>
+      <c r="VBX102" s="6"/>
+      <c r="VBZ102" s="6"/>
+      <c r="VCB102" s="6"/>
+      <c r="VCD102" s="6"/>
+      <c r="VCF102" s="6"/>
+      <c r="VCH102" s="6"/>
+      <c r="VCJ102" s="6"/>
+      <c r="VCL102" s="6"/>
+      <c r="VCN102" s="6"/>
+      <c r="VCP102" s="6"/>
+      <c r="VCR102" s="6"/>
+      <c r="VCT102" s="6"/>
+      <c r="VCV102" s="6"/>
+      <c r="VCX102" s="6"/>
+      <c r="VCZ102" s="6"/>
+      <c r="VDB102" s="6"/>
+      <c r="VDD102" s="6"/>
+      <c r="VDF102" s="6"/>
+      <c r="VDH102" s="6"/>
+      <c r="VDJ102" s="6"/>
+      <c r="VDL102" s="6"/>
+      <c r="VDN102" s="6"/>
+      <c r="VDP102" s="6"/>
+      <c r="VDR102" s="6"/>
+      <c r="VDT102" s="6"/>
+      <c r="VDV102" s="6"/>
+      <c r="VDX102" s="6"/>
+      <c r="VDZ102" s="6"/>
+      <c r="VEB102" s="6"/>
+      <c r="VED102" s="6"/>
+      <c r="VEF102" s="6"/>
+      <c r="VEH102" s="6"/>
+      <c r="VEJ102" s="6"/>
+      <c r="VEL102" s="6"/>
+      <c r="VEN102" s="6"/>
+      <c r="VEP102" s="6"/>
+      <c r="VER102" s="6"/>
+      <c r="VET102" s="6"/>
+      <c r="VEV102" s="6"/>
+      <c r="VEX102" s="6"/>
+      <c r="VEZ102" s="6"/>
+      <c r="VFB102" s="6"/>
+      <c r="VFD102" s="6"/>
+      <c r="VFF102" s="6"/>
+      <c r="VFH102" s="6"/>
+      <c r="VFJ102" s="6"/>
+      <c r="VFL102" s="6"/>
+      <c r="VFN102" s="6"/>
+      <c r="VFP102" s="6"/>
+      <c r="VFR102" s="6"/>
+      <c r="VFT102" s="6"/>
+      <c r="VFV102" s="6"/>
+      <c r="VFX102" s="6"/>
+      <c r="VFZ102" s="6"/>
+      <c r="VGB102" s="6"/>
+      <c r="VGD102" s="6"/>
+      <c r="VGF102" s="6"/>
+      <c r="VGH102" s="6"/>
+      <c r="VGJ102" s="6"/>
+      <c r="VGL102" s="6"/>
+      <c r="VGN102" s="6"/>
+      <c r="VGP102" s="6"/>
+      <c r="VGR102" s="6"/>
+      <c r="VGT102" s="6"/>
+      <c r="VGV102" s="6"/>
+      <c r="VGX102" s="6"/>
+      <c r="VGZ102" s="6"/>
+      <c r="VHB102" s="6"/>
+      <c r="VHD102" s="6"/>
+      <c r="VHF102" s="6"/>
+      <c r="VHH102" s="6"/>
+      <c r="VHJ102" s="6"/>
+      <c r="VHL102" s="6"/>
+      <c r="VHN102" s="6"/>
+      <c r="VHP102" s="6"/>
+      <c r="VHR102" s="6"/>
+      <c r="VHT102" s="6"/>
+      <c r="VHV102" s="6"/>
+      <c r="VHX102" s="6"/>
+      <c r="VHZ102" s="6"/>
+      <c r="VIB102" s="6"/>
+      <c r="VID102" s="6"/>
+      <c r="VIF102" s="6"/>
+      <c r="VIH102" s="6"/>
+      <c r="VIJ102" s="6"/>
+      <c r="VIL102" s="6"/>
+      <c r="VIN102" s="6"/>
+      <c r="VIP102" s="6"/>
+      <c r="VIR102" s="6"/>
+      <c r="VIT102" s="6"/>
+      <c r="VIV102" s="6"/>
+      <c r="VIX102" s="6"/>
+      <c r="VIZ102" s="6"/>
+      <c r="VJB102" s="6"/>
+      <c r="VJD102" s="6"/>
+      <c r="VJF102" s="6"/>
+      <c r="VJH102" s="6"/>
+      <c r="VJJ102" s="6"/>
+      <c r="VJL102" s="6"/>
+      <c r="VJN102" s="6"/>
+      <c r="VJP102" s="6"/>
+      <c r="VJR102" s="6"/>
+      <c r="VJT102" s="6"/>
+      <c r="VJV102" s="6"/>
+      <c r="VJX102" s="6"/>
+      <c r="VJZ102" s="6"/>
+      <c r="VKB102" s="6"/>
+      <c r="VKD102" s="6"/>
+      <c r="VKF102" s="6"/>
+      <c r="VKH102" s="6"/>
+      <c r="VKJ102" s="6"/>
+      <c r="VKL102" s="6"/>
+      <c r="VKN102" s="6"/>
+      <c r="VKP102" s="6"/>
+      <c r="VKR102" s="6"/>
+      <c r="VKT102" s="6"/>
+      <c r="VKV102" s="6"/>
+      <c r="VKX102" s="6"/>
+      <c r="VKZ102" s="6"/>
+      <c r="VLB102" s="6"/>
+      <c r="VLD102" s="6"/>
+      <c r="VLF102" s="6"/>
+      <c r="VLH102" s="6"/>
+      <c r="VLJ102" s="6"/>
+      <c r="VLL102" s="6"/>
+      <c r="VLN102" s="6"/>
+      <c r="VLP102" s="6"/>
+      <c r="VLR102" s="6"/>
+      <c r="VLT102" s="6"/>
+      <c r="VLV102" s="6"/>
+      <c r="VLX102" s="6"/>
+      <c r="VLZ102" s="6"/>
+      <c r="VMB102" s="6"/>
+      <c r="VMD102" s="6"/>
+      <c r="VMF102" s="6"/>
+      <c r="VMH102" s="6"/>
+      <c r="VMJ102" s="6"/>
+      <c r="VML102" s="6"/>
+      <c r="VMN102" s="6"/>
+      <c r="VMP102" s="6"/>
+      <c r="VMR102" s="6"/>
+      <c r="VMT102" s="6"/>
+      <c r="VMV102" s="6"/>
+      <c r="VMX102" s="6"/>
+      <c r="VMZ102" s="6"/>
+      <c r="VNB102" s="6"/>
+      <c r="VND102" s="6"/>
+      <c r="VNF102" s="6"/>
+      <c r="VNH102" s="6"/>
+      <c r="VNJ102" s="6"/>
+      <c r="VNL102" s="6"/>
+      <c r="VNN102" s="6"/>
+      <c r="VNP102" s="6"/>
+      <c r="VNR102" s="6"/>
+      <c r="VNT102" s="6"/>
+      <c r="VNV102" s="6"/>
+      <c r="VNX102" s="6"/>
+      <c r="VNZ102" s="6"/>
+      <c r="VOB102" s="6"/>
+      <c r="VOD102" s="6"/>
+      <c r="VOF102" s="6"/>
+      <c r="VOH102" s="6"/>
+      <c r="VOJ102" s="6"/>
+      <c r="VOL102" s="6"/>
+      <c r="VON102" s="6"/>
+      <c r="VOP102" s="6"/>
+      <c r="VOR102" s="6"/>
+      <c r="VOT102" s="6"/>
+      <c r="VOV102" s="6"/>
+      <c r="VOX102" s="6"/>
+      <c r="VOZ102" s="6"/>
+      <c r="VPB102" s="6"/>
+      <c r="VPD102" s="6"/>
+      <c r="VPF102" s="6"/>
+      <c r="VPH102" s="6"/>
+      <c r="VPJ102" s="6"/>
+      <c r="VPL102" s="6"/>
+      <c r="VPN102" s="6"/>
+      <c r="VPP102" s="6"/>
+      <c r="VPR102" s="6"/>
+      <c r="VPT102" s="6"/>
+      <c r="VPV102" s="6"/>
+      <c r="VPX102" s="6"/>
+      <c r="VPZ102" s="6"/>
+      <c r="VQB102" s="6"/>
+      <c r="VQD102" s="6"/>
+      <c r="VQF102" s="6"/>
+      <c r="VQH102" s="6"/>
+      <c r="VQJ102" s="6"/>
+      <c r="VQL102" s="6"/>
+      <c r="VQN102" s="6"/>
+      <c r="VQP102" s="6"/>
+      <c r="VQR102" s="6"/>
+      <c r="VQT102" s="6"/>
+      <c r="VQV102" s="6"/>
+      <c r="VQX102" s="6"/>
+      <c r="VQZ102" s="6"/>
+      <c r="VRB102" s="6"/>
+      <c r="VRD102" s="6"/>
+      <c r="VRF102" s="6"/>
+      <c r="VRH102" s="6"/>
+      <c r="VRJ102" s="6"/>
+      <c r="VRL102" s="6"/>
+      <c r="VRN102" s="6"/>
+      <c r="VRP102" s="6"/>
+      <c r="VRR102" s="6"/>
+      <c r="VRT102" s="6"/>
+      <c r="VRV102" s="6"/>
+      <c r="VRX102" s="6"/>
+      <c r="VRZ102" s="6"/>
+      <c r="VSB102" s="6"/>
+      <c r="VSD102" s="6"/>
+      <c r="VSF102" s="6"/>
+      <c r="VSH102" s="6"/>
+      <c r="VSJ102" s="6"/>
+      <c r="VSL102" s="6"/>
+      <c r="VSN102" s="6"/>
+      <c r="VSP102" s="6"/>
+      <c r="VSR102" s="6"/>
+      <c r="VST102" s="6"/>
+      <c r="VSV102" s="6"/>
+      <c r="VSX102" s="6"/>
+      <c r="VSZ102" s="6"/>
+      <c r="VTB102" s="6"/>
+      <c r="VTD102" s="6"/>
+      <c r="VTF102" s="6"/>
+      <c r="VTH102" s="6"/>
+      <c r="VTJ102" s="6"/>
+      <c r="VTL102" s="6"/>
+      <c r="VTN102" s="6"/>
+      <c r="VTP102" s="6"/>
+      <c r="VTR102" s="6"/>
+      <c r="VTT102" s="6"/>
+      <c r="VTV102" s="6"/>
+      <c r="VTX102" s="6"/>
+      <c r="VTZ102" s="6"/>
+      <c r="VUB102" s="6"/>
+      <c r="VUD102" s="6"/>
+      <c r="VUF102" s="6"/>
+      <c r="VUH102" s="6"/>
+      <c r="VUJ102" s="6"/>
+      <c r="VUL102" s="6"/>
+      <c r="VUN102" s="6"/>
+      <c r="VUP102" s="6"/>
+      <c r="VUR102" s="6"/>
+      <c r="VUT102" s="6"/>
+      <c r="VUV102" s="6"/>
+      <c r="VUX102" s="6"/>
+      <c r="VUZ102" s="6"/>
+      <c r="VVB102" s="6"/>
+      <c r="VVD102" s="6"/>
+      <c r="VVF102" s="6"/>
+      <c r="VVH102" s="6"/>
+      <c r="VVJ102" s="6"/>
+      <c r="VVL102" s="6"/>
+      <c r="VVN102" s="6"/>
+      <c r="VVP102" s="6"/>
+      <c r="VVR102" s="6"/>
+      <c r="VVT102" s="6"/>
+      <c r="VVV102" s="6"/>
+      <c r="VVX102" s="6"/>
+      <c r="VVZ102" s="6"/>
+      <c r="VWB102" s="6"/>
+      <c r="VWD102" s="6"/>
+      <c r="VWF102" s="6"/>
+      <c r="VWH102" s="6"/>
+      <c r="VWJ102" s="6"/>
+      <c r="VWL102" s="6"/>
+      <c r="VWN102" s="6"/>
+      <c r="VWP102" s="6"/>
+      <c r="VWR102" s="6"/>
+      <c r="VWT102" s="6"/>
+      <c r="VWV102" s="6"/>
+      <c r="VWX102" s="6"/>
+      <c r="VWZ102" s="6"/>
+      <c r="VXB102" s="6"/>
+      <c r="VXD102" s="6"/>
+      <c r="VXF102" s="6"/>
+      <c r="VXH102" s="6"/>
+      <c r="VXJ102" s="6"/>
+      <c r="VXL102" s="6"/>
+      <c r="VXN102" s="6"/>
+      <c r="VXP102" s="6"/>
+      <c r="VXR102" s="6"/>
+      <c r="VXT102" s="6"/>
+      <c r="VXV102" s="6"/>
+      <c r="VXX102" s="6"/>
+      <c r="VXZ102" s="6"/>
+      <c r="VYB102" s="6"/>
+      <c r="VYD102" s="6"/>
+      <c r="VYF102" s="6"/>
+      <c r="VYH102" s="6"/>
+      <c r="VYJ102" s="6"/>
+      <c r="VYL102" s="6"/>
+      <c r="VYN102" s="6"/>
+      <c r="VYP102" s="6"/>
+      <c r="VYR102" s="6"/>
+      <c r="VYT102" s="6"/>
+      <c r="VYV102" s="6"/>
+      <c r="VYX102" s="6"/>
+      <c r="VYZ102" s="6"/>
+      <c r="VZB102" s="6"/>
+      <c r="VZD102" s="6"/>
+      <c r="VZF102" s="6"/>
+      <c r="VZH102" s="6"/>
+      <c r="VZJ102" s="6"/>
+      <c r="VZL102" s="6"/>
+      <c r="VZN102" s="6"/>
+      <c r="VZP102" s="6"/>
+      <c r="VZR102" s="6"/>
+      <c r="VZT102" s="6"/>
+      <c r="VZV102" s="6"/>
+      <c r="VZX102" s="6"/>
+      <c r="VZZ102" s="6"/>
+      <c r="WAB102" s="6"/>
+      <c r="WAD102" s="6"/>
+      <c r="WAF102" s="6"/>
+      <c r="WAH102" s="6"/>
+      <c r="WAJ102" s="6"/>
+      <c r="WAL102" s="6"/>
+      <c r="WAN102" s="6"/>
+      <c r="WAP102" s="6"/>
+      <c r="WAR102" s="6"/>
+      <c r="WAT102" s="6"/>
+      <c r="WAV102" s="6"/>
+      <c r="WAX102" s="6"/>
+      <c r="WAZ102" s="6"/>
+      <c r="WBB102" s="6"/>
+      <c r="WBD102" s="6"/>
+      <c r="WBF102" s="6"/>
+      <c r="WBH102" s="6"/>
+      <c r="WBJ102" s="6"/>
+      <c r="WBL102" s="6"/>
+      <c r="WBN102" s="6"/>
+      <c r="WBP102" s="6"/>
+      <c r="WBR102" s="6"/>
+      <c r="WBT102" s="6"/>
+      <c r="WBV102" s="6"/>
+      <c r="WBX102" s="6"/>
+      <c r="WBZ102" s="6"/>
+      <c r="WCB102" s="6"/>
+      <c r="WCD102" s="6"/>
+      <c r="WCF102" s="6"/>
+      <c r="WCH102" s="6"/>
+      <c r="WCJ102" s="6"/>
+      <c r="WCL102" s="6"/>
+      <c r="WCN102" s="6"/>
+      <c r="WCP102" s="6"/>
+      <c r="WCR102" s="6"/>
+      <c r="WCT102" s="6"/>
+      <c r="WCV102" s="6"/>
+      <c r="WCX102" s="6"/>
+      <c r="WCZ102" s="6"/>
+      <c r="WDB102" s="6"/>
+      <c r="WDD102" s="6"/>
+      <c r="WDF102" s="6"/>
+      <c r="WDH102" s="6"/>
+      <c r="WDJ102" s="6"/>
+      <c r="WDL102" s="6"/>
+      <c r="WDN102" s="6"/>
+      <c r="WDP102" s="6"/>
+      <c r="WDR102" s="6"/>
+      <c r="WDT102" s="6"/>
+      <c r="WDV102" s="6"/>
+      <c r="WDX102" s="6"/>
+      <c r="WDZ102" s="6"/>
+      <c r="WEB102" s="6"/>
+      <c r="WED102" s="6"/>
+      <c r="WEF102" s="6"/>
+      <c r="WEH102" s="6"/>
+      <c r="WEJ102" s="6"/>
+      <c r="WEL102" s="6"/>
+      <c r="WEN102" s="6"/>
+      <c r="WEP102" s="6"/>
+      <c r="WER102" s="6"/>
+      <c r="WET102" s="6"/>
+      <c r="WEV102" s="6"/>
+      <c r="WEX102" s="6"/>
+      <c r="WEZ102" s="6"/>
+      <c r="WFB102" s="6"/>
+      <c r="WFD102" s="6"/>
+      <c r="WFF102" s="6"/>
+      <c r="WFH102" s="6"/>
+      <c r="WFJ102" s="6"/>
+      <c r="WFL102" s="6"/>
+      <c r="WFN102" s="6"/>
+      <c r="WFP102" s="6"/>
+      <c r="WFR102" s="6"/>
+      <c r="WFT102" s="6"/>
+      <c r="WFV102" s="6"/>
+      <c r="WFX102" s="6"/>
+      <c r="WFZ102" s="6"/>
+      <c r="WGB102" s="6"/>
+      <c r="WGD102" s="6"/>
+      <c r="WGF102" s="6"/>
+      <c r="WGH102" s="6"/>
+      <c r="WGJ102" s="6"/>
+      <c r="WGL102" s="6"/>
+      <c r="WGN102" s="6"/>
+      <c r="WGP102" s="6"/>
+      <c r="WGR102" s="6"/>
+      <c r="WGT102" s="6"/>
+      <c r="WGV102" s="6"/>
+      <c r="WGX102" s="6"/>
+      <c r="WGZ102" s="6"/>
+      <c r="WHB102" s="6"/>
+      <c r="WHD102" s="6"/>
+      <c r="WHF102" s="6"/>
+      <c r="WHH102" s="6"/>
+      <c r="WHJ102" s="6"/>
+      <c r="WHL102" s="6"/>
+      <c r="WHN102" s="6"/>
+      <c r="WHP102" s="6"/>
+      <c r="WHR102" s="6"/>
+      <c r="WHT102" s="6"/>
+      <c r="WHV102" s="6"/>
+      <c r="WHX102" s="6"/>
+      <c r="WHZ102" s="6"/>
+      <c r="WIB102" s="6"/>
+      <c r="WID102" s="6"/>
+      <c r="WIF102" s="6"/>
+      <c r="WIH102" s="6"/>
+      <c r="WIJ102" s="6"/>
+      <c r="WIL102" s="6"/>
+      <c r="WIN102" s="6"/>
+      <c r="WIP102" s="6"/>
+      <c r="WIR102" s="6"/>
+      <c r="WIT102" s="6"/>
+      <c r="WIV102" s="6"/>
+      <c r="WIX102" s="6"/>
+      <c r="WIZ102" s="6"/>
+      <c r="WJB102" s="6"/>
+      <c r="WJD102" s="6"/>
+      <c r="WJF102" s="6"/>
+      <c r="WJH102" s="6"/>
+      <c r="WJJ102" s="6"/>
+      <c r="WJL102" s="6"/>
+      <c r="WJN102" s="6"/>
+      <c r="WJP102" s="6"/>
+      <c r="WJR102" s="6"/>
+      <c r="WJT102" s="6"/>
+      <c r="WJV102" s="6"/>
+      <c r="WJX102" s="6"/>
+      <c r="WJZ102" s="6"/>
+      <c r="WKB102" s="6"/>
+      <c r="WKD102" s="6"/>
+      <c r="WKF102" s="6"/>
+      <c r="WKH102" s="6"/>
+      <c r="WKJ102" s="6"/>
+      <c r="WKL102" s="6"/>
+      <c r="WKN102" s="6"/>
+      <c r="WKP102" s="6"/>
+      <c r="WKR102" s="6"/>
+      <c r="WKT102" s="6"/>
+      <c r="WKV102" s="6"/>
+      <c r="WKX102" s="6"/>
+      <c r="WKZ102" s="6"/>
+      <c r="WLB102" s="6"/>
+      <c r="WLD102" s="6"/>
+      <c r="WLF102" s="6"/>
+      <c r="WLH102" s="6"/>
+      <c r="WLJ102" s="6"/>
+      <c r="WLL102" s="6"/>
+      <c r="WLN102" s="6"/>
+      <c r="WLP102" s="6"/>
+      <c r="WLR102" s="6"/>
+      <c r="WLT102" s="6"/>
+      <c r="WLV102" s="6"/>
+      <c r="WLX102" s="6"/>
+      <c r="WLZ102" s="6"/>
+      <c r="WMB102" s="6"/>
+      <c r="WMD102" s="6"/>
+      <c r="WMF102" s="6"/>
+      <c r="WMH102" s="6"/>
+      <c r="WMJ102" s="6"/>
+      <c r="WML102" s="6"/>
+      <c r="WMN102" s="6"/>
+      <c r="WMP102" s="6"/>
+      <c r="WMR102" s="6"/>
+      <c r="WMT102" s="6"/>
+      <c r="WMV102" s="6"/>
+      <c r="WMX102" s="6"/>
+      <c r="WMZ102" s="6"/>
+      <c r="WNB102" s="6"/>
+      <c r="WND102" s="6"/>
+      <c r="WNF102" s="6"/>
+      <c r="WNH102" s="6"/>
+      <c r="WNJ102" s="6"/>
+      <c r="WNL102" s="6"/>
+      <c r="WNN102" s="6"/>
+      <c r="WNP102" s="6"/>
+      <c r="WNR102" s="6"/>
+      <c r="WNT102" s="6"/>
+      <c r="WNV102" s="6"/>
+      <c r="WNX102" s="6"/>
+      <c r="WNZ102" s="6"/>
+      <c r="WOB102" s="6"/>
+      <c r="WOD102" s="6"/>
+      <c r="WOF102" s="6"/>
+      <c r="WOH102" s="6"/>
+      <c r="WOJ102" s="6"/>
+      <c r="WOL102" s="6"/>
+      <c r="WON102" s="6"/>
+      <c r="WOP102" s="6"/>
+      <c r="WOR102" s="6"/>
+      <c r="WOT102" s="6"/>
+      <c r="WOV102" s="6"/>
+      <c r="WOX102" s="6"/>
+      <c r="WOZ102" s="6"/>
+      <c r="WPB102" s="6"/>
+      <c r="WPD102" s="6"/>
+      <c r="WPF102" s="6"/>
+      <c r="WPH102" s="6"/>
+      <c r="WPJ102" s="6"/>
+      <c r="WPL102" s="6"/>
+      <c r="WPN102" s="6"/>
+      <c r="WPP102" s="6"/>
+      <c r="WPR102" s="6"/>
+      <c r="WPT102" s="6"/>
+      <c r="WPV102" s="6"/>
+      <c r="WPX102" s="6"/>
+      <c r="WPZ102" s="6"/>
+      <c r="WQB102" s="6"/>
+      <c r="WQD102" s="6"/>
+      <c r="WQF102" s="6"/>
+      <c r="WQH102" s="6"/>
+      <c r="WQJ102" s="6"/>
+      <c r="WQL102" s="6"/>
+      <c r="WQN102" s="6"/>
+      <c r="WQP102" s="6"/>
+      <c r="WQR102" s="6"/>
+      <c r="WQT102" s="6"/>
+      <c r="WQV102" s="6"/>
+      <c r="WQX102" s="6"/>
+      <c r="WQZ102" s="6"/>
+      <c r="WRB102" s="6"/>
+      <c r="WRD102" s="6"/>
+      <c r="WRF102" s="6"/>
+      <c r="WRH102" s="6"/>
+      <c r="WRJ102" s="6"/>
+      <c r="WRL102" s="6"/>
+      <c r="WRN102" s="6"/>
+      <c r="WRP102" s="6"/>
+      <c r="WRR102" s="6"/>
+      <c r="WRT102" s="6"/>
+      <c r="WRV102" s="6"/>
+      <c r="WRX102" s="6"/>
+      <c r="WRZ102" s="6"/>
+      <c r="WSB102" s="6"/>
+      <c r="WSD102" s="6"/>
+      <c r="WSF102" s="6"/>
+      <c r="WSH102" s="6"/>
+      <c r="WSJ102" s="6"/>
+      <c r="WSL102" s="6"/>
+      <c r="WSN102" s="6"/>
+      <c r="WSP102" s="6"/>
+      <c r="WSR102" s="6"/>
+      <c r="WST102" s="6"/>
+      <c r="WSV102" s="6"/>
+      <c r="WSX102" s="6"/>
+      <c r="WSZ102" s="6"/>
+      <c r="WTB102" s="6"/>
+      <c r="WTD102" s="6"/>
+      <c r="WTF102" s="6"/>
+      <c r="WTH102" s="6"/>
+      <c r="WTJ102" s="6"/>
+      <c r="WTL102" s="6"/>
+      <c r="WTN102" s="6"/>
+      <c r="WTP102" s="6"/>
+      <c r="WTR102" s="6"/>
+      <c r="WTT102" s="6"/>
+      <c r="WTV102" s="6"/>
+      <c r="WTX102" s="6"/>
+      <c r="WTZ102" s="6"/>
+      <c r="WUB102" s="6"/>
+      <c r="WUD102" s="6"/>
+      <c r="WUF102" s="6"/>
+      <c r="WUH102" s="6"/>
+      <c r="WUJ102" s="6"/>
+      <c r="WUL102" s="6"/>
+      <c r="WUN102" s="6"/>
+      <c r="WUP102" s="6"/>
+      <c r="WUR102" s="6"/>
+      <c r="WUT102" s="6"/>
+      <c r="WUV102" s="6"/>
+      <c r="WUX102" s="6"/>
+      <c r="WUZ102" s="6"/>
+      <c r="WVB102" s="6"/>
+      <c r="WVD102" s="6"/>
+      <c r="WVF102" s="6"/>
+      <c r="WVH102" s="6"/>
+      <c r="WVJ102" s="6"/>
+      <c r="WVL102" s="6"/>
+      <c r="WVN102" s="6"/>
+      <c r="WVP102" s="6"/>
+      <c r="WVR102" s="6"/>
+      <c r="WVT102" s="6"/>
+      <c r="WVV102" s="6"/>
+      <c r="WVX102" s="6"/>
+      <c r="WVZ102" s="6"/>
+      <c r="WWB102" s="6"/>
+      <c r="WWD102" s="6"/>
+      <c r="WWF102" s="6"/>
+      <c r="WWH102" s="6"/>
+      <c r="WWJ102" s="6"/>
+      <c r="WWL102" s="6"/>
+      <c r="WWN102" s="6"/>
+      <c r="WWP102" s="6"/>
+      <c r="WWR102" s="6"/>
+      <c r="WWT102" s="6"/>
+      <c r="WWV102" s="6"/>
+      <c r="WWX102" s="6"/>
+      <c r="WWZ102" s="6"/>
+      <c r="WXB102" s="6"/>
+      <c r="WXD102" s="6"/>
+      <c r="WXF102" s="6"/>
+      <c r="WXH102" s="6"/>
+      <c r="WXJ102" s="6"/>
+      <c r="WXL102" s="6"/>
+      <c r="WXN102" s="6"/>
+      <c r="WXP102" s="6"/>
+      <c r="WXR102" s="6"/>
+      <c r="WXT102" s="6"/>
+      <c r="WXV102" s="6"/>
+      <c r="WXX102" s="6"/>
+      <c r="WXZ102" s="6"/>
+      <c r="WYB102" s="6"/>
+      <c r="WYD102" s="6"/>
+      <c r="WYF102" s="6"/>
+      <c r="WYH102" s="6"/>
+      <c r="WYJ102" s="6"/>
+      <c r="WYL102" s="6"/>
+      <c r="WYN102" s="6"/>
+      <c r="WYP102" s="6"/>
+      <c r="WYR102" s="6"/>
+      <c r="WYT102" s="6"/>
+      <c r="WYV102" s="6"/>
+      <c r="WYX102" s="6"/>
+      <c r="WYZ102" s="6"/>
+      <c r="WZB102" s="6"/>
+      <c r="WZD102" s="6"/>
+      <c r="WZF102" s="6"/>
+      <c r="WZH102" s="6"/>
+      <c r="WZJ102" s="6"/>
+      <c r="WZL102" s="6"/>
+      <c r="WZN102" s="6"/>
+      <c r="WZP102" s="6"/>
+      <c r="WZR102" s="6"/>
+      <c r="WZT102" s="6"/>
+      <c r="WZV102" s="6"/>
+      <c r="WZX102" s="6"/>
+      <c r="WZZ102" s="6"/>
+      <c r="XAB102" s="6"/>
+      <c r="XAD102" s="6"/>
+      <c r="XAF102" s="6"/>
+      <c r="XAH102" s="6"/>
+      <c r="XAJ102" s="6"/>
+      <c r="XAL102" s="6"/>
+      <c r="XAN102" s="6"/>
+      <c r="XAP102" s="6"/>
+      <c r="XAR102" s="6"/>
+      <c r="XAT102" s="6"/>
+      <c r="XAV102" s="6"/>
+      <c r="XAX102" s="6"/>
+      <c r="XAZ102" s="6"/>
+      <c r="XBB102" s="6"/>
+      <c r="XBD102" s="6"/>
+      <c r="XBF102" s="6"/>
+      <c r="XBH102" s="6"/>
+      <c r="XBJ102" s="6"/>
+      <c r="XBL102" s="6"/>
+      <c r="XBN102" s="6"/>
+      <c r="XBP102" s="6"/>
+      <c r="XBR102" s="6"/>
+      <c r="XBT102" s="6"/>
+      <c r="XBV102" s="6"/>
+      <c r="XBX102" s="6"/>
+      <c r="XBZ102" s="6"/>
+      <c r="XCB102" s="6"/>
+      <c r="XCD102" s="6"/>
+      <c r="XCF102" s="6"/>
+      <c r="XCH102" s="6"/>
+      <c r="XCJ102" s="6"/>
+      <c r="XCL102" s="6"/>
+      <c r="XCN102" s="6"/>
+      <c r="XCP102" s="6"/>
+      <c r="XCR102" s="6"/>
+      <c r="XCT102" s="6"/>
+      <c r="XCV102" s="6"/>
+      <c r="XCX102" s="6"/>
+      <c r="XCZ102" s="6"/>
+      <c r="XDB102" s="6"/>
+      <c r="XDD102" s="6"/>
+      <c r="XDF102" s="6"/>
+      <c r="XDH102" s="6"/>
+      <c r="XDJ102" s="6"/>
+      <c r="XDL102" s="6"/>
+      <c r="XDN102" s="6"/>
+      <c r="XDP102" s="6"/>
+      <c r="XDR102" s="6"/>
+      <c r="XDT102" s="6"/>
+      <c r="XDV102" s="6"/>
+      <c r="XDX102" s="6"/>
+      <c r="XDZ102" s="6"/>
+      <c r="XEB102" s="6"/>
+      <c r="XED102" s="6"/>
+      <c r="XEF102" s="6"/>
+      <c r="XEH102" s="6"/>
+      <c r="XEJ102" s="6"/>
+      <c r="XEL102" s="6"/>
+      <c r="XEN102" s="6"/>
+      <c r="XEP102" s="6"/>
+      <c r="XER102" s="6"/>
+      <c r="XET102" s="6"/>
+      <c r="XEV102" s="6"/>
+      <c r="XEX102" s="6"/>
+      <c r="XEZ102" s="6"/>
+      <c r="XFB102" s="6"/>
+      <c r="XFD102" s="6"/>
+    </row>
+    <row r="103" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16384" x14ac:dyDescent="0.25">
+      <c r="A103" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B103" s="10"/>
+      <c r="C103" s="10"/>
+    </row>
+    <row r="104" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16384" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16384" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16384" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16384" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16384" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16384" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16384" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16384" x14ac:dyDescent="0.25">
+      <c r="A111" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="B111" s="10"/>
+      <c r="C111" s="10"/>
+    </row>
+    <row r="112" spans="1:1024 1026:2048 2050:3072 3074:4096 4098:5120 5122:6144 6146:7168 7170:8192 8194:9216 9218:10240 10242:11264 11266:12288 12290:13312 13314:14336 14338:15360 15362:16384" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B112" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B113" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B114" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B115" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B116" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B117" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B118" t="s">
+        <v>108</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A36:C36"/>
-  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" xr:uid="{7E2A60B6-5F3A-4B23-8FE5-01F213F08C6C}"/>
-    <hyperlink ref="B6" r:id="rId2" xr:uid="{3546B9DB-36BC-4906-B1CC-9C3F62CA4285}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>